--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>3,651</v>
+        <v>3,845</v>
       </c>
       <c r="F2" t="str">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="G2" t="str">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="H2" t="str">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="str">
-        <v>255,251,498</v>
+        <v>266,893,118</v>
       </c>
       <c r="J2" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="str">
-        <v>103,084,915</v>
+        <v>124,500,127</v>
       </c>
       <c r="L2" t="str">
-        <v>15,891,722,157</v>
+        <v>16,925,066,205</v>
       </c>
       <c r="M2" t="str">
-        <v>889,156,985</v>
+        <v>950,442,193</v>
       </c>
       <c r="N2" t="str">
-        <v>5.60%</v>
+        <v>5.62%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>2,341</v>
+        <v>2,452</v>
       </c>
       <c r="F3" t="str">
-        <v>642</v>
+        <v>675</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>4,316,959,612</v>
+        <v>4,536,658,217</v>
       </c>
       <c r="M3" t="str">
-        <v>1,099,529,337</v>
+        <v>1,179,738,284</v>
       </c>
       <c r="N3" t="str">
-        <v>25.47%</v>
+        <v>26.00%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>8,941</v>
+        <v>9,424</v>
       </c>
       <c r="F4" t="str">
-        <v>2,578</v>
+        <v>2,723</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>16,646,876,278</v>
+        <v>17,580,564,628</v>
       </c>
       <c r="M4" t="str">
-        <v>4,633,754,641</v>
+        <v>4,899,833,035</v>
       </c>
       <c r="N4" t="str">
-        <v>27.84%</v>
+        <v>27.87%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>973</v>
+        <v>1,053</v>
       </c>
       <c r="F5" t="str">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="G5" t="str">
-        <v>582</v>
+        <v>629</v>
       </c>
       <c r="H5" t="str">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I5" t="str">
-        <v>1,319,985,920</v>
+        <v>1,429,598,341</v>
       </c>
       <c r="J5" t="str">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K5" t="str">
-        <v>1,213,674,906</v>
+        <v>1,489,207,567</v>
       </c>
       <c r="L5" t="str">
-        <v>11,491,668,452</v>
+        <v>12,449,627,945</v>
       </c>
       <c r="M5" t="str">
-        <v>3,739,452,630</v>
+        <v>4,203,210,006</v>
       </c>
       <c r="N5" t="str">
-        <v>32.54%</v>
+        <v>33.76%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,298</v>
+        <v>1,369</v>
       </c>
       <c r="F6" t="str">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="G6" t="str">
-        <v>734</v>
+        <v>774</v>
       </c>
       <c r="H6" t="str">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I6" t="str">
-        <v>1,743,586,566</v>
+        <v>1,851,214,959</v>
       </c>
       <c r="J6" t="str">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K6" t="str">
-        <v>1,378,949,012</v>
+        <v>1,474,898,313</v>
       </c>
       <c r="L6" t="str">
-        <v>15,180,037,651</v>
+        <v>15,987,279,364</v>
       </c>
       <c r="M6" t="str">
-        <v>4,835,882,372</v>
+        <v>5,141,361,930</v>
       </c>
       <c r="N6" t="str">
-        <v>31.86%</v>
+        <v>32.16%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,213</v>
+        <v>1,292</v>
       </c>
       <c r="F7" t="str">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="G7" t="str">
-        <v>716</v>
+        <v>766</v>
       </c>
       <c r="H7" t="str">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I7" t="str">
-        <v>1,786,826,023</v>
+        <v>1,846,015,886</v>
       </c>
       <c r="J7" t="str">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K7" t="str">
-        <v>1,282,341,695</v>
+        <v>1,380,285,787</v>
       </c>
       <c r="L7" t="str">
-        <v>14,352,206,820</v>
+        <v>15,315,555,614</v>
       </c>
       <c r="M7" t="str">
-        <v>4,689,824,418</v>
+        <v>4,876,665,364</v>
       </c>
       <c r="N7" t="str">
-        <v>32.68%</v>
+        <v>31.84%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="F8" t="str">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G8" t="str">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="H8" t="str">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I8" t="str">
-        <v>699,781,222</v>
+        <v>763,111,978</v>
       </c>
       <c r="J8" t="str">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K8" t="str">
-        <v>709,104,417</v>
+        <v>767,980,709</v>
       </c>
       <c r="L8" t="str">
-        <v>7,265,263,477</v>
+        <v>7,747,163,455</v>
       </c>
       <c r="M8" t="str">
-        <v>2,233,006,477</v>
+        <v>2,391,173,872</v>
       </c>
       <c r="N8" t="str">
-        <v>30.74%</v>
+        <v>30.87%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>13,900</v>
+        <v>14,658</v>
       </c>
       <c r="F9" t="str">
-        <v>3,827</v>
+        <v>4,057</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>25,957,704,141</v>
+        <v>27,336,922,958</v>
       </c>
       <c r="M9" t="str">
-        <v>6,860,121,625</v>
+        <v>7,253,694,710</v>
       </c>
       <c r="N9" t="str">
-        <v>26.43%</v>
+        <v>26.53%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,461</v>
+        <v>1,537</v>
       </c>
       <c r="F10" t="str">
-        <v>681</v>
+        <v>724</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>490,121,444</v>
+        <v>514,736,669</v>
       </c>
       <c r="M10" t="str">
-        <v>204,525,802</v>
+        <v>216,026,280</v>
       </c>
       <c r="N10" t="str">
-        <v>41.73%</v>
+        <v>41.97%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,795</v>
+        <v>2,932</v>
       </c>
       <c r="F11" t="str">
-        <v>776</v>
+        <v>817</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>5,342,682,847</v>
+        <v>5,608,330,639</v>
       </c>
       <c r="M11" t="str">
-        <v>1,375,315,420</v>
+        <v>1,435,905,074</v>
       </c>
       <c r="N11" t="str">
-        <v>25.74%</v>
+        <v>25.60%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,047</v>
+        <v>2,172</v>
       </c>
       <c r="F12" t="str">
-        <v>616</v>
+        <v>651</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>3,923,860,481</v>
+        <v>4,144,925,042</v>
       </c>
       <c r="M12" t="str">
-        <v>1,094,490,124</v>
+        <v>1,150,016,445</v>
       </c>
       <c r="N12" t="str">
-        <v>27.89%</v>
+        <v>27.75%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>3,071</v>
+        <v>3,241</v>
       </c>
       <c r="F13" t="str">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" t="str">
-        <v>5,101</v>
+        <v>5,485</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>9,959,676,269</v>
+        <v>10,533,294,275</v>
       </c>
       <c r="M13" t="str">
-        <v>103,788,283</v>
+        <v>106,351,955</v>
       </c>
       <c r="N13" t="str">
-        <v>1.04%</v>
+        <v>1.01%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>8,629</v>
+        <v>9,110</v>
       </c>
       <c r="F14" t="str">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G14" t="str">
-        <v>19,667</v>
+        <v>20,659</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1000,19 +1000,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="str">
-        <v>15,992,700</v>
+        <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>26,886,575,443</v>
+        <v>28,324,417,508</v>
       </c>
       <c r="M14" t="str">
-        <v>243,738,734</v>
+        <v>289,673,466</v>
       </c>
       <c r="N14" t="str">
-        <v>0.91%</v>
+        <v>1.02%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>6,146</v>
+        <v>6,493</v>
       </c>
       <c r="F15" t="str">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G15" t="str">
-        <v>14,100</v>
+        <v>14,837</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>20,002,906,924</v>
+        <v>20,968,814,741</v>
       </c>
       <c r="M15" t="str">
-        <v>344,530,068</v>
+        <v>348,077,827</v>
       </c>
       <c r="N15" t="str">
-        <v>1.72%</v>
+        <v>1.66%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,10 +1073,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="F16" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>322,842,849</v>
+        <v>346,148,747</v>
       </c>
       <c r="M16" t="str">
-        <v>3,793,531</v>
+        <v>4,518,334</v>
       </c>
       <c r="N16" t="str">
-        <v>1.18%</v>
+        <v>1.31%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>11,096</v>
+        <v>11,667</v>
       </c>
       <c r="F17" t="str">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G17" t="str">
-        <v>52,970</v>
+        <v>55,345</v>
       </c>
       <c r="H17" t="str">
         <v>3</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>45,292,383,434</v>
+        <v>47,280,701,855</v>
       </c>
       <c r="M17" t="str">
-        <v>225,219,184</v>
+        <v>238,836,703</v>
       </c>
       <c r="N17" t="str">
-        <v>0.50%</v>
+        <v>0.51%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>964</v>
+        <v>1,013</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>4,573</v>
+        <v>4,782</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>3,968,108,844</v>
+        <v>4,184,117,097</v>
       </c>
       <c r="M18" t="str">
         <v>13,388,652</v>
       </c>
       <c r="N18" t="str">
-        <v>0.34%</v>
+        <v>0.32%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>4,336</v>
+        <v>4,561</v>
       </c>
       <c r="F19" t="str">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" t="str">
-        <v>19,668</v>
+        <v>20,579</v>
       </c>
       <c r="H19" t="str">
         <v>2</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>18,101,596,888</v>
+        <v>18,776,392,126</v>
       </c>
       <c r="M19" t="str">
-        <v>100,999,429</v>
+        <v>101,999,429</v>
       </c>
       <c r="N19" t="str">
-        <v>0.56%</v>
+        <v>0.54%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,183</v>
+        <v>3,196</v>
       </c>
       <c r="F20" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" t="str">
-        <v>14,475</v>
+        <v>15,283</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,903,894,584</v>
+        <v>11,914,589,926</v>
       </c>
       <c r="M20" t="str">
-        <v>110,561,818</v>
+        <v>112,583,658</v>
       </c>
       <c r="N20" t="str">
-        <v>0.93%</v>
+        <v>0.94%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,831</v>
+        <v>2,839</v>
       </c>
       <c r="F21" t="str">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G21" t="str">
-        <v>93,990</v>
+        <v>99,215</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>257,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,898,764,610</v>
+        <v>8,902,164,475</v>
       </c>
       <c r="M21" t="str">
-        <v>225,320,358</v>
+        <v>231,104,191</v>
       </c>
       <c r="N21" t="str">
-        <v>2.53%</v>
+        <v>2.60%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,19 +1337,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>10,264</v>
+        <v>10,571</v>
       </c>
       <c r="F22" t="str">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="G22" t="str">
-        <v>359,134</v>
+        <v>379,561</v>
       </c>
       <c r="H22" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I22" t="str">
-        <v>85,402,620</v>
+        <v>122,902,620</v>
       </c>
       <c r="J22" t="str">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>50,809,225,107</v>
+        <v>52,173,923,538</v>
       </c>
       <c r="M22" t="str">
-        <v>1,117,923,940</v>
+        <v>1,226,538,593</v>
       </c>
       <c r="N22" t="str">
-        <v>2.20%</v>
+        <v>2.35%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>7,896</v>
+        <v>7,919</v>
       </c>
       <c r="F24" t="str">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G24" t="str">
-        <v>48,386</v>
+        <v>51,076</v>
       </c>
       <c r="H24" t="str">
         <v>18</v>
@@ -1446,13 +1446,13 @@
         <v>127,273,040</v>
       </c>
       <c r="L24" t="str">
-        <v>52,343,251,825</v>
+        <v>52,361,294,674</v>
       </c>
       <c r="M24" t="str">
-        <v>341,191,392</v>
+        <v>371,955,057</v>
       </c>
       <c r="N24" t="str">
-        <v>0.65%</v>
+        <v>0.71%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,19 +1513,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>21,367</v>
+        <v>22,511</v>
       </c>
       <c r="F26" t="str">
-        <v>6,966</v>
+        <v>7,352</v>
       </c>
       <c r="G26" t="str">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H26" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" t="str">
-        <v>133,994,403</v>
+        <v>147,382,240</v>
       </c>
       <c r="J26" t="str">
         <v>7</v>
@@ -1534,13 +1534,13 @@
         <v>126,486,868</v>
       </c>
       <c r="L26" t="str">
-        <v>46,828,124,136</v>
+        <v>49,325,235,514</v>
       </c>
       <c r="M26" t="str">
-        <v>16,452,240,766</v>
+        <v>17,365,823,453</v>
       </c>
       <c r="N26" t="str">
-        <v>35.13%</v>
+        <v>35.21%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>3,449</v>
+        <v>3,612</v>
       </c>
       <c r="F27" t="str">
-        <v>1,822</v>
+        <v>1,945</v>
       </c>
       <c r="G27" t="str">
-        <v>3,436</v>
+        <v>3,621</v>
       </c>
       <c r="H27" t="str">
-        <v>489</v>
+        <v>522</v>
       </c>
       <c r="I27" t="str">
-        <v>6,075,821,722</v>
+        <v>6,483,176,970</v>
       </c>
       <c r="J27" t="str">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K27" t="str">
-        <v>9,253,371,892</v>
+        <v>9,745,752,635</v>
       </c>
       <c r="L27" t="str">
-        <v>42,360,993,238</v>
+        <v>44,328,527,031</v>
       </c>
       <c r="M27" t="str">
-        <v>19,718,701,196</v>
+        <v>20,950,562,890</v>
       </c>
       <c r="N27" t="str">
-        <v>46.55%</v>
+        <v>47.26%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,310</v>
+        <v>3,482</v>
       </c>
       <c r="F28" t="str">
-        <v>1,693</v>
+        <v>1,798</v>
       </c>
       <c r="G28" t="str">
-        <v>3,260</v>
+        <v>3,418</v>
       </c>
       <c r="H28" t="str">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="I28" t="str">
-        <v>6,269,121,403</v>
+        <v>6,664,296,905</v>
       </c>
       <c r="J28" t="str">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="K28" t="str">
-        <v>8,097,366,487</v>
+        <v>8,596,763,629</v>
       </c>
       <c r="L28" t="str">
-        <v>41,072,770,159</v>
+        <v>42,909,574,477</v>
       </c>
       <c r="M28" t="str">
-        <v>18,877,468,873</v>
+        <v>20,033,520,311</v>
       </c>
       <c r="N28" t="str">
-        <v>45.96%</v>
+        <v>46.69%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,134</v>
+        <v>2,233</v>
       </c>
       <c r="F29" t="str">
-        <v>1,098</v>
+        <v>1,165</v>
       </c>
       <c r="G29" t="str">
-        <v>2,189</v>
+        <v>2,295</v>
       </c>
       <c r="H29" t="str">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="I29" t="str">
-        <v>4,161,447,919</v>
+        <v>4,345,039,060</v>
       </c>
       <c r="J29" t="str">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="K29" t="str">
-        <v>5,890,939,451</v>
+        <v>6,164,584,999</v>
       </c>
       <c r="L29" t="str">
-        <v>26,497,141,667</v>
+        <v>27,669,506,518</v>
       </c>
       <c r="M29" t="str">
-        <v>12,470,465,180</v>
+        <v>13,146,948,344</v>
       </c>
       <c r="N29" t="str">
-        <v>47.06%</v>
+        <v>47.51%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>22,253</v>
+        <v>23,407</v>
       </c>
       <c r="F30" t="str">
-        <v>7,409</v>
+        <v>7,846</v>
       </c>
       <c r="G30" t="str">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H30" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" t="str">
-        <v>137,290,888</v>
+        <v>147,384,118</v>
       </c>
       <c r="J30" t="str">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K30" t="str">
-        <v>80,293,839</v>
+        <v>144,884,049</v>
       </c>
       <c r="L30" t="str">
-        <v>48,846,438,543</v>
+        <v>51,418,748,303</v>
       </c>
       <c r="M30" t="str">
-        <v>17,833,364,347</v>
+        <v>18,932,819,662</v>
       </c>
       <c r="N30" t="str">
-        <v>36.51%</v>
+        <v>36.82%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,060</v>
+        <v>2,174</v>
       </c>
       <c r="F31" t="str">
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>784,414,848</v>
+        <v>826,218,288</v>
       </c>
       <c r="M31" t="str">
-        <v>366,046,893</v>
+        <v>383,649,333</v>
       </c>
       <c r="N31" t="str">
-        <v>46.66%</v>
+        <v>46.43%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,397</v>
+        <v>1,471</v>
       </c>
       <c r="F32" t="str">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G32" t="str">
         <v>15</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,496,219,218</v>
+        <v>2,644,611,913</v>
       </c>
       <c r="M32" t="str">
-        <v>374,727,649</v>
+        <v>401,121,256</v>
       </c>
       <c r="N32" t="str">
-        <v>15.01%</v>
+        <v>15.17%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,748</v>
+        <v>1,840</v>
       </c>
       <c r="F33" t="str">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="G33" t="str">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>3,046,717,795</v>
+        <v>3,203,897,799</v>
       </c>
       <c r="M33" t="str">
-        <v>397,797,969</v>
+        <v>423,348,109</v>
       </c>
       <c r="N33" t="str">
-        <v>13.06%</v>
+        <v>13.21%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>7,100</v>
+        <v>7,513</v>
       </c>
       <c r="F34" t="str">
-        <v>1,175</v>
+        <v>1,240</v>
       </c>
       <c r="G34" t="str">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>13,409,551,995</v>
+        <v>14,141,978,570</v>
       </c>
       <c r="M34" t="str">
-        <v>1,808,602,490</v>
+        <v>1,919,697,595</v>
       </c>
       <c r="N34" t="str">
-        <v>13.49%</v>
+        <v>13.57%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,517</v>
+        <v>1,593</v>
       </c>
       <c r="F35" t="str">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="G35" t="str">
-        <v>4,755</v>
+        <v>4,985</v>
       </c>
       <c r="H35" t="str">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I35" t="str">
-        <v>1,062,507,216</v>
+        <v>1,125,530,730</v>
       </c>
       <c r="J35" t="str">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K35" t="str">
-        <v>790,330,164</v>
+        <v>856,350,661</v>
       </c>
       <c r="L35" t="str">
-        <v>16,765,444,361</v>
+        <v>17,609,796,296</v>
       </c>
       <c r="M35" t="str">
-        <v>2,606,289,463</v>
+        <v>2,778,161,901</v>
       </c>
       <c r="N35" t="str">
-        <v>15.55%</v>
+        <v>15.78%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,188</v>
+        <v>1,234</v>
       </c>
       <c r="F36" t="str">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G36" t="str">
-        <v>3,212</v>
+        <v>3,394</v>
       </c>
       <c r="H36" t="str">
         <v>49</v>
@@ -1968,19 +1968,19 @@
         <v>616,122,501</v>
       </c>
       <c r="J36" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="str">
-        <v>716,873,346</v>
+        <v>733,325,775</v>
       </c>
       <c r="L36" t="str">
-        <v>12,993,593,828</v>
+        <v>13,506,475,762</v>
       </c>
       <c r="M36" t="str">
-        <v>1,905,804,496</v>
+        <v>1,967,932,351</v>
       </c>
       <c r="N36" t="str">
-        <v>14.67%</v>
+        <v>14.57%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>6,653</v>
+        <v>6,998</v>
       </c>
       <c r="F37" t="str">
-        <v>1,041</v>
+        <v>1,103</v>
       </c>
       <c r="G37" t="str">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>12,101,768,868</v>
+        <v>12,722,444,729</v>
       </c>
       <c r="M37" t="str">
-        <v>2,057,988,837</v>
+        <v>2,167,659,158</v>
       </c>
       <c r="N37" t="str">
-        <v>17.01%</v>
+        <v>17.04%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>745</v>
+        <v>789</v>
       </c>
       <c r="F38" t="str">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>336,505,781</v>
+        <v>352,568,316</v>
       </c>
       <c r="M38" t="str">
-        <v>69,810,291</v>
+        <v>74,234,851</v>
       </c>
       <c r="N38" t="str">
-        <v>20.75%</v>
+        <v>21.06%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,296</v>
+        <v>2,417</v>
       </c>
       <c r="F39" t="str">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="G39" t="str">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>4,188,822,353</v>
+        <v>4,425,134,263</v>
       </c>
       <c r="M39" t="str">
-        <v>548,357,221</v>
+        <v>581,387,921</v>
       </c>
       <c r="N39" t="str">
-        <v>13.09%</v>
+        <v>13.14%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,945</v>
+        <v>2,051</v>
       </c>
       <c r="F41" t="str">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="G41" t="str">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H41" t="str">
         <v>0</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>3,446,062,957</v>
+        <v>3,656,437,894</v>
       </c>
       <c r="M41" t="str">
-        <v>479,837,174</v>
+        <v>522,719,558</v>
       </c>
       <c r="N41" t="str">
-        <v>13.92%</v>
+        <v>14.30%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,10 +2217,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,098</v>
+        <v>2,225</v>
       </c>
       <c r="F42" t="str">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="G42" t="str">
         <v>36</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>3,888,311,648</v>
+        <v>4,114,589,129</v>
       </c>
       <c r="M42" t="str">
-        <v>549,155,032</v>
+        <v>566,179,987</v>
       </c>
       <c r="N42" t="str">
-        <v>14.12%</v>
+        <v>13.76%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,34 +2261,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>6,426</v>
+        <v>6,796</v>
       </c>
       <c r="F43" t="str">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="G43" t="str">
-        <v>8,381</v>
+        <v>8,782</v>
       </c>
       <c r="H43" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" t="str">
-        <v>34,925,450</v>
+        <v>47,726,470</v>
       </c>
       <c r="J43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" t="str">
-        <v>19,852,307</v>
+        <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>18,042,225,673</v>
+        <v>19,085,127,557</v>
       </c>
       <c r="M43" t="str">
-        <v>556,530,268</v>
+        <v>633,245,381</v>
       </c>
       <c r="N43" t="str">
-        <v>3.08%</v>
+        <v>3.32%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>8,413</v>
+        <v>8,971</v>
       </c>
       <c r="F44" t="str">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="G44" t="str">
-        <v>11,282</v>
+        <v>11,945</v>
       </c>
       <c r="H44" t="str">
         <v>17</v>
@@ -2320,16 +2320,16 @@
         <v>196,498,541</v>
       </c>
       <c r="J44" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K44" t="str">
-        <v>183,894,947</v>
+        <v>211,633,742</v>
       </c>
       <c r="L44" t="str">
-        <v>24,746,818,553</v>
+        <v>26,266,911,683</v>
       </c>
       <c r="M44" t="str">
-        <v>1,004,045,642</v>
+        <v>1,066,427,261</v>
       </c>
       <c r="N44" t="str">
         <v>4.06%</v>
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>5,361</v>
+        <v>5,768</v>
       </c>
       <c r="F45" t="str">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="G45" t="str">
-        <v>6,602</v>
+        <v>6,978</v>
       </c>
       <c r="H45" t="str">
         <v>15</v>
@@ -2364,19 +2364,19 @@
         <v>182,692,160</v>
       </c>
       <c r="J45" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45" t="str">
-        <v>90,336,291</v>
+        <v>105,849,346</v>
       </c>
       <c r="L45" t="str">
-        <v>15,315,881,032</v>
+        <v>16,426,296,432</v>
       </c>
       <c r="M45" t="str">
-        <v>731,716,180</v>
+        <v>777,172,570</v>
       </c>
       <c r="N45" t="str">
-        <v>4.78%</v>
+        <v>4.73%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="F46" t="str">
         <v>45</v>
       </c>
       <c r="G46" t="str">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H46" t="str">
         <v>0</v>
@@ -2414,13 +2414,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L46" t="str">
-        <v>278,200,689</v>
+        <v>287,819,945</v>
       </c>
       <c r="M46" t="str">
         <v>36,019,377</v>
       </c>
       <c r="N46" t="str">
-        <v>12.95%</v>
+        <v>12.51%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,19 +457,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>3,845</v>
+        <v>4,050</v>
       </c>
       <c r="F2" t="str">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G2" t="str">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="H2" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="str">
-        <v>266,893,118</v>
+        <v>278,525,858</v>
       </c>
       <c r="J2" t="str">
         <v>6</v>
@@ -478,13 +478,13 @@
         <v>124,500,127</v>
       </c>
       <c r="L2" t="str">
-        <v>16,925,066,205</v>
+        <v>17,839,366,238</v>
       </c>
       <c r="M2" t="str">
-        <v>950,442,193</v>
+        <v>990,247,515</v>
       </c>
       <c r="N2" t="str">
-        <v>5.62%</v>
+        <v>5.55%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>2,452</v>
+        <v>2,570</v>
       </c>
       <c r="F3" t="str">
-        <v>675</v>
+        <v>712</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>4,536,658,217</v>
+        <v>4,761,517,795</v>
       </c>
       <c r="M3" t="str">
-        <v>1,179,738,284</v>
+        <v>1,234,336,605</v>
       </c>
       <c r="N3" t="str">
-        <v>26.00%</v>
+        <v>25.92%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>9,424</v>
+        <v>9,957</v>
       </c>
       <c r="F4" t="str">
-        <v>2,723</v>
+        <v>2,870</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>17,580,564,628</v>
+        <v>18,541,952,574</v>
       </c>
       <c r="M4" t="str">
-        <v>4,899,833,035</v>
+        <v>5,156,562,260</v>
       </c>
       <c r="N4" t="str">
-        <v>27.87%</v>
+        <v>27.81%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,053</v>
+        <v>1,104</v>
       </c>
       <c r="F5" t="str">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="G5" t="str">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="H5" t="str">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I5" t="str">
-        <v>1,429,598,341</v>
+        <v>1,520,935,932</v>
       </c>
       <c r="J5" t="str">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K5" t="str">
-        <v>1,489,207,567</v>
+        <v>1,541,832,157</v>
       </c>
       <c r="L5" t="str">
-        <v>12,449,627,945</v>
+        <v>13,026,607,315</v>
       </c>
       <c r="M5" t="str">
-        <v>4,203,210,006</v>
+        <v>4,402,073,592</v>
       </c>
       <c r="N5" t="str">
-        <v>33.76%</v>
+        <v>33.79%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,369</v>
+        <v>1,463</v>
       </c>
       <c r="F6" t="str">
-        <v>543</v>
+        <v>578</v>
       </c>
       <c r="G6" t="str">
-        <v>774</v>
+        <v>826</v>
       </c>
       <c r="H6" t="str">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I6" t="str">
-        <v>1,851,214,959</v>
+        <v>1,932,357,004</v>
       </c>
       <c r="J6" t="str">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K6" t="str">
-        <v>1,474,898,313</v>
+        <v>1,571,093,257</v>
       </c>
       <c r="L6" t="str">
-        <v>15,987,279,364</v>
+        <v>17,075,505,756</v>
       </c>
       <c r="M6" t="str">
-        <v>5,141,361,930</v>
+        <v>5,473,985,027</v>
       </c>
       <c r="N6" t="str">
-        <v>32.16%</v>
+        <v>32.06%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,292</v>
+        <v>1,360</v>
       </c>
       <c r="F7" t="str">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="G7" t="str">
-        <v>766</v>
+        <v>803</v>
       </c>
       <c r="H7" t="str">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I7" t="str">
-        <v>1,846,015,886</v>
+        <v>1,965,386,186</v>
       </c>
       <c r="J7" t="str">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7" t="str">
-        <v>1,380,285,787</v>
+        <v>1,397,830,277</v>
       </c>
       <c r="L7" t="str">
-        <v>15,315,555,614</v>
+        <v>16,093,154,916</v>
       </c>
       <c r="M7" t="str">
-        <v>4,876,665,364</v>
+        <v>5,107,758,465</v>
       </c>
       <c r="N7" t="str">
-        <v>31.84%</v>
+        <v>31.74%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>650</v>
+        <v>684</v>
       </c>
       <c r="F8" t="str">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="G8" t="str">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="H8" t="str">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I8" t="str">
-        <v>763,111,978</v>
+        <v>789,425,773</v>
       </c>
       <c r="J8" t="str">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K8" t="str">
-        <v>767,980,709</v>
+        <v>804,112,774</v>
       </c>
       <c r="L8" t="str">
-        <v>7,747,163,455</v>
+        <v>8,144,347,121</v>
       </c>
       <c r="M8" t="str">
-        <v>2,391,173,872</v>
+        <v>2,502,008,207</v>
       </c>
       <c r="N8" t="str">
-        <v>30.87%</v>
+        <v>30.72%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>14,658</v>
+        <v>15,483</v>
       </c>
       <c r="F9" t="str">
-        <v>4,057</v>
+        <v>4,306</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>27,336,922,958</v>
+        <v>28,846,592,561</v>
       </c>
       <c r="M9" t="str">
-        <v>7,253,694,710</v>
+        <v>7,715,945,435</v>
       </c>
       <c r="N9" t="str">
-        <v>26.53%</v>
+        <v>26.75%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,537</v>
+        <v>1,614</v>
       </c>
       <c r="F10" t="str">
-        <v>724</v>
+        <v>760</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>514,736,669</v>
+        <v>537,937,971</v>
       </c>
       <c r="M10" t="str">
-        <v>216,026,280</v>
+        <v>227,610,514</v>
       </c>
       <c r="N10" t="str">
-        <v>41.97%</v>
+        <v>42.31%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,932</v>
+        <v>3,061</v>
       </c>
       <c r="F11" t="str">
-        <v>817</v>
+        <v>837</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>5,608,330,639</v>
+        <v>5,837,608,391</v>
       </c>
       <c r="M11" t="str">
-        <v>1,435,905,074</v>
+        <v>1,462,831,460</v>
       </c>
       <c r="N11" t="str">
-        <v>25.60%</v>
+        <v>25.06%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,172</v>
+        <v>2,277</v>
       </c>
       <c r="F12" t="str">
-        <v>651</v>
+        <v>674</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>4,144,925,042</v>
+        <v>4,329,984,966</v>
       </c>
       <c r="M12" t="str">
-        <v>1,150,016,445</v>
+        <v>1,199,378,764</v>
       </c>
       <c r="N12" t="str">
-        <v>27.75%</v>
+        <v>27.70%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>3,241</v>
+        <v>3,425</v>
       </c>
       <c r="F13" t="str">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G13" t="str">
-        <v>5,485</v>
+        <v>5,852</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>10,533,294,275</v>
+        <v>11,008,409,762</v>
       </c>
       <c r="M13" t="str">
-        <v>106,351,955</v>
+        <v>117,288,584</v>
       </c>
       <c r="N13" t="str">
-        <v>1.01%</v>
+        <v>1.07%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>9,110</v>
+        <v>9,619</v>
       </c>
       <c r="F14" t="str">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G14" t="str">
-        <v>20,659</v>
+        <v>21,654</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>28,324,417,508</v>
+        <v>29,993,997,530</v>
       </c>
       <c r="M14" t="str">
-        <v>289,673,466</v>
+        <v>347,645,620</v>
       </c>
       <c r="N14" t="str">
-        <v>1.02%</v>
+        <v>1.16%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>6,493</v>
+        <v>6,857</v>
       </c>
       <c r="F15" t="str">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G15" t="str">
-        <v>14,837</v>
+        <v>15,570</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>20,968,814,741</v>
+        <v>22,088,436,405</v>
       </c>
       <c r="M15" t="str">
-        <v>348,077,827</v>
+        <v>361,679,558</v>
       </c>
       <c r="N15" t="str">
-        <v>1.66%</v>
+        <v>1.64%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,7 +1073,7 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="F16" t="str">
         <v>7</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>346,148,747</v>
+        <v>367,801,261</v>
       </c>
       <c r="M16" t="str">
         <v>4,518,334</v>
       </c>
       <c r="N16" t="str">
-        <v>1.31%</v>
+        <v>1.23%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>11,667</v>
+        <v>12,406</v>
       </c>
       <c r="F17" t="str">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G17" t="str">
-        <v>55,345</v>
+        <v>57,738</v>
       </c>
       <c r="H17" t="str">
         <v>3</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>47,280,701,855</v>
+        <v>50,198,020,224</v>
       </c>
       <c r="M17" t="str">
-        <v>238,836,703</v>
+        <v>251,518,849</v>
       </c>
       <c r="N17" t="str">
-        <v>0.51%</v>
+        <v>0.50%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,013</v>
+        <v>1,077</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>4,782</v>
+        <v>4,987</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>4,184,117,097</v>
+        <v>4,447,988,020</v>
       </c>
       <c r="M18" t="str">
         <v>13,388,652</v>
       </c>
       <c r="N18" t="str">
-        <v>0.32%</v>
+        <v>0.30%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>4,561</v>
+        <v>4,852</v>
       </c>
       <c r="F19" t="str">
         <v>49</v>
       </c>
       <c r="G19" t="str">
-        <v>20,579</v>
+        <v>21,487</v>
       </c>
       <c r="H19" t="str">
         <v>2</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>18,776,392,126</v>
+        <v>19,799,056,402</v>
       </c>
       <c r="M19" t="str">
         <v>101,999,429</v>
       </c>
       <c r="N19" t="str">
-        <v>0.54%</v>
+        <v>0.52%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,196</v>
+        <v>3,206</v>
       </c>
       <c r="F20" t="str">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G20" t="str">
-        <v>15,283</v>
+        <v>16,092</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,914,589,926</v>
+        <v>11,919,203,880</v>
       </c>
       <c r="M20" t="str">
-        <v>112,583,658</v>
+        <v>126,826,274</v>
       </c>
       <c r="N20" t="str">
-        <v>0.94%</v>
+        <v>1.06%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,839</v>
+        <v>2,857</v>
       </c>
       <c r="F21" t="str">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G21" t="str">
-        <v>99,215</v>
+        <v>104,439</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>257,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,902,164,475</v>
+        <v>8,916,437,866</v>
       </c>
       <c r="M21" t="str">
-        <v>231,104,191</v>
+        <v>249,006,940</v>
       </c>
       <c r="N21" t="str">
-        <v>2.60%</v>
+        <v>2.79%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>10,571</v>
+        <v>10,864</v>
       </c>
       <c r="F22" t="str">
-        <v>766</v>
+        <v>825</v>
       </c>
       <c r="G22" t="str">
-        <v>379,561</v>
+        <v>400,022</v>
       </c>
       <c r="H22" t="str">
         <v>10</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>52,173,923,538</v>
+        <v>53,470,996,740</v>
       </c>
       <c r="M22" t="str">
-        <v>1,226,538,593</v>
+        <v>1,320,878,984</v>
       </c>
       <c r="N22" t="str">
-        <v>2.35%</v>
+        <v>2.47%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>7,919</v>
+        <v>7,931</v>
       </c>
       <c r="F24" t="str">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G24" t="str">
-        <v>51,076</v>
+        <v>53,766</v>
       </c>
       <c r="H24" t="str">
         <v>18</v>
@@ -1446,13 +1446,13 @@
         <v>127,273,040</v>
       </c>
       <c r="L24" t="str">
-        <v>52,361,294,674</v>
+        <v>52,368,256,096</v>
       </c>
       <c r="M24" t="str">
-        <v>371,955,057</v>
+        <v>404,476,817</v>
       </c>
       <c r="N24" t="str">
-        <v>0.71%</v>
+        <v>0.77%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>22,511</v>
+        <v>23,691</v>
       </c>
       <c r="F26" t="str">
-        <v>7,352</v>
+        <v>7,710</v>
       </c>
       <c r="G26" t="str">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H26" t="str">
         <v>12</v>
@@ -1528,19 +1528,19 @@
         <v>147,382,240</v>
       </c>
       <c r="J26" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K26" t="str">
-        <v>126,486,868</v>
+        <v>145,226,288</v>
       </c>
       <c r="L26" t="str">
-        <v>49,325,235,514</v>
+        <v>52,046,689,921</v>
       </c>
       <c r="M26" t="str">
-        <v>17,365,823,453</v>
+        <v>18,201,499,096</v>
       </c>
       <c r="N26" t="str">
-        <v>35.21%</v>
+        <v>34.97%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>3,612</v>
+        <v>3,865</v>
       </c>
       <c r="F27" t="str">
-        <v>1,945</v>
+        <v>2,070</v>
       </c>
       <c r="G27" t="str">
-        <v>3,621</v>
+        <v>3,837</v>
       </c>
       <c r="H27" t="str">
-        <v>522</v>
+        <v>565</v>
       </c>
       <c r="I27" t="str">
-        <v>6,483,176,970</v>
+        <v>7,033,040,185</v>
       </c>
       <c r="J27" t="str">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="K27" t="str">
-        <v>9,745,752,635</v>
+        <v>10,143,317,277</v>
       </c>
       <c r="L27" t="str">
-        <v>44,328,527,031</v>
+        <v>47,490,282,586</v>
       </c>
       <c r="M27" t="str">
-        <v>20,950,562,890</v>
+        <v>22,222,435,484</v>
       </c>
       <c r="N27" t="str">
-        <v>47.26%</v>
+        <v>46.79%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,482</v>
+        <v>3,656</v>
       </c>
       <c r="F28" t="str">
-        <v>1,798</v>
+        <v>1,859</v>
       </c>
       <c r="G28" t="str">
-        <v>3,418</v>
+        <v>3,554</v>
       </c>
       <c r="H28" t="str">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="I28" t="str">
-        <v>6,664,296,905</v>
+        <v>6,881,595,610</v>
       </c>
       <c r="J28" t="str">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="K28" t="str">
-        <v>8,596,763,629</v>
+        <v>8,822,465,106</v>
       </c>
       <c r="L28" t="str">
-        <v>42,909,574,477</v>
+        <v>44,907,295,919</v>
       </c>
       <c r="M28" t="str">
-        <v>20,033,520,311</v>
+        <v>20,622,250,513</v>
       </c>
       <c r="N28" t="str">
-        <v>46.69%</v>
+        <v>45.92%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,233</v>
+        <v>2,362</v>
       </c>
       <c r="F29" t="str">
-        <v>1,165</v>
+        <v>1,233</v>
       </c>
       <c r="G29" t="str">
-        <v>2,295</v>
+        <v>2,418</v>
       </c>
       <c r="H29" t="str">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="I29" t="str">
-        <v>4,345,039,060</v>
+        <v>4,620,666,667</v>
       </c>
       <c r="J29" t="str">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="K29" t="str">
-        <v>6,164,584,999</v>
+        <v>6,696,045,770</v>
       </c>
       <c r="L29" t="str">
-        <v>27,669,506,518</v>
+        <v>29,290,591,906</v>
       </c>
       <c r="M29" t="str">
-        <v>13,146,948,344</v>
+        <v>14,030,816,385</v>
       </c>
       <c r="N29" t="str">
-        <v>47.51%</v>
+        <v>47.90%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>23,407</v>
+        <v>24,645</v>
       </c>
       <c r="F30" t="str">
-        <v>7,846</v>
+        <v>8,288</v>
       </c>
       <c r="G30" t="str">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H30" t="str">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I30" t="str">
-        <v>147,384,118</v>
+        <v>169,719,994</v>
       </c>
       <c r="J30" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" t="str">
-        <v>144,884,049</v>
+        <v>181,072,079</v>
       </c>
       <c r="L30" t="str">
-        <v>51,418,748,303</v>
+        <v>54,238,586,621</v>
       </c>
       <c r="M30" t="str">
-        <v>18,932,819,662</v>
+        <v>20,017,729,908</v>
       </c>
       <c r="N30" t="str">
-        <v>36.82%</v>
+        <v>36.91%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,174</v>
+        <v>2,291</v>
       </c>
       <c r="F31" t="str">
-        <v>990</v>
+        <v>1,039</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>826,218,288</v>
+        <v>875,101,674</v>
       </c>
       <c r="M31" t="str">
-        <v>383,649,333</v>
+        <v>402,756,014</v>
       </c>
       <c r="N31" t="str">
-        <v>46.43%</v>
+        <v>46.02%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,471</v>
+        <v>1,537</v>
       </c>
       <c r="F32" t="str">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G32" t="str">
         <v>15</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,644,611,913</v>
+        <v>2,778,228,338</v>
       </c>
       <c r="M32" t="str">
-        <v>401,121,256</v>
+        <v>440,865,303</v>
       </c>
       <c r="N32" t="str">
-        <v>15.17%</v>
+        <v>15.87%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,840</v>
+        <v>1,926</v>
       </c>
       <c r="F33" t="str">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="G33" t="str">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>3,203,897,799</v>
+        <v>3,356,483,687</v>
       </c>
       <c r="M33" t="str">
-        <v>423,348,109</v>
+        <v>463,382,012</v>
       </c>
       <c r="N33" t="str">
-        <v>13.21%</v>
+        <v>13.81%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>7,513</v>
+        <v>7,859</v>
       </c>
       <c r="F34" t="str">
-        <v>1,240</v>
+        <v>1,308</v>
       </c>
       <c r="G34" t="str">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>14,141,978,570</v>
+        <v>14,774,895,912</v>
       </c>
       <c r="M34" t="str">
-        <v>1,919,697,595</v>
+        <v>2,059,727,892</v>
       </c>
       <c r="N34" t="str">
-        <v>13.57%</v>
+        <v>13.94%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,593</v>
+        <v>1,674</v>
       </c>
       <c r="F35" t="str">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="G35" t="str">
-        <v>4,985</v>
+        <v>5,215</v>
       </c>
       <c r="H35" t="str">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I35" t="str">
-        <v>1,125,530,730</v>
+        <v>1,190,066,266</v>
       </c>
       <c r="J35" t="str">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K35" t="str">
-        <v>856,350,661</v>
+        <v>895,279,596</v>
       </c>
       <c r="L35" t="str">
-        <v>17,609,796,296</v>
+        <v>18,512,829,295</v>
       </c>
       <c r="M35" t="str">
-        <v>2,778,161,901</v>
+        <v>2,892,760,071</v>
       </c>
       <c r="N35" t="str">
-        <v>15.78%</v>
+        <v>15.63%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,34 +1953,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,234</v>
+        <v>1,328</v>
       </c>
       <c r="F36" t="str">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="G36" t="str">
-        <v>3,394</v>
+        <v>3,582</v>
       </c>
       <c r="H36" t="str">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I36" t="str">
-        <v>616,122,501</v>
+        <v>649,877,747</v>
       </c>
       <c r="J36" t="str">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K36" t="str">
-        <v>733,325,775</v>
+        <v>783,420,424</v>
       </c>
       <c r="L36" t="str">
-        <v>13,506,475,762</v>
+        <v>14,484,026,617</v>
       </c>
       <c r="M36" t="str">
-        <v>1,967,932,351</v>
+        <v>2,093,373,961</v>
       </c>
       <c r="N36" t="str">
-        <v>14.57%</v>
+        <v>14.45%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>6,998</v>
+        <v>7,319</v>
       </c>
       <c r="F37" t="str">
-        <v>1,103</v>
+        <v>1,150</v>
       </c>
       <c r="G37" t="str">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>12,722,444,729</v>
+        <v>13,283,189,491</v>
       </c>
       <c r="M37" t="str">
-        <v>2,167,659,158</v>
+        <v>2,277,517,979</v>
       </c>
       <c r="N37" t="str">
-        <v>17.04%</v>
+        <v>17.15%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>789</v>
+        <v>820</v>
       </c>
       <c r="F38" t="str">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>352,568,316</v>
+        <v>363,784,264</v>
       </c>
       <c r="M38" t="str">
-        <v>74,234,851</v>
+        <v>77,487,177</v>
       </c>
       <c r="N38" t="str">
-        <v>21.06%</v>
+        <v>21.30%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,417</v>
+        <v>2,514</v>
       </c>
       <c r="F39" t="str">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="G39" t="str">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>4,425,134,263</v>
+        <v>4,602,060,762</v>
       </c>
       <c r="M39" t="str">
-        <v>581,387,921</v>
+        <v>604,143,373</v>
       </c>
       <c r="N39" t="str">
-        <v>13.14%</v>
+        <v>13.13%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,051</v>
+        <v>2,144</v>
       </c>
       <c r="F41" t="str">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>3,656,437,894</v>
+        <v>3,836,086,320</v>
       </c>
       <c r="M41" t="str">
-        <v>522,719,558</v>
+        <v>549,135,604</v>
       </c>
       <c r="N41" t="str">
-        <v>14.30%</v>
+        <v>14.31%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,225</v>
+        <v>2,359</v>
       </c>
       <c r="F42" t="str">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="G42" t="str">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>4,114,589,129</v>
+        <v>4,397,002,064</v>
       </c>
       <c r="M42" t="str">
-        <v>566,179,987</v>
+        <v>608,320,800</v>
       </c>
       <c r="N42" t="str">
-        <v>13.76%</v>
+        <v>13.83%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>6,796</v>
+        <v>7,110</v>
       </c>
       <c r="F43" t="str">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="G43" t="str">
-        <v>8,782</v>
+        <v>9,184</v>
       </c>
       <c r="H43" t="str">
         <v>4</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>19,085,127,557</v>
+        <v>20,013,766,435</v>
       </c>
       <c r="M43" t="str">
-        <v>633,245,381</v>
+        <v>659,258,959</v>
       </c>
       <c r="N43" t="str">
-        <v>3.32%</v>
+        <v>3.29%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>8,971</v>
+        <v>9,446</v>
       </c>
       <c r="F44" t="str">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="G44" t="str">
-        <v>11,945</v>
+        <v>12,590</v>
       </c>
       <c r="H44" t="str">
         <v>17</v>
@@ -2326,13 +2326,13 @@
         <v>211,633,742</v>
       </c>
       <c r="L44" t="str">
-        <v>26,266,911,683</v>
+        <v>27,614,044,350</v>
       </c>
       <c r="M44" t="str">
-        <v>1,066,427,261</v>
+        <v>1,132,539,253</v>
       </c>
       <c r="N44" t="str">
-        <v>4.06%</v>
+        <v>4.10%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,19 +2349,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>5,768</v>
+        <v>6,113</v>
       </c>
       <c r="F45" t="str">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="G45" t="str">
-        <v>6,978</v>
+        <v>7,362</v>
       </c>
       <c r="H45" t="str">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I45" t="str">
-        <v>182,692,160</v>
+        <v>196,411,797</v>
       </c>
       <c r="J45" t="str">
         <v>6</v>
@@ -2370,10 +2370,10 @@
         <v>105,849,346</v>
       </c>
       <c r="L45" t="str">
-        <v>16,426,296,432</v>
+        <v>17,442,147,606</v>
       </c>
       <c r="M45" t="str">
-        <v>777,172,570</v>
+        <v>824,737,403</v>
       </c>
       <c r="N45" t="str">
         <v>4.73%</v>
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="F46" t="str">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G46" t="str">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H46" t="str">
         <v>0</v>
@@ -2414,13 +2414,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L46" t="str">
-        <v>287,819,945</v>
+        <v>296,981,831</v>
       </c>
       <c r="M46" t="str">
-        <v>36,019,377</v>
+        <v>38,468,105</v>
       </c>
       <c r="N46" t="str">
-        <v>12.51%</v>
+        <v>12.95%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,19 +457,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>4,050</v>
+        <v>4,260</v>
       </c>
       <c r="F2" t="str">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="G2" t="str">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="H2" t="str">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2" t="str">
-        <v>278,525,858</v>
+        <v>301,800,218</v>
       </c>
       <c r="J2" t="str">
         <v>6</v>
@@ -478,13 +478,13 @@
         <v>124,500,127</v>
       </c>
       <c r="L2" t="str">
-        <v>17,839,366,238</v>
+        <v>18,692,731,163</v>
       </c>
       <c r="M2" t="str">
-        <v>990,247,515</v>
+        <v>1,054,178,991</v>
       </c>
       <c r="N2" t="str">
-        <v>5.55%</v>
+        <v>5.64%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>2,570</v>
+        <v>2,682</v>
       </c>
       <c r="F3" t="str">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>4,761,517,795</v>
+        <v>4,975,416,488</v>
       </c>
       <c r="M3" t="str">
-        <v>1,234,336,605</v>
+        <v>1,279,197,364</v>
       </c>
       <c r="N3" t="str">
-        <v>25.92%</v>
+        <v>25.71%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>9,957</v>
+        <v>10,492</v>
       </c>
       <c r="F4" t="str">
-        <v>2,870</v>
+        <v>3,028</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>18,541,952,574</v>
+        <v>19,573,000,924</v>
       </c>
       <c r="M4" t="str">
-        <v>5,156,562,260</v>
+        <v>5,385,881,565</v>
       </c>
       <c r="N4" t="str">
-        <v>27.81%</v>
+        <v>27.52%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,104</v>
+        <v>1,139</v>
       </c>
       <c r="F5" t="str">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G5" t="str">
-        <v>657</v>
+        <v>675</v>
       </c>
       <c r="H5" t="str">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I5" t="str">
-        <v>1,520,935,932</v>
+        <v>1,554,059,644</v>
       </c>
       <c r="J5" t="str">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K5" t="str">
-        <v>1,541,832,157</v>
+        <v>1,634,145,956</v>
       </c>
       <c r="L5" t="str">
-        <v>13,026,607,315</v>
+        <v>13,434,942,984</v>
       </c>
       <c r="M5" t="str">
-        <v>4,402,073,592</v>
+        <v>4,568,384,199</v>
       </c>
       <c r="N5" t="str">
-        <v>33.79%</v>
+        <v>34.00%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,463</v>
+        <v>1,521</v>
       </c>
       <c r="F6" t="str">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="G6" t="str">
-        <v>826</v>
+        <v>860</v>
       </c>
       <c r="H6" t="str">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I6" t="str">
-        <v>1,932,357,004</v>
+        <v>2,045,173,911</v>
       </c>
       <c r="J6" t="str">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K6" t="str">
-        <v>1,571,093,257</v>
+        <v>1,647,546,447</v>
       </c>
       <c r="L6" t="str">
-        <v>17,075,505,756</v>
+        <v>17,746,144,449</v>
       </c>
       <c r="M6" t="str">
-        <v>5,473,985,027</v>
+        <v>5,709,357,018</v>
       </c>
       <c r="N6" t="str">
-        <v>32.06%</v>
+        <v>32.17%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,360</v>
+        <v>1,406</v>
       </c>
       <c r="F7" t="str">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="G7" t="str">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="H7" t="str">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I7" t="str">
-        <v>1,965,386,186</v>
+        <v>2,043,292,464</v>
       </c>
       <c r="J7" t="str">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K7" t="str">
-        <v>1,397,830,277</v>
+        <v>1,434,343,071</v>
       </c>
       <c r="L7" t="str">
-        <v>16,093,154,916</v>
+        <v>16,643,067,494</v>
       </c>
       <c r="M7" t="str">
-        <v>5,107,758,465</v>
+        <v>5,289,245,057</v>
       </c>
       <c r="N7" t="str">
-        <v>31.74%</v>
+        <v>31.78%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>684</v>
+        <v>707</v>
       </c>
       <c r="F8" t="str">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G8" t="str">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="H8" t="str">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I8" t="str">
-        <v>789,425,773</v>
+        <v>836,224,253</v>
       </c>
       <c r="J8" t="str">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" t="str">
-        <v>804,112,774</v>
+        <v>821,657,264</v>
       </c>
       <c r="L8" t="str">
-        <v>8,144,347,121</v>
+        <v>8,433,510,196</v>
       </c>
       <c r="M8" t="str">
-        <v>2,502,008,207</v>
+        <v>2,591,848,036</v>
       </c>
       <c r="N8" t="str">
-        <v>30.72%</v>
+        <v>30.73%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>15,483</v>
+        <v>16,270</v>
       </c>
       <c r="F9" t="str">
-        <v>4,306</v>
+        <v>4,516</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>28,846,592,561</v>
+        <v>30,337,547,827</v>
       </c>
       <c r="M9" t="str">
-        <v>7,715,945,435</v>
+        <v>8,079,351,212</v>
       </c>
       <c r="N9" t="str">
-        <v>26.75%</v>
+        <v>26.63%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,614</v>
+        <v>1,705</v>
       </c>
       <c r="F10" t="str">
-        <v>760</v>
+        <v>802</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>537,937,971</v>
+        <v>568,450,693</v>
       </c>
       <c r="M10" t="str">
-        <v>227,610,514</v>
+        <v>240,625,716</v>
       </c>
       <c r="N10" t="str">
-        <v>42.31%</v>
+        <v>42.33%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,061</v>
+        <v>3,179</v>
       </c>
       <c r="F11" t="str">
-        <v>837</v>
+        <v>869</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>5,837,608,391</v>
+        <v>6,050,595,202</v>
       </c>
       <c r="M11" t="str">
-        <v>1,462,831,460</v>
+        <v>1,510,559,398</v>
       </c>
       <c r="N11" t="str">
-        <v>25.06%</v>
+        <v>24.97%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,277</v>
+        <v>2,383</v>
       </c>
       <c r="F12" t="str">
-        <v>674</v>
+        <v>700</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>4,329,984,966</v>
+        <v>4,530,612,322</v>
       </c>
       <c r="M12" t="str">
-        <v>1,199,378,764</v>
+        <v>1,237,161,324</v>
       </c>
       <c r="N12" t="str">
-        <v>27.70%</v>
+        <v>27.31%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>3,425</v>
+        <v>3,595</v>
       </c>
       <c r="F13" t="str">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G13" t="str">
-        <v>5,852</v>
+        <v>6,217</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>11,008,409,762</v>
+        <v>11,566,830,748</v>
       </c>
       <c r="M13" t="str">
-        <v>117,288,584</v>
+        <v>117,820,927</v>
       </c>
       <c r="N13" t="str">
-        <v>1.07%</v>
+        <v>1.02%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>9,619</v>
+        <v>10,091</v>
       </c>
       <c r="F14" t="str">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G14" t="str">
-        <v>21,654</v>
+        <v>22,646</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>29,993,997,530</v>
+        <v>31,741,416,235</v>
       </c>
       <c r="M14" t="str">
-        <v>347,645,620</v>
+        <v>365,850,758</v>
       </c>
       <c r="N14" t="str">
-        <v>1.16%</v>
+        <v>1.15%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>6,857</v>
+        <v>7,197</v>
       </c>
       <c r="F15" t="str">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G15" t="str">
-        <v>15,570</v>
+        <v>16,290</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>22,088,436,405</v>
+        <v>23,072,445,502</v>
       </c>
       <c r="M15" t="str">
-        <v>361,679,558</v>
+        <v>402,680,402</v>
       </c>
       <c r="N15" t="str">
-        <v>1.64%</v>
+        <v>1.75%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="F16" t="str">
         <v>7</v>
       </c>
       <c r="G16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>367,801,261</v>
+        <v>398,769,975</v>
       </c>
       <c r="M16" t="str">
         <v>4,518,334</v>
       </c>
       <c r="N16" t="str">
-        <v>1.23%</v>
+        <v>1.13%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,19 +1117,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>12,406</v>
+        <v>13,130</v>
       </c>
       <c r="F17" t="str">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G17" t="str">
-        <v>57,738</v>
+        <v>60,114</v>
       </c>
       <c r="H17" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="str">
-        <v>34,383,394</v>
+        <v>45,136,474</v>
       </c>
       <c r="J17" t="str">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>50,198,020,224</v>
+        <v>52,997,223,774</v>
       </c>
       <c r="M17" t="str">
-        <v>251,518,849</v>
+        <v>265,838,711</v>
       </c>
       <c r="N17" t="str">
         <v>0.50%</v>
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,077</v>
+        <v>1,140</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>4,987</v>
+        <v>5,193</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>4,447,988,020</v>
+        <v>4,683,555,556</v>
       </c>
       <c r="M18" t="str">
         <v>13,388,652</v>
       </c>
       <c r="N18" t="str">
-        <v>0.30%</v>
+        <v>0.29%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>4,852</v>
+        <v>5,135</v>
       </c>
       <c r="F19" t="str">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" t="str">
-        <v>21,487</v>
+        <v>22,411</v>
       </c>
       <c r="H19" t="str">
         <v>2</v>
@@ -1226,10 +1226,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>19,799,056,402</v>
+        <v>20,875,765,067</v>
       </c>
       <c r="M19" t="str">
-        <v>101,999,429</v>
+        <v>109,334,233</v>
       </c>
       <c r="N19" t="str">
         <v>0.52%</v>
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,206</v>
+        <v>3,213</v>
       </c>
       <c r="F20" t="str">
         <v>46</v>
       </c>
       <c r="G20" t="str">
-        <v>16,092</v>
+        <v>16,902</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,7 +1270,7 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,919,203,880</v>
+        <v>11,923,396,642</v>
       </c>
       <c r="M20" t="str">
         <v>126,826,274</v>
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,857</v>
+        <v>2,879</v>
       </c>
       <c r="F21" t="str">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G21" t="str">
-        <v>104,439</v>
+        <v>109,662</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>257,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,916,437,866</v>
+        <v>8,928,775,236</v>
       </c>
       <c r="M21" t="str">
-        <v>249,006,940</v>
+        <v>255,718,745</v>
       </c>
       <c r="N21" t="str">
-        <v>2.79%</v>
+        <v>2.86%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,19 +1337,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>10,864</v>
+        <v>11,177</v>
       </c>
       <c r="F22" t="str">
-        <v>825</v>
+        <v>876</v>
       </c>
       <c r="G22" t="str">
-        <v>400,022</v>
+        <v>420,507</v>
       </c>
       <c r="H22" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I22" t="str">
-        <v>122,902,620</v>
+        <v>154,125,552</v>
       </c>
       <c r="J22" t="str">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>53,470,996,740</v>
+        <v>54,710,640,423</v>
       </c>
       <c r="M22" t="str">
-        <v>1,320,878,984</v>
+        <v>1,416,051,815</v>
       </c>
       <c r="N22" t="str">
-        <v>2.47%</v>
+        <v>2.59%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>7,931</v>
+        <v>7,946</v>
       </c>
       <c r="F24" t="str">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G24" t="str">
-        <v>53,766</v>
+        <v>56,456</v>
       </c>
       <c r="H24" t="str">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I24" t="str">
-        <v>217,826,900</v>
+        <v>240,826,900</v>
       </c>
       <c r="J24" t="str">
         <v>7</v>
@@ -1446,13 +1446,13 @@
         <v>127,273,040</v>
       </c>
       <c r="L24" t="str">
-        <v>52,368,256,096</v>
+        <v>52,380,677,497</v>
       </c>
       <c r="M24" t="str">
-        <v>404,476,817</v>
+        <v>430,088,067</v>
       </c>
       <c r="N24" t="str">
-        <v>0.77%</v>
+        <v>0.82%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,34 +1513,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>23,691</v>
+        <v>25,028</v>
       </c>
       <c r="F26" t="str">
-        <v>7,710</v>
+        <v>8,150</v>
       </c>
       <c r="G26" t="str">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H26" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" t="str">
-        <v>147,382,240</v>
+        <v>160,770,077</v>
       </c>
       <c r="J26" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K26" t="str">
-        <v>145,226,288</v>
+        <v>163,965,708</v>
       </c>
       <c r="L26" t="str">
-        <v>52,046,689,921</v>
+        <v>55,004,818,826</v>
       </c>
       <c r="M26" t="str">
-        <v>18,201,499,096</v>
+        <v>19,326,015,244</v>
       </c>
       <c r="N26" t="str">
-        <v>34.97%</v>
+        <v>35.14%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>3,865</v>
+        <v>4,038</v>
       </c>
       <c r="F27" t="str">
-        <v>2,070</v>
+        <v>2,178</v>
       </c>
       <c r="G27" t="str">
-        <v>3,837</v>
+        <v>4,051</v>
       </c>
       <c r="H27" t="str">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="I27" t="str">
-        <v>7,033,040,185</v>
+        <v>7,358,686,109</v>
       </c>
       <c r="J27" t="str">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="K27" t="str">
-        <v>10,143,317,277</v>
+        <v>10,677,052,701</v>
       </c>
       <c r="L27" t="str">
-        <v>47,490,282,586</v>
+        <v>49,787,137,110</v>
       </c>
       <c r="M27" t="str">
-        <v>22,222,435,484</v>
+        <v>23,407,126,973</v>
       </c>
       <c r="N27" t="str">
-        <v>46.79%</v>
+        <v>47.01%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,656</v>
+        <v>3,829</v>
       </c>
       <c r="F28" t="str">
-        <v>1,859</v>
+        <v>1,935</v>
       </c>
       <c r="G28" t="str">
-        <v>3,554</v>
+        <v>3,743</v>
       </c>
       <c r="H28" t="str">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="I28" t="str">
-        <v>6,881,595,610</v>
+        <v>7,288,106,831</v>
       </c>
       <c r="J28" t="str">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="K28" t="str">
-        <v>8,822,465,106</v>
+        <v>9,037,751,216</v>
       </c>
       <c r="L28" t="str">
-        <v>44,907,295,919</v>
+        <v>47,092,851,782</v>
       </c>
       <c r="M28" t="str">
-        <v>20,622,250,513</v>
+        <v>21,411,602,063</v>
       </c>
       <c r="N28" t="str">
-        <v>45.92%</v>
+        <v>45.47%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,362</v>
+        <v>2,494</v>
       </c>
       <c r="F29" t="str">
-        <v>1,233</v>
+        <v>1,283</v>
       </c>
       <c r="G29" t="str">
-        <v>2,418</v>
+        <v>2,545</v>
       </c>
       <c r="H29" t="str">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="I29" t="str">
-        <v>4,620,666,667</v>
+        <v>4,801,877,982</v>
       </c>
       <c r="J29" t="str">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="K29" t="str">
-        <v>6,696,045,770</v>
+        <v>6,931,221,874</v>
       </c>
       <c r="L29" t="str">
-        <v>29,290,591,906</v>
+        <v>30,881,475,029</v>
       </c>
       <c r="M29" t="str">
-        <v>14,030,816,385</v>
+        <v>14,552,113,013</v>
       </c>
       <c r="N29" t="str">
-        <v>47.90%</v>
+        <v>47.12%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,19 +1689,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>24,645</v>
+        <v>25,941</v>
       </c>
       <c r="F30" t="str">
-        <v>8,288</v>
+        <v>8,735</v>
       </c>
       <c r="G30" t="str">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H30" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" t="str">
-        <v>169,719,994</v>
+        <v>184,261,169</v>
       </c>
       <c r="J30" t="str">
         <v>9</v>
@@ -1710,13 +1710,13 @@
         <v>181,072,079</v>
       </c>
       <c r="L30" t="str">
-        <v>54,238,586,621</v>
+        <v>56,948,295,774</v>
       </c>
       <c r="M30" t="str">
-        <v>20,017,729,908</v>
+        <v>21,125,879,955</v>
       </c>
       <c r="N30" t="str">
-        <v>36.91%</v>
+        <v>37.10%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,291</v>
+        <v>2,410</v>
       </c>
       <c r="F31" t="str">
-        <v>1,039</v>
+        <v>1,081</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>875,101,674</v>
+        <v>917,668,467</v>
       </c>
       <c r="M31" t="str">
-        <v>402,756,014</v>
+        <v>419,466,980</v>
       </c>
       <c r="N31" t="str">
-        <v>46.02%</v>
+        <v>45.71%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,537</v>
+        <v>1,615</v>
       </c>
       <c r="F32" t="str">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="G32" t="str">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,778,228,338</v>
+        <v>2,929,646,732</v>
       </c>
       <c r="M32" t="str">
-        <v>440,865,303</v>
+        <v>459,731,248</v>
       </c>
       <c r="N32" t="str">
-        <v>15.87%</v>
+        <v>15.69%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,926</v>
+        <v>2,025</v>
       </c>
       <c r="F33" t="str">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="G33" t="str">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>3,356,483,687</v>
+        <v>3,513,393,598</v>
       </c>
       <c r="M33" t="str">
-        <v>463,382,012</v>
+        <v>483,412,031</v>
       </c>
       <c r="N33" t="str">
-        <v>13.81%</v>
+        <v>13.76%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>7,859</v>
+        <v>8,290</v>
       </c>
       <c r="F34" t="str">
-        <v>1,308</v>
+        <v>1,366</v>
       </c>
       <c r="G34" t="str">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>14,774,895,912</v>
+        <v>15,533,857,977</v>
       </c>
       <c r="M34" t="str">
-        <v>2,059,727,892</v>
+        <v>2,147,653,000</v>
       </c>
       <c r="N34" t="str">
-        <v>13.94%</v>
+        <v>13.83%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,674</v>
+        <v>1,770</v>
       </c>
       <c r="F35" t="str">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="G35" t="str">
-        <v>5,215</v>
+        <v>5,457</v>
       </c>
       <c r="H35" t="str">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I35" t="str">
-        <v>1,190,066,266</v>
+        <v>1,242,816,143</v>
       </c>
       <c r="J35" t="str">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K35" t="str">
-        <v>895,279,596</v>
+        <v>951,951,456</v>
       </c>
       <c r="L35" t="str">
-        <v>18,512,829,295</v>
+        <v>19,434,659,476</v>
       </c>
       <c r="M35" t="str">
-        <v>2,892,760,071</v>
+        <v>3,030,949,711</v>
       </c>
       <c r="N35" t="str">
-        <v>15.63%</v>
+        <v>15.60%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,19 +1953,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,328</v>
+        <v>1,394</v>
       </c>
       <c r="F36" t="str">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="G36" t="str">
-        <v>3,582</v>
+        <v>3,777</v>
       </c>
       <c r="H36" t="str">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I36" t="str">
-        <v>649,877,747</v>
+        <v>761,138,948</v>
       </c>
       <c r="J36" t="str">
         <v>39</v>
@@ -1974,13 +1974,13 @@
         <v>783,420,424</v>
       </c>
       <c r="L36" t="str">
-        <v>14,484,026,617</v>
+        <v>15,212,855,617</v>
       </c>
       <c r="M36" t="str">
-        <v>2,093,373,961</v>
+        <v>2,261,753,687</v>
       </c>
       <c r="N36" t="str">
-        <v>14.45%</v>
+        <v>14.87%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>7,319</v>
+        <v>7,694</v>
       </c>
       <c r="F37" t="str">
-        <v>1,150</v>
+        <v>1,216</v>
       </c>
       <c r="G37" t="str">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>13,283,189,491</v>
+        <v>14,020,131,703</v>
       </c>
       <c r="M37" t="str">
-        <v>2,277,517,979</v>
+        <v>2,423,176,543</v>
       </c>
       <c r="N37" t="str">
-        <v>17.15%</v>
+        <v>17.28%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>820</v>
+        <v>857</v>
       </c>
       <c r="F38" t="str">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>363,784,264</v>
+        <v>374,022,382</v>
       </c>
       <c r="M38" t="str">
-        <v>77,487,177</v>
+        <v>79,971,834</v>
       </c>
       <c r="N38" t="str">
-        <v>21.30%</v>
+        <v>21.38%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,514</v>
+        <v>2,642</v>
       </c>
       <c r="F39" t="str">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="G39" t="str">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>4,602,060,762</v>
+        <v>4,815,802,015</v>
       </c>
       <c r="M39" t="str">
-        <v>604,143,373</v>
+        <v>636,963,433</v>
       </c>
       <c r="N39" t="str">
-        <v>13.13%</v>
+        <v>13.23%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,144</v>
+        <v>2,205</v>
       </c>
       <c r="F41" t="str">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>3,836,086,320</v>
+        <v>3,966,912,276</v>
       </c>
       <c r="M41" t="str">
-        <v>549,135,604</v>
+        <v>581,742,592</v>
       </c>
       <c r="N41" t="str">
-        <v>14.31%</v>
+        <v>14.66%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,359</v>
+        <v>2,451</v>
       </c>
       <c r="F42" t="str">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="G42" t="str">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>4,397,002,064</v>
+        <v>4,554,276,569</v>
       </c>
       <c r="M42" t="str">
-        <v>608,320,800</v>
+        <v>629,266,185</v>
       </c>
       <c r="N42" t="str">
-        <v>13.83%</v>
+        <v>13.82%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>7,110</v>
+        <v>7,420</v>
       </c>
       <c r="F43" t="str">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G43" t="str">
-        <v>9,184</v>
+        <v>9,578</v>
       </c>
       <c r="H43" t="str">
         <v>4</v>
@@ -2282,10 +2282,10 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>20,013,766,435</v>
+        <v>20,872,779,257</v>
       </c>
       <c r="M43" t="str">
-        <v>659,258,959</v>
+        <v>687,165,559</v>
       </c>
       <c r="N43" t="str">
         <v>3.29%</v>
@@ -2305,34 +2305,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>9,446</v>
+        <v>9,912</v>
       </c>
       <c r="F44" t="str">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="G44" t="str">
-        <v>12,590</v>
+        <v>13,216</v>
       </c>
       <c r="H44" t="str">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I44" t="str">
-        <v>196,498,541</v>
+        <v>207,633,707</v>
       </c>
       <c r="J44" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K44" t="str">
-        <v>211,633,742</v>
+        <v>226,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>27,614,044,350</v>
+        <v>28,790,953,531</v>
       </c>
       <c r="M44" t="str">
-        <v>1,132,539,253</v>
+        <v>1,225,129,592</v>
       </c>
       <c r="N44" t="str">
-        <v>4.10%</v>
+        <v>4.26%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>6,113</v>
+        <v>6,454</v>
       </c>
       <c r="F45" t="str">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="G45" t="str">
-        <v>7,362</v>
+        <v>7,748</v>
       </c>
       <c r="H45" t="str">
         <v>16</v>
@@ -2370,13 +2370,13 @@
         <v>105,849,346</v>
       </c>
       <c r="L45" t="str">
-        <v>17,442,147,606</v>
+        <v>18,392,183,805</v>
       </c>
       <c r="M45" t="str">
-        <v>824,737,403</v>
+        <v>854,614,406</v>
       </c>
       <c r="N45" t="str">
-        <v>4.73%</v>
+        <v>4.65%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="F46" t="str">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G46" t="str">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H46" t="str">
         <v>0</v>
@@ -2414,13 +2414,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L46" t="str">
-        <v>296,981,831</v>
+        <v>306,907,017</v>
       </c>
       <c r="M46" t="str">
-        <v>38,468,105</v>
+        <v>38,696,446</v>
       </c>
       <c r="N46" t="str">
-        <v>12.95%</v>
+        <v>12.61%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,13 +457,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>4,260</v>
+        <v>4,460</v>
       </c>
       <c r="F2" t="str">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G2" t="str">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="H2" t="str">
         <v>25</v>
@@ -478,13 +478,13 @@
         <v>124,500,127</v>
       </c>
       <c r="L2" t="str">
-        <v>18,692,731,163</v>
+        <v>19,539,410,852</v>
       </c>
       <c r="M2" t="str">
-        <v>1,054,178,991</v>
+        <v>1,085,063,677</v>
       </c>
       <c r="N2" t="str">
-        <v>5.64%</v>
+        <v>5.55%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>2,682</v>
+        <v>2,798</v>
       </c>
       <c r="F3" t="str">
-        <v>735</v>
+        <v>765</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>4,975,416,488</v>
+        <v>5,227,576,123</v>
       </c>
       <c r="M3" t="str">
-        <v>1,279,197,364</v>
+        <v>1,351,000,415</v>
       </c>
       <c r="N3" t="str">
-        <v>25.71%</v>
+        <v>25.84%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>10,492</v>
+        <v>11,010</v>
       </c>
       <c r="F4" t="str">
-        <v>3,028</v>
+        <v>3,179</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>19,573,000,924</v>
+        <v>20,578,809,166</v>
       </c>
       <c r="M4" t="str">
-        <v>5,385,881,565</v>
+        <v>5,674,441,539</v>
       </c>
       <c r="N4" t="str">
-        <v>27.52%</v>
+        <v>27.57%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,139</v>
+        <v>1,195</v>
       </c>
       <c r="F5" t="str">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="G5" t="str">
-        <v>675</v>
+        <v>710</v>
       </c>
       <c r="H5" t="str">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I5" t="str">
-        <v>1,554,059,644</v>
+        <v>1,633,450,145</v>
       </c>
       <c r="J5" t="str">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K5" t="str">
-        <v>1,634,145,956</v>
+        <v>1,715,226,558</v>
       </c>
       <c r="L5" t="str">
-        <v>13,434,942,984</v>
+        <v>14,113,611,312</v>
       </c>
       <c r="M5" t="str">
-        <v>4,568,384,199</v>
+        <v>4,781,138,725</v>
       </c>
       <c r="N5" t="str">
-        <v>34.00%</v>
+        <v>33.88%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,521</v>
+        <v>1,633</v>
       </c>
       <c r="F6" t="str">
-        <v>599</v>
+        <v>643</v>
       </c>
       <c r="G6" t="str">
-        <v>860</v>
+        <v>928</v>
       </c>
       <c r="H6" t="str">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="I6" t="str">
-        <v>2,045,173,911</v>
+        <v>2,218,371,701</v>
       </c>
       <c r="J6" t="str">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K6" t="str">
-        <v>1,647,546,447</v>
+        <v>1,840,591,811</v>
       </c>
       <c r="L6" t="str">
-        <v>17,746,144,449</v>
+        <v>19,151,965,402</v>
       </c>
       <c r="M6" t="str">
-        <v>5,709,357,018</v>
+        <v>6,203,868,325</v>
       </c>
       <c r="N6" t="str">
-        <v>32.17%</v>
+        <v>32.39%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,406</v>
+        <v>1,485</v>
       </c>
       <c r="F7" t="str">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="G7" t="str">
-        <v>830</v>
+        <v>872</v>
       </c>
       <c r="H7" t="str">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I7" t="str">
-        <v>2,043,292,464</v>
+        <v>2,161,318,730</v>
       </c>
       <c r="J7" t="str">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K7" t="str">
-        <v>1,434,343,071</v>
+        <v>1,526,970,649</v>
       </c>
       <c r="L7" t="str">
-        <v>16,643,067,494</v>
+        <v>17,534,518,971</v>
       </c>
       <c r="M7" t="str">
-        <v>5,289,245,057</v>
+        <v>5,553,975,812</v>
       </c>
       <c r="N7" t="str">
-        <v>31.78%</v>
+        <v>31.67%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="F8" t="str">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="G8" t="str">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="H8" t="str">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I8" t="str">
-        <v>836,224,253</v>
+        <v>875,925,885</v>
       </c>
       <c r="J8" t="str">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K8" t="str">
-        <v>821,657,264</v>
+        <v>877,195,409</v>
       </c>
       <c r="L8" t="str">
-        <v>8,433,510,196</v>
+        <v>8,888,265,591</v>
       </c>
       <c r="M8" t="str">
-        <v>2,591,848,036</v>
+        <v>2,723,703,002</v>
       </c>
       <c r="N8" t="str">
-        <v>30.73%</v>
+        <v>30.64%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>16,270</v>
+        <v>17,026</v>
       </c>
       <c r="F9" t="str">
-        <v>4,516</v>
+        <v>4,711</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>30,337,547,827</v>
+        <v>31,759,721,863</v>
       </c>
       <c r="M9" t="str">
-        <v>8,079,351,212</v>
+        <v>8,415,184,178</v>
       </c>
       <c r="N9" t="str">
-        <v>26.63%</v>
+        <v>26.50%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,705</v>
+        <v>1,789</v>
       </c>
       <c r="F10" t="str">
-        <v>802</v>
+        <v>839</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>568,450,693</v>
+        <v>600,552,077</v>
       </c>
       <c r="M10" t="str">
-        <v>240,625,716</v>
+        <v>253,216,943</v>
       </c>
       <c r="N10" t="str">
-        <v>42.33%</v>
+        <v>42.16%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,179</v>
+        <v>3,293</v>
       </c>
       <c r="F11" t="str">
-        <v>869</v>
+        <v>906</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>6,050,595,202</v>
+        <v>6,270,057,463</v>
       </c>
       <c r="M11" t="str">
-        <v>1,510,559,398</v>
+        <v>1,572,510,282</v>
       </c>
       <c r="N11" t="str">
-        <v>24.97%</v>
+        <v>25.08%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,383</v>
+        <v>2,513</v>
       </c>
       <c r="F12" t="str">
-        <v>700</v>
+        <v>736</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>4,530,612,322</v>
+        <v>4,775,879,373</v>
       </c>
       <c r="M12" t="str">
-        <v>1,237,161,324</v>
+        <v>1,308,891,175</v>
       </c>
       <c r="N12" t="str">
-        <v>27.31%</v>
+        <v>27.41%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>3,595</v>
+        <v>3,766</v>
       </c>
       <c r="F13" t="str">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G13" t="str">
-        <v>6,217</v>
+        <v>6,590</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>11,566,830,748</v>
+        <v>12,227,302,237</v>
       </c>
       <c r="M13" t="str">
-        <v>117,820,927</v>
+        <v>121,462,165</v>
       </c>
       <c r="N13" t="str">
-        <v>1.02%</v>
+        <v>0.99%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>10,091</v>
+        <v>10,568</v>
       </c>
       <c r="F14" t="str">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G14" t="str">
-        <v>22,646</v>
+        <v>23,644</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>31,741,416,235</v>
+        <v>33,414,910,223</v>
       </c>
       <c r="M14" t="str">
-        <v>365,850,758</v>
+        <v>387,395,899</v>
       </c>
       <c r="N14" t="str">
-        <v>1.15%</v>
+        <v>1.16%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>7,197</v>
+        <v>7,538</v>
       </c>
       <c r="F15" t="str">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G15" t="str">
-        <v>16,290</v>
+        <v>16,993</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>23,072,445,502</v>
+        <v>24,092,051,587</v>
       </c>
       <c r="M15" t="str">
-        <v>402,680,402</v>
+        <v>414,314,329</v>
       </c>
       <c r="N15" t="str">
-        <v>1.75%</v>
+        <v>1.72%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="F16" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>398,769,975</v>
+        <v>410,779,246</v>
       </c>
       <c r="M16" t="str">
-        <v>4,518,334</v>
+        <v>4,784,115</v>
       </c>
       <c r="N16" t="str">
-        <v>1.13%</v>
+        <v>1.16%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>13,130</v>
+        <v>13,747</v>
       </c>
       <c r="F17" t="str">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G17" t="str">
-        <v>60,114</v>
+        <v>62,487</v>
       </c>
       <c r="H17" t="str">
         <v>4</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>52,997,223,774</v>
+        <v>55,194,781,709</v>
       </c>
       <c r="M17" t="str">
-        <v>265,838,711</v>
+        <v>271,002,041</v>
       </c>
       <c r="N17" t="str">
-        <v>0.50%</v>
+        <v>0.49%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,140</v>
+        <v>1,194</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>5,193</v>
+        <v>5,395</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>4,683,555,556</v>
+        <v>4,849,794,649</v>
       </c>
       <c r="M18" t="str">
         <v>13,388,652</v>
       </c>
       <c r="N18" t="str">
-        <v>0.29%</v>
+        <v>0.28%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,19 +1205,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>5,135</v>
+        <v>5,374</v>
       </c>
       <c r="F19" t="str">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G19" t="str">
-        <v>22,411</v>
+        <v>23,343</v>
       </c>
       <c r="H19" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I19" t="str">
-        <v>24,400,000</v>
+        <v>56,628,300</v>
       </c>
       <c r="J19" t="str">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>20,875,765,067</v>
+        <v>21,968,919,431</v>
       </c>
       <c r="M19" t="str">
-        <v>109,334,233</v>
+        <v>137,003,046</v>
       </c>
       <c r="N19" t="str">
-        <v>0.52%</v>
+        <v>0.62%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,213</v>
+        <v>3,218</v>
       </c>
       <c r="F20" t="str">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G20" t="str">
-        <v>16,902</v>
+        <v>17,712</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,923,396,642</v>
+        <v>11,925,905,971</v>
       </c>
       <c r="M20" t="str">
-        <v>126,826,274</v>
+        <v>143,421,274</v>
       </c>
       <c r="N20" t="str">
-        <v>1.06%</v>
+        <v>1.20%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,879</v>
+        <v>2,893</v>
       </c>
       <c r="F21" t="str">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G21" t="str">
-        <v>109,662</v>
+        <v>114,884</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>257,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,928,775,236</v>
+        <v>8,936,751,555</v>
       </c>
       <c r="M21" t="str">
-        <v>255,718,745</v>
+        <v>264,922,975</v>
       </c>
       <c r="N21" t="str">
-        <v>2.86%</v>
+        <v>2.96%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,19 +1337,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>11,177</v>
+        <v>11,515</v>
       </c>
       <c r="F22" t="str">
-        <v>876</v>
+        <v>929</v>
       </c>
       <c r="G22" t="str">
-        <v>420,507</v>
+        <v>441,020</v>
       </c>
       <c r="H22" t="str">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I22" t="str">
-        <v>154,125,552</v>
+        <v>252,531,680</v>
       </c>
       <c r="J22" t="str">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>54,710,640,423</v>
+        <v>56,160,331,766</v>
       </c>
       <c r="M22" t="str">
-        <v>1,416,051,815</v>
+        <v>1,574,576,144</v>
       </c>
       <c r="N22" t="str">
-        <v>2.59%</v>
+        <v>2.80%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>7,946</v>
+        <v>7,969</v>
       </c>
       <c r="F24" t="str">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G24" t="str">
-        <v>56,456</v>
+        <v>59,145</v>
       </c>
       <c r="H24" t="str">
         <v>20</v>
@@ -1446,13 +1446,13 @@
         <v>127,273,040</v>
       </c>
       <c r="L24" t="str">
-        <v>52,380,677,497</v>
+        <v>52,392,235,919</v>
       </c>
       <c r="M24" t="str">
-        <v>430,088,067</v>
+        <v>442,495,468</v>
       </c>
       <c r="N24" t="str">
-        <v>0.82%</v>
+        <v>0.84%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>25,028</v>
+        <v>26,287</v>
       </c>
       <c r="F26" t="str">
-        <v>8,150</v>
+        <v>8,533</v>
       </c>
       <c r="G26" t="str">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H26" t="str">
         <v>13</v>
@@ -1534,13 +1534,13 @@
         <v>163,965,708</v>
       </c>
       <c r="L26" t="str">
-        <v>55,004,818,826</v>
+        <v>57,733,116,787</v>
       </c>
       <c r="M26" t="str">
-        <v>19,326,015,244</v>
+        <v>20,291,088,888</v>
       </c>
       <c r="N26" t="str">
-        <v>35.14%</v>
+        <v>35.15%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>4,038</v>
+        <v>4,232</v>
       </c>
       <c r="F27" t="str">
-        <v>2,178</v>
+        <v>2,305</v>
       </c>
       <c r="G27" t="str">
-        <v>4,051</v>
+        <v>4,240</v>
       </c>
       <c r="H27" t="str">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="I27" t="str">
-        <v>7,358,686,109</v>
+        <v>7,784,468,165</v>
       </c>
       <c r="J27" t="str">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="K27" t="str">
-        <v>10,677,052,701</v>
+        <v>11,222,263,753</v>
       </c>
       <c r="L27" t="str">
-        <v>49,787,137,110</v>
+        <v>52,187,047,485</v>
       </c>
       <c r="M27" t="str">
-        <v>23,407,126,973</v>
+        <v>24,721,638,299</v>
       </c>
       <c r="N27" t="str">
-        <v>47.01%</v>
+        <v>47.37%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,829</v>
+        <v>4,005</v>
       </c>
       <c r="F28" t="str">
-        <v>1,935</v>
+        <v>2,027</v>
       </c>
       <c r="G28" t="str">
-        <v>3,743</v>
+        <v>3,921</v>
       </c>
       <c r="H28" t="str">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="I28" t="str">
-        <v>7,288,106,831</v>
+        <v>7,670,728,998</v>
       </c>
       <c r="J28" t="str">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="K28" t="str">
-        <v>9,037,751,216</v>
+        <v>9,670,396,625</v>
       </c>
       <c r="L28" t="str">
-        <v>47,092,851,782</v>
+        <v>49,299,515,181</v>
       </c>
       <c r="M28" t="str">
-        <v>21,411,602,063</v>
+        <v>22,580,025,082</v>
       </c>
       <c r="N28" t="str">
-        <v>45.47%</v>
+        <v>45.80%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,494</v>
+        <v>2,612</v>
       </c>
       <c r="F29" t="str">
-        <v>1,283</v>
+        <v>1,353</v>
       </c>
       <c r="G29" t="str">
-        <v>2,545</v>
+        <v>2,681</v>
       </c>
       <c r="H29" t="str">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="I29" t="str">
-        <v>4,801,877,982</v>
+        <v>5,148,838,838</v>
       </c>
       <c r="J29" t="str">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K29" t="str">
-        <v>6,931,221,874</v>
+        <v>7,320,701,578</v>
       </c>
       <c r="L29" t="str">
-        <v>30,881,475,029</v>
+        <v>32,293,333,925</v>
       </c>
       <c r="M29" t="str">
-        <v>14,552,113,013</v>
+        <v>15,396,483,801</v>
       </c>
       <c r="N29" t="str">
-        <v>47.12%</v>
+        <v>47.68%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>25,941</v>
+        <v>27,274</v>
       </c>
       <c r="F30" t="str">
-        <v>8,735</v>
+        <v>9,131</v>
       </c>
       <c r="G30" t="str">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H30" t="str">
         <v>15</v>
@@ -1704,19 +1704,19 @@
         <v>184,261,169</v>
       </c>
       <c r="J30" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" t="str">
-        <v>181,072,079</v>
+        <v>207,254,874</v>
       </c>
       <c r="L30" t="str">
-        <v>56,948,295,774</v>
+        <v>59,739,516,422</v>
       </c>
       <c r="M30" t="str">
-        <v>21,125,879,955</v>
+        <v>22,037,712,439</v>
       </c>
       <c r="N30" t="str">
-        <v>37.10%</v>
+        <v>36.89%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,410</v>
+        <v>2,546</v>
       </c>
       <c r="F31" t="str">
-        <v>1,081</v>
+        <v>1,135</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>917,668,467</v>
+        <v>971,065,624</v>
       </c>
       <c r="M31" t="str">
-        <v>419,466,980</v>
+        <v>438,381,205</v>
       </c>
       <c r="N31" t="str">
-        <v>45.71%</v>
+        <v>45.14%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,615</v>
+        <v>1,692</v>
       </c>
       <c r="F32" t="str">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G32" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,929,646,732</v>
+        <v>3,059,521,986</v>
       </c>
       <c r="M32" t="str">
-        <v>459,731,248</v>
+        <v>492,378,286</v>
       </c>
       <c r="N32" t="str">
-        <v>15.69%</v>
+        <v>16.09%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,10 +1821,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,025</v>
+        <v>2,121</v>
       </c>
       <c r="F33" t="str">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="G33" t="str">
         <v>41</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>3,513,393,598</v>
+        <v>3,695,882,322</v>
       </c>
       <c r="M33" t="str">
-        <v>483,412,031</v>
+        <v>494,762,521</v>
       </c>
       <c r="N33" t="str">
-        <v>13.76%</v>
+        <v>13.39%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>8,290</v>
+        <v>8,728</v>
       </c>
       <c r="F34" t="str">
-        <v>1,366</v>
+        <v>1,425</v>
       </c>
       <c r="G34" t="str">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>15,533,857,977</v>
+        <v>16,418,973,457</v>
       </c>
       <c r="M34" t="str">
-        <v>2,147,653,000</v>
+        <v>2,246,831,711</v>
       </c>
       <c r="N34" t="str">
-        <v>13.83%</v>
+        <v>13.68%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,770</v>
+        <v>1,820</v>
       </c>
       <c r="F35" t="str">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="G35" t="str">
-        <v>5,457</v>
+        <v>5,692</v>
       </c>
       <c r="H35" t="str">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I35" t="str">
-        <v>1,242,816,143</v>
+        <v>1,252,816,143</v>
       </c>
       <c r="J35" t="str">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K35" t="str">
-        <v>951,951,456</v>
+        <v>1,046,008,797</v>
       </c>
       <c r="L35" t="str">
-        <v>19,434,659,476</v>
+        <v>20,002,167,124</v>
       </c>
       <c r="M35" t="str">
-        <v>3,030,949,711</v>
+        <v>3,192,129,926</v>
       </c>
       <c r="N35" t="str">
-        <v>15.60%</v>
+        <v>15.96%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,34 +1953,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,394</v>
+        <v>1,447</v>
       </c>
       <c r="F36" t="str">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G36" t="str">
-        <v>3,777</v>
+        <v>3,959</v>
       </c>
       <c r="H36" t="str">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I36" t="str">
-        <v>761,138,948</v>
+        <v>804,307,362</v>
       </c>
       <c r="J36" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K36" t="str">
-        <v>783,420,424</v>
+        <v>802,311,044</v>
       </c>
       <c r="L36" t="str">
-        <v>15,212,855,617</v>
+        <v>15,728,488,277</v>
       </c>
       <c r="M36" t="str">
-        <v>2,261,753,687</v>
+        <v>2,345,755,080</v>
       </c>
       <c r="N36" t="str">
-        <v>14.87%</v>
+        <v>14.91%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>7,694</v>
+        <v>8,075</v>
       </c>
       <c r="F37" t="str">
-        <v>1,216</v>
+        <v>1,265</v>
       </c>
       <c r="G37" t="str">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>14,020,131,703</v>
+        <v>14,711,031,312</v>
       </c>
       <c r="M37" t="str">
-        <v>2,423,176,543</v>
+        <v>2,516,079,456</v>
       </c>
       <c r="N37" t="str">
-        <v>17.28%</v>
+        <v>17.10%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>857</v>
+        <v>903</v>
       </c>
       <c r="F38" t="str">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>374,022,382</v>
+        <v>389,762,341</v>
       </c>
       <c r="M38" t="str">
-        <v>79,971,834</v>
+        <v>83,760,618</v>
       </c>
       <c r="N38" t="str">
-        <v>21.38%</v>
+        <v>21.49%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,642</v>
+        <v>2,756</v>
       </c>
       <c r="F39" t="str">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="G39" t="str">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>4,815,802,015</v>
+        <v>5,025,626,351</v>
       </c>
       <c r="M39" t="str">
-        <v>636,963,433</v>
+        <v>666,471,738</v>
       </c>
       <c r="N39" t="str">
-        <v>13.23%</v>
+        <v>13.26%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,205</v>
+        <v>2,320</v>
       </c>
       <c r="F41" t="str">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>3,966,912,276</v>
+        <v>4,182,954,459</v>
       </c>
       <c r="M41" t="str">
-        <v>581,742,592</v>
+        <v>598,532,251</v>
       </c>
       <c r="N41" t="str">
-        <v>14.66%</v>
+        <v>14.31%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,451</v>
+        <v>2,566</v>
       </c>
       <c r="F42" t="str">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="G42" t="str">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>4,554,276,569</v>
+        <v>4,760,071,407</v>
       </c>
       <c r="M42" t="str">
-        <v>629,266,185</v>
+        <v>658,293,732</v>
       </c>
       <c r="N42" t="str">
-        <v>13.82%</v>
+        <v>13.83%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,19 +2261,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>7,420</v>
+        <v>7,691</v>
       </c>
       <c r="F43" t="str">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="G43" t="str">
-        <v>9,578</v>
+        <v>9,967</v>
       </c>
       <c r="H43" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" t="str">
-        <v>47,726,470</v>
+        <v>59,836,290</v>
       </c>
       <c r="J43" t="str">
         <v>2</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>20,872,779,257</v>
+        <v>21,619,014,076</v>
       </c>
       <c r="M43" t="str">
-        <v>687,165,559</v>
+        <v>723,293,623</v>
       </c>
       <c r="N43" t="str">
-        <v>3.29%</v>
+        <v>3.35%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>9,912</v>
+        <v>10,315</v>
       </c>
       <c r="F44" t="str">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="G44" t="str">
-        <v>13,216</v>
+        <v>13,828</v>
       </c>
       <c r="H44" t="str">
         <v>18</v>
@@ -2320,24 +2320,24 @@
         <v>207,633,707</v>
       </c>
       <c r="J44" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K44" t="str">
-        <v>226,768,797</v>
+        <v>243,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>28,790,953,531</v>
+        <v>29,823,193,931</v>
       </c>
       <c r="M44" t="str">
-        <v>1,225,129,592</v>
+        <v>1,274,915,796</v>
       </c>
       <c r="N44" t="str">
-        <v>4.26%</v>
+        <v>4.27%</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Internal Collection</v>
+        <v>DC07</v>
       </c>
       <c r="B45" t="str">
         <v>S2</v>
@@ -2349,39 +2349,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>6,454</v>
+        <v>161</v>
       </c>
       <c r="F45" t="str">
-        <v>322</v>
+        <v>5</v>
       </c>
       <c r="G45" t="str">
-        <v>7,748</v>
+        <v>13</v>
       </c>
       <c r="H45" t="str">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
-        <v>196,411,797</v>
+        <v>0</v>
       </c>
       <c r="J45" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K45" t="str">
-        <v>105,849,346</v>
+        <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>18,392,183,805</v>
+        <v>558,783,302</v>
       </c>
       <c r="M45" t="str">
-        <v>854,614,406</v>
+        <v>11,434,283</v>
       </c>
       <c r="N45" t="str">
-        <v>4.65%</v>
+        <v>2.05%</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Internal Collection-2</v>
+        <v>Internal Collection</v>
       </c>
       <c r="B46" t="str">
         <v>S2</v>
@@ -2393,39 +2393,83 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>544</v>
+        <v>6,755</v>
       </c>
       <c r="F46" t="str">
-        <v>51</v>
+        <v>338</v>
       </c>
       <c r="G46" t="str">
-        <v>56</v>
+        <v>8,132</v>
       </c>
       <c r="H46" t="str">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I46" t="str">
-        <v>0</v>
+        <v>196,411,797</v>
       </c>
       <c r="J46" t="str">
+        <v>7</v>
+      </c>
+      <c r="K46" t="str">
+        <v>124,130,356</v>
+      </c>
+      <c r="L46" t="str">
+        <v>19,197,920,925</v>
+      </c>
+      <c r="M46" t="str">
+        <v>908,187,877</v>
+      </c>
+      <c r="N46" t="str">
+        <v>4.73%</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Internal Collection-2</v>
+      </c>
+      <c r="B47" t="str">
+        <v>S2</v>
+      </c>
+      <c r="C47" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="D47" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="E47" t="str">
+        <v>577</v>
+      </c>
+      <c r="F47" t="str">
+        <v>52</v>
+      </c>
+      <c r="G47" t="str">
+        <v>59</v>
+      </c>
+      <c r="H47" t="str">
+        <v>0</v>
+      </c>
+      <c r="I47" t="str">
+        <v>0</v>
+      </c>
+      <c r="J47" t="str">
         <v>1</v>
       </c>
-      <c r="K46" t="str">
+      <c r="K47" t="str">
         <v>18,808,290</v>
       </c>
-      <c r="L46" t="str">
-        <v>306,907,017</v>
-      </c>
-      <c r="M46" t="str">
-        <v>38,696,446</v>
-      </c>
-      <c r="N46" t="str">
-        <v>12.61%</v>
+      <c r="L47" t="str">
+        <v>320,425,310</v>
+      </c>
+      <c r="M47" t="str">
+        <v>38,927,847</v>
+      </c>
+      <c r="N47" t="str">
+        <v>12.15%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,19 +457,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>4,460</v>
+        <v>4,668</v>
       </c>
       <c r="F2" t="str">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G2" t="str">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="H2" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="str">
-        <v>301,800,218</v>
+        <v>313,441,838</v>
       </c>
       <c r="J2" t="str">
         <v>6</v>
@@ -478,13 +478,13 @@
         <v>124,500,127</v>
       </c>
       <c r="L2" t="str">
-        <v>19,539,410,852</v>
+        <v>20,413,805,156</v>
       </c>
       <c r="M2" t="str">
-        <v>1,085,063,677</v>
+        <v>1,124,389,713</v>
       </c>
       <c r="N2" t="str">
-        <v>5.55%</v>
+        <v>5.51%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>2,798</v>
+        <v>2,924</v>
       </c>
       <c r="F3" t="str">
-        <v>765</v>
+        <v>794</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>5,227,576,123</v>
+        <v>5,442,602,312</v>
       </c>
       <c r="M3" t="str">
-        <v>1,351,000,415</v>
+        <v>1,405,255,886</v>
       </c>
       <c r="N3" t="str">
-        <v>25.84%</v>
+        <v>25.82%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>11,010</v>
+        <v>11,628</v>
       </c>
       <c r="F4" t="str">
-        <v>3,179</v>
+        <v>3,342</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>20,578,809,166</v>
+        <v>21,719,038,833</v>
       </c>
       <c r="M4" t="str">
-        <v>5,674,441,539</v>
+        <v>5,989,430,797</v>
       </c>
       <c r="N4" t="str">
-        <v>27.57%</v>
+        <v>27.58%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,195</v>
+        <v>1,259</v>
       </c>
       <c r="F5" t="str">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="G5" t="str">
-        <v>710</v>
+        <v>747</v>
       </c>
       <c r="H5" t="str">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I5" t="str">
-        <v>1,633,450,145</v>
+        <v>1,658,413,108</v>
       </c>
       <c r="J5" t="str">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K5" t="str">
-        <v>1,715,226,558</v>
+        <v>1,770,241,009</v>
       </c>
       <c r="L5" t="str">
-        <v>14,113,611,312</v>
+        <v>14,866,988,344</v>
       </c>
       <c r="M5" t="str">
-        <v>4,781,138,725</v>
+        <v>4,935,940,473</v>
       </c>
       <c r="N5" t="str">
-        <v>33.88%</v>
+        <v>33.20%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,633</v>
+        <v>1,697</v>
       </c>
       <c r="F6" t="str">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="G6" t="str">
-        <v>928</v>
+        <v>964</v>
       </c>
       <c r="H6" t="str">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I6" t="str">
-        <v>2,218,371,701</v>
+        <v>2,280,894,522</v>
       </c>
       <c r="J6" t="str">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K6" t="str">
-        <v>1,840,591,811</v>
+        <v>1,945,849,871</v>
       </c>
       <c r="L6" t="str">
-        <v>19,151,965,402</v>
+        <v>19,918,812,443</v>
       </c>
       <c r="M6" t="str">
-        <v>6,203,868,325</v>
+        <v>6,495,086,991</v>
       </c>
       <c r="N6" t="str">
-        <v>32.39%</v>
+        <v>32.61%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,485</v>
+        <v>1,549</v>
       </c>
       <c r="F7" t="str">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="G7" t="str">
-        <v>872</v>
+        <v>905</v>
       </c>
       <c r="H7" t="str">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="I7" t="str">
-        <v>2,161,318,730</v>
+        <v>2,295,516,674</v>
       </c>
       <c r="J7" t="str">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K7" t="str">
-        <v>1,526,970,649</v>
+        <v>1,606,099,269</v>
       </c>
       <c r="L7" t="str">
-        <v>17,534,518,971</v>
+        <v>18,265,796,343</v>
       </c>
       <c r="M7" t="str">
-        <v>5,553,975,812</v>
+        <v>5,893,871,525</v>
       </c>
       <c r="N7" t="str">
-        <v>31.67%</v>
+        <v>32.27%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="F8" t="str">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="G8" t="str">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="H8" t="str">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I8" t="str">
-        <v>875,925,885</v>
+        <v>937,060,489</v>
       </c>
       <c r="J8" t="str">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" t="str">
-        <v>877,195,409</v>
+        <v>901,286,412</v>
       </c>
       <c r="L8" t="str">
-        <v>8,888,265,591</v>
+        <v>9,257,437,928</v>
       </c>
       <c r="M8" t="str">
-        <v>2,723,703,002</v>
+        <v>2,859,653,488</v>
       </c>
       <c r="N8" t="str">
-        <v>30.64%</v>
+        <v>30.89%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>17,026</v>
+        <v>17,949</v>
       </c>
       <c r="F9" t="str">
-        <v>4,711</v>
+        <v>4,948</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>31,759,721,863</v>
+        <v>33,348,450,463</v>
       </c>
       <c r="M9" t="str">
-        <v>8,415,184,178</v>
+        <v>8,852,731,105</v>
       </c>
       <c r="N9" t="str">
-        <v>26.50%</v>
+        <v>26.55%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,789</v>
+        <v>1,884</v>
       </c>
       <c r="F10" t="str">
-        <v>839</v>
+        <v>887</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>600,552,077</v>
+        <v>632,107,895</v>
       </c>
       <c r="M10" t="str">
-        <v>253,216,943</v>
+        <v>268,302,369</v>
       </c>
       <c r="N10" t="str">
-        <v>42.16%</v>
+        <v>42.45%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,293</v>
+        <v>3,390</v>
       </c>
       <c r="F11" t="str">
-        <v>906</v>
+        <v>932</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>6,270,057,463</v>
+        <v>6,433,024,428</v>
       </c>
       <c r="M11" t="str">
-        <v>1,572,510,282</v>
+        <v>1,618,135,076</v>
       </c>
       <c r="N11" t="str">
-        <v>25.08%</v>
+        <v>25.15%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,513</v>
+        <v>2,592</v>
       </c>
       <c r="F12" t="str">
-        <v>736</v>
+        <v>762</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>4,775,879,373</v>
+        <v>4,930,869,579</v>
       </c>
       <c r="M12" t="str">
-        <v>1,308,891,175</v>
+        <v>1,351,536,428</v>
       </c>
       <c r="N12" t="str">
         <v>27.41%</v>
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>3,766</v>
+        <v>3,934</v>
       </c>
       <c r="F13" t="str">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" t="str">
-        <v>6,590</v>
+        <v>6,965</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>12,227,302,237</v>
+        <v>12,753,986,317</v>
       </c>
       <c r="M13" t="str">
-        <v>121,462,165</v>
+        <v>122,942,860</v>
       </c>
       <c r="N13" t="str">
-        <v>0.99%</v>
+        <v>0.96%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>10,568</v>
+        <v>11,043</v>
       </c>
       <c r="F14" t="str">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G14" t="str">
-        <v>23,644</v>
+        <v>24,647</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>33,414,910,223</v>
+        <v>34,881,204,018</v>
       </c>
       <c r="M14" t="str">
-        <v>387,395,899</v>
+        <v>395,553,392</v>
       </c>
       <c r="N14" t="str">
-        <v>1.16%</v>
+        <v>1.13%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>7,538</v>
+        <v>7,876</v>
       </c>
       <c r="F15" t="str">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G15" t="str">
-        <v>16,993</v>
+        <v>17,694</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,10 +1050,10 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>24,092,051,587</v>
+        <v>25,078,189,590</v>
       </c>
       <c r="M15" t="str">
-        <v>414,314,329</v>
+        <v>431,128,334</v>
       </c>
       <c r="N15" t="str">
         <v>1.72%</v>
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="F16" t="str">
         <v>8</v>
       </c>
       <c r="G16" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>410,779,246</v>
+        <v>427,766,361</v>
       </c>
       <c r="M16" t="str">
         <v>4,784,115</v>
       </c>
       <c r="N16" t="str">
-        <v>1.16%</v>
+        <v>1.12%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,19 +1117,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>13,747</v>
+        <v>14,355</v>
       </c>
       <c r="F17" t="str">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G17" t="str">
-        <v>62,487</v>
+        <v>64,831</v>
       </c>
       <c r="H17" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" t="str">
-        <v>45,136,474</v>
+        <v>65,177,834</v>
       </c>
       <c r="J17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>55,194,781,709</v>
+        <v>57,480,436,613</v>
       </c>
       <c r="M17" t="str">
-        <v>271,002,041</v>
+        <v>294,641,068</v>
       </c>
       <c r="N17" t="str">
-        <v>0.49%</v>
+        <v>0.51%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,194</v>
+        <v>1,248</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>5,395</v>
+        <v>5,591</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>4,849,794,649</v>
+        <v>4,994,885,117</v>
       </c>
       <c r="M18" t="str">
         <v>13,388,652</v>
       </c>
       <c r="N18" t="str">
-        <v>0.28%</v>
+        <v>0.27%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>5,374</v>
+        <v>5,615</v>
       </c>
       <c r="F19" t="str">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G19" t="str">
-        <v>23,343</v>
+        <v>24,267</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>21,968,919,431</v>
+        <v>22,820,438,940</v>
       </c>
       <c r="M19" t="str">
-        <v>137,003,046</v>
+        <v>139,067,204</v>
       </c>
       <c r="N19" t="str">
-        <v>0.62%</v>
+        <v>0.61%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,218</v>
+        <v>3,227</v>
       </c>
       <c r="F20" t="str">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G20" t="str">
-        <v>17,712</v>
+        <v>18,524</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,925,905,971</v>
+        <v>11,931,260,911</v>
       </c>
       <c r="M20" t="str">
-        <v>143,421,274</v>
+        <v>154,077,298</v>
       </c>
       <c r="N20" t="str">
-        <v>1.20%</v>
+        <v>1.29%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,893</v>
+        <v>2,904</v>
       </c>
       <c r="F21" t="str">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G21" t="str">
-        <v>114,884</v>
+        <v>120,106</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1308,19 +1308,19 @@
         <v>0</v>
       </c>
       <c r="J21" t="str">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K21" t="str">
-        <v>257,831,070</v>
+        <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,936,751,555</v>
+        <v>8,943,685,983</v>
       </c>
       <c r="M21" t="str">
-        <v>264,922,975</v>
+        <v>288,110,444</v>
       </c>
       <c r="N21" t="str">
-        <v>2.96%</v>
+        <v>3.22%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,19 +1337,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>11,515</v>
+        <v>11,843</v>
       </c>
       <c r="F22" t="str">
-        <v>929</v>
+        <v>991</v>
       </c>
       <c r="G22" t="str">
-        <v>441,020</v>
+        <v>461,561</v>
       </c>
       <c r="H22" t="str">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I22" t="str">
-        <v>252,531,680</v>
+        <v>368,124,920</v>
       </c>
       <c r="J22" t="str">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>56,160,331,766</v>
+        <v>57,539,078,875</v>
       </c>
       <c r="M22" t="str">
-        <v>1,574,576,144</v>
+        <v>1,698,469,822</v>
       </c>
       <c r="N22" t="str">
-        <v>2.80%</v>
+        <v>2.95%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>7,969</v>
+        <v>7,989</v>
       </c>
       <c r="F24" t="str">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="G24" t="str">
-        <v>59,145</v>
+        <v>61,834</v>
       </c>
       <c r="H24" t="str">
         <v>20</v>
@@ -1440,19 +1440,19 @@
         <v>240,826,900</v>
       </c>
       <c r="J24" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K24" t="str">
-        <v>127,273,040</v>
+        <v>184,925,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,392,235,919</v>
+        <v>52,409,483,640</v>
       </c>
       <c r="M24" t="str">
-        <v>442,495,468</v>
+        <v>486,876,756</v>
       </c>
       <c r="N24" t="str">
-        <v>0.84%</v>
+        <v>0.93%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>26,287</v>
+        <v>27,669</v>
       </c>
       <c r="F26" t="str">
-        <v>8,533</v>
+        <v>8,984</v>
       </c>
       <c r="G26" t="str">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H26" t="str">
         <v>13</v>
@@ -1534,13 +1534,13 @@
         <v>163,965,708</v>
       </c>
       <c r="L26" t="str">
-        <v>57,733,116,787</v>
+        <v>60,564,451,821</v>
       </c>
       <c r="M26" t="str">
-        <v>20,291,088,888</v>
+        <v>21,343,807,461</v>
       </c>
       <c r="N26" t="str">
-        <v>35.15%</v>
+        <v>35.24%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>4,232</v>
+        <v>4,468</v>
       </c>
       <c r="F27" t="str">
-        <v>2,305</v>
+        <v>2,450</v>
       </c>
       <c r="G27" t="str">
-        <v>4,240</v>
+        <v>4,466</v>
       </c>
       <c r="H27" t="str">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="I27" t="str">
-        <v>7,784,468,165</v>
+        <v>8,396,729,500</v>
       </c>
       <c r="J27" t="str">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="K27" t="str">
-        <v>11,222,263,753</v>
+        <v>11,917,738,992</v>
       </c>
       <c r="L27" t="str">
-        <v>52,187,047,485</v>
+        <v>55,180,832,648</v>
       </c>
       <c r="M27" t="str">
-        <v>24,721,638,299</v>
+        <v>26,315,062,184</v>
       </c>
       <c r="N27" t="str">
-        <v>47.37%</v>
+        <v>47.69%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>4,005</v>
+        <v>4,183</v>
       </c>
       <c r="F28" t="str">
-        <v>2,027</v>
+        <v>2,125</v>
       </c>
       <c r="G28" t="str">
-        <v>3,921</v>
+        <v>4,101</v>
       </c>
       <c r="H28" t="str">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="I28" t="str">
-        <v>7,670,728,998</v>
+        <v>8,033,088,090</v>
       </c>
       <c r="J28" t="str">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="K28" t="str">
-        <v>9,670,396,625</v>
+        <v>10,331,439,368</v>
       </c>
       <c r="L28" t="str">
-        <v>49,299,515,181</v>
+        <v>51,483,778,173</v>
       </c>
       <c r="M28" t="str">
-        <v>22,580,025,082</v>
+        <v>23,754,689,068</v>
       </c>
       <c r="N28" t="str">
-        <v>45.80%</v>
+        <v>46.14%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,612</v>
+        <v>2,731</v>
       </c>
       <c r="F29" t="str">
-        <v>1,353</v>
+        <v>1,413</v>
       </c>
       <c r="G29" t="str">
-        <v>2,681</v>
+        <v>2,800</v>
       </c>
       <c r="H29" t="str">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="I29" t="str">
-        <v>5,148,838,838</v>
+        <v>5,349,465,874</v>
       </c>
       <c r="J29" t="str">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="K29" t="str">
-        <v>7,320,701,578</v>
+        <v>7,582,594,755</v>
       </c>
       <c r="L29" t="str">
-        <v>32,293,333,925</v>
+        <v>33,727,836,398</v>
       </c>
       <c r="M29" t="str">
-        <v>15,396,483,801</v>
+        <v>16,006,919,956</v>
       </c>
       <c r="N29" t="str">
-        <v>47.68%</v>
+        <v>47.46%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,10 +1689,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>27,274</v>
+        <v>28,636</v>
       </c>
       <c r="F30" t="str">
-        <v>9,131</v>
+        <v>9,642</v>
       </c>
       <c r="G30" t="str">
         <v>135</v>
@@ -1710,13 +1710,13 @@
         <v>207,254,874</v>
       </c>
       <c r="L30" t="str">
-        <v>59,739,516,422</v>
+        <v>62,490,464,834</v>
       </c>
       <c r="M30" t="str">
-        <v>22,037,712,439</v>
+        <v>23,183,245,460</v>
       </c>
       <c r="N30" t="str">
-        <v>36.89%</v>
+        <v>37.10%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,546</v>
+        <v>2,670</v>
       </c>
       <c r="F31" t="str">
-        <v>1,135</v>
+        <v>1,193</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>971,065,624</v>
+        <v>1,015,703,832</v>
       </c>
       <c r="M31" t="str">
-        <v>438,381,205</v>
+        <v>459,369,510</v>
       </c>
       <c r="N31" t="str">
-        <v>45.14%</v>
+        <v>45.23%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,692</v>
+        <v>1,759</v>
       </c>
       <c r="F32" t="str">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="G32" t="str">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,059,521,986</v>
+        <v>3,176,882,854</v>
       </c>
       <c r="M32" t="str">
-        <v>492,378,286</v>
+        <v>516,644,307</v>
       </c>
       <c r="N32" t="str">
-        <v>16.09%</v>
+        <v>16.26%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,10 +1821,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,121</v>
+        <v>2,203</v>
       </c>
       <c r="F33" t="str">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="G33" t="str">
         <v>41</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>3,695,882,322</v>
+        <v>3,845,738,739</v>
       </c>
       <c r="M33" t="str">
-        <v>494,762,521</v>
+        <v>523,265,140</v>
       </c>
       <c r="N33" t="str">
-        <v>13.39%</v>
+        <v>13.61%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>8,728</v>
+        <v>9,113</v>
       </c>
       <c r="F34" t="str">
-        <v>1,425</v>
+        <v>1,492</v>
       </c>
       <c r="G34" t="str">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>16,418,973,457</v>
+        <v>17,113,497,950</v>
       </c>
       <c r="M34" t="str">
-        <v>2,246,831,711</v>
+        <v>2,365,432,594</v>
       </c>
       <c r="N34" t="str">
-        <v>13.68%</v>
+        <v>13.82%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,820</v>
+        <v>1,923</v>
       </c>
       <c r="F35" t="str">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="G35" t="str">
-        <v>5,692</v>
+        <v>5,949</v>
       </c>
       <c r="H35" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I35" t="str">
-        <v>1,252,816,143</v>
+        <v>1,279,810,318</v>
       </c>
       <c r="J35" t="str">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K35" t="str">
-        <v>1,046,008,797</v>
+        <v>1,063,995,837</v>
       </c>
       <c r="L35" t="str">
-        <v>20,002,167,124</v>
+        <v>21,130,531,494</v>
       </c>
       <c r="M35" t="str">
-        <v>3,192,129,926</v>
+        <v>3,319,856,475</v>
       </c>
       <c r="N35" t="str">
-        <v>15.96%</v>
+        <v>15.71%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,447</v>
+        <v>1,527</v>
       </c>
       <c r="F36" t="str">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G36" t="str">
-        <v>3,959</v>
+        <v>4,156</v>
       </c>
       <c r="H36" t="str">
         <v>65</v>
@@ -1968,19 +1968,19 @@
         <v>804,307,362</v>
       </c>
       <c r="J36" t="str">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K36" t="str">
-        <v>802,311,044</v>
+        <v>836,314,099</v>
       </c>
       <c r="L36" t="str">
-        <v>15,728,488,277</v>
+        <v>16,658,989,484</v>
       </c>
       <c r="M36" t="str">
-        <v>2,345,755,080</v>
+        <v>2,444,814,790</v>
       </c>
       <c r="N36" t="str">
-        <v>14.91%</v>
+        <v>14.68%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>8,075</v>
+        <v>8,407</v>
       </c>
       <c r="F37" t="str">
-        <v>1,265</v>
+        <v>1,328</v>
       </c>
       <c r="G37" t="str">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,10 +2018,10 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>14,711,031,312</v>
+        <v>15,270,198,181</v>
       </c>
       <c r="M37" t="str">
-        <v>2,516,079,456</v>
+        <v>2,611,019,663</v>
       </c>
       <c r="N37" t="str">
         <v>17.10%</v>
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>903</v>
+        <v>949</v>
       </c>
       <c r="F38" t="str">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>389,762,341</v>
+        <v>422,975,607</v>
       </c>
       <c r="M38" t="str">
-        <v>83,760,618</v>
+        <v>93,643,521</v>
       </c>
       <c r="N38" t="str">
-        <v>21.49%</v>
+        <v>22.14%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,756</v>
+        <v>2,830</v>
       </c>
       <c r="F39" t="str">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="G39" t="str">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>5,025,626,351</v>
+        <v>5,168,747,733</v>
       </c>
       <c r="M39" t="str">
-        <v>666,471,738</v>
+        <v>700,345,960</v>
       </c>
       <c r="N39" t="str">
-        <v>13.26%</v>
+        <v>13.55%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,320</v>
+        <v>2,446</v>
       </c>
       <c r="F41" t="str">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>4,182,954,459</v>
+        <v>4,433,154,461</v>
       </c>
       <c r="M41" t="str">
-        <v>598,532,251</v>
+        <v>649,814,473</v>
       </c>
       <c r="N41" t="str">
-        <v>14.31%</v>
+        <v>14.66%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,566</v>
+        <v>2,666</v>
       </c>
       <c r="F42" t="str">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="G42" t="str">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>4,760,071,407</v>
+        <v>4,978,308,500</v>
       </c>
       <c r="M42" t="str">
-        <v>658,293,732</v>
+        <v>705,065,469</v>
       </c>
       <c r="N42" t="str">
-        <v>13.83%</v>
+        <v>14.16%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>7,691</v>
+        <v>7,984</v>
       </c>
       <c r="F43" t="str">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="G43" t="str">
-        <v>9,967</v>
+        <v>10,354</v>
       </c>
       <c r="H43" t="str">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>21,619,014,076</v>
+        <v>22,323,569,071</v>
       </c>
       <c r="M43" t="str">
-        <v>723,293,623</v>
+        <v>758,000,021</v>
       </c>
       <c r="N43" t="str">
-        <v>3.35%</v>
+        <v>3.40%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,19 +2305,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>10,315</v>
+        <v>10,755</v>
       </c>
       <c r="F44" t="str">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="G44" t="str">
-        <v>13,828</v>
+        <v>14,435</v>
       </c>
       <c r="H44" t="str">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I44" t="str">
-        <v>207,633,707</v>
+        <v>218,788,073</v>
       </c>
       <c r="J44" t="str">
         <v>13</v>
@@ -2326,13 +2326,13 @@
         <v>243,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>29,823,193,931</v>
+        <v>30,917,764,000</v>
       </c>
       <c r="M44" t="str">
-        <v>1,274,915,796</v>
+        <v>1,344,355,635</v>
       </c>
       <c r="N44" t="str">
-        <v>4.27%</v>
+        <v>4.35%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,19 +2349,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>161</v>
+        <v>339</v>
       </c>
       <c r="F45" t="str">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G45" t="str">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H45" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="str">
-        <v>0</v>
+        <v>13,819,837</v>
       </c>
       <c r="J45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>558,783,302</v>
+        <v>1,239,648,419</v>
       </c>
       <c r="M45" t="str">
-        <v>11,434,283</v>
+        <v>32,848,040</v>
       </c>
       <c r="N45" t="str">
-        <v>2.05%</v>
+        <v>2.65%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,19 +2393,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>6,755</v>
+        <v>7,076</v>
       </c>
       <c r="F46" t="str">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="G46" t="str">
-        <v>8,132</v>
+        <v>8,495</v>
       </c>
       <c r="H46" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" t="str">
-        <v>196,411,797</v>
+        <v>210,093,634</v>
       </c>
       <c r="J46" t="str">
         <v>7</v>
@@ -2414,13 +2414,13 @@
         <v>124,130,356</v>
       </c>
       <c r="L46" t="str">
-        <v>19,197,920,925</v>
+        <v>19,947,442,330</v>
       </c>
       <c r="M46" t="str">
-        <v>908,187,877</v>
+        <v>950,966,241</v>
       </c>
       <c r="N46" t="str">
-        <v>4.73%</v>
+        <v>4.77%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="F47" t="str">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G47" t="str">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>320,425,310</v>
+        <v>335,488,869</v>
       </c>
       <c r="M47" t="str">
-        <v>38,927,847</v>
+        <v>39,957,885</v>
       </c>
       <c r="N47" t="str">
-        <v>12.15%</v>
+        <v>11.91%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>4,668</v>
+        <v>4,877</v>
       </c>
       <c r="F2" t="str">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="G2" t="str">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="H2" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" t="str">
-        <v>313,441,838</v>
+        <v>325,083,458</v>
       </c>
       <c r="J2" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="str">
-        <v>124,500,127</v>
+        <v>140,563,756</v>
       </c>
       <c r="L2" t="str">
-        <v>20,413,805,156</v>
+        <v>21,424,452,735</v>
       </c>
       <c r="M2" t="str">
-        <v>1,124,389,713</v>
+        <v>1,171,229,372</v>
       </c>
       <c r="N2" t="str">
-        <v>5.51%</v>
+        <v>5.47%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>2,924</v>
+        <v>3,057</v>
       </c>
       <c r="F3" t="str">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>5,442,602,312</v>
+        <v>5,663,430,932</v>
       </c>
       <c r="M3" t="str">
-        <v>1,405,255,886</v>
+        <v>1,466,873,822</v>
       </c>
       <c r="N3" t="str">
-        <v>25.82%</v>
+        <v>25.90%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>11,628</v>
+        <v>12,153</v>
       </c>
       <c r="F4" t="str">
-        <v>3,342</v>
+        <v>3,496</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>21,719,038,833</v>
+        <v>22,684,062,955</v>
       </c>
       <c r="M4" t="str">
-        <v>5,989,430,797</v>
+        <v>6,260,183,078</v>
       </c>
       <c r="N4" t="str">
-        <v>27.58%</v>
+        <v>27.60%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,259</v>
+        <v>1,298</v>
       </c>
       <c r="F5" t="str">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="G5" t="str">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="H5" t="str">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I5" t="str">
-        <v>1,658,413,108</v>
+        <v>1,740,295,688</v>
       </c>
       <c r="J5" t="str">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K5" t="str">
-        <v>1,770,241,009</v>
+        <v>1,877,364,624</v>
       </c>
       <c r="L5" t="str">
-        <v>14,866,988,344</v>
+        <v>15,343,874,562</v>
       </c>
       <c r="M5" t="str">
-        <v>4,935,940,473</v>
+        <v>5,182,980,361</v>
       </c>
       <c r="N5" t="str">
-        <v>33.20%</v>
+        <v>33.78%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,697</v>
+        <v>1,775</v>
       </c>
       <c r="F6" t="str">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="G6" t="str">
-        <v>964</v>
+        <v>1,007</v>
       </c>
       <c r="H6" t="str">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I6" t="str">
-        <v>2,280,894,522</v>
+        <v>2,360,716,189</v>
       </c>
       <c r="J6" t="str">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K6" t="str">
-        <v>1,945,849,871</v>
+        <v>1,966,316,796</v>
       </c>
       <c r="L6" t="str">
-        <v>19,918,812,443</v>
+        <v>20,794,552,485</v>
       </c>
       <c r="M6" t="str">
-        <v>6,495,086,991</v>
+        <v>6,714,865,941</v>
       </c>
       <c r="N6" t="str">
-        <v>32.61%</v>
+        <v>32.29%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,549</v>
+        <v>1,602</v>
       </c>
       <c r="F7" t="str">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="G7" t="str">
-        <v>905</v>
+        <v>938</v>
       </c>
       <c r="H7" t="str">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="I7" t="str">
-        <v>2,295,516,674</v>
+        <v>2,353,966,607</v>
       </c>
       <c r="J7" t="str">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K7" t="str">
-        <v>1,606,099,269</v>
+        <v>1,648,487,456</v>
       </c>
       <c r="L7" t="str">
-        <v>18,265,796,343</v>
+        <v>18,871,891,664</v>
       </c>
       <c r="M7" t="str">
-        <v>5,893,871,525</v>
+        <v>6,056,247,626</v>
       </c>
       <c r="N7" t="str">
-        <v>32.27%</v>
+        <v>32.09%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>776</v>
+        <v>802</v>
       </c>
       <c r="F8" t="str">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="G8" t="str">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="H8" t="str">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" t="str">
-        <v>937,060,489</v>
+        <v>951,683,544</v>
       </c>
       <c r="J8" t="str">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K8" t="str">
-        <v>901,286,412</v>
+        <v>987,288,717</v>
       </c>
       <c r="L8" t="str">
-        <v>9,257,437,928</v>
+        <v>9,596,985,519</v>
       </c>
       <c r="M8" t="str">
-        <v>2,859,653,488</v>
+        <v>3,000,958,606</v>
       </c>
       <c r="N8" t="str">
-        <v>30.89%</v>
+        <v>31.27%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>17,949</v>
+        <v>18,853</v>
       </c>
       <c r="F9" t="str">
-        <v>4,948</v>
+        <v>5,199</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>33,348,450,463</v>
+        <v>34,922,243,776</v>
       </c>
       <c r="M9" t="str">
-        <v>8,852,731,105</v>
+        <v>9,283,508,039</v>
       </c>
       <c r="N9" t="str">
-        <v>26.55%</v>
+        <v>26.58%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,884</v>
+        <v>1,978</v>
       </c>
       <c r="F10" t="str">
-        <v>887</v>
+        <v>932</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>632,107,895</v>
+        <v>664,042,905</v>
       </c>
       <c r="M10" t="str">
-        <v>268,302,369</v>
+        <v>283,919,693</v>
       </c>
       <c r="N10" t="str">
-        <v>42.45%</v>
+        <v>42.76%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,390</v>
+        <v>3,510</v>
       </c>
       <c r="F11" t="str">
-        <v>932</v>
+        <v>971</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>6,433,024,428</v>
+        <v>6,653,298,624</v>
       </c>
       <c r="M11" t="str">
-        <v>1,618,135,076</v>
+        <v>1,685,738,010</v>
       </c>
       <c r="N11" t="str">
-        <v>25.15%</v>
+        <v>25.34%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,592</v>
+        <v>2,718</v>
       </c>
       <c r="F12" t="str">
-        <v>762</v>
+        <v>792</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>4,930,869,579</v>
+        <v>5,152,176,167</v>
       </c>
       <c r="M12" t="str">
-        <v>1,351,536,428</v>
+        <v>1,401,323,790</v>
       </c>
       <c r="N12" t="str">
-        <v>27.41%</v>
+        <v>27.20%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>3,934</v>
+        <v>4,097</v>
       </c>
       <c r="F13" t="str">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G13" t="str">
-        <v>6,965</v>
+        <v>7,329</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,10 +962,10 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>12,753,986,317</v>
+        <v>13,229,844,421</v>
       </c>
       <c r="M13" t="str">
-        <v>122,942,860</v>
+        <v>126,418,155</v>
       </c>
       <c r="N13" t="str">
         <v>0.96%</v>
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>11,043</v>
+        <v>11,497</v>
       </c>
       <c r="F14" t="str">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G14" t="str">
-        <v>24,647</v>
+        <v>25,652</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>34,881,204,018</v>
+        <v>36,327,403,243</v>
       </c>
       <c r="M14" t="str">
-        <v>395,553,392</v>
+        <v>403,936,215</v>
       </c>
       <c r="N14" t="str">
-        <v>1.13%</v>
+        <v>1.11%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>7,876</v>
+        <v>8,203</v>
       </c>
       <c r="F15" t="str">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G15" t="str">
-        <v>17,694</v>
+        <v>18,386</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>25,078,189,590</v>
+        <v>26,082,754,516</v>
       </c>
       <c r="M15" t="str">
-        <v>431,128,334</v>
+        <v>435,562,412</v>
       </c>
       <c r="N15" t="str">
-        <v>1.72%</v>
+        <v>1.67%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="F16" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>427,766,361</v>
+        <v>451,386,617</v>
       </c>
       <c r="M16" t="str">
-        <v>4,784,115</v>
+        <v>5,315,782</v>
       </c>
       <c r="N16" t="str">
-        <v>1.12%</v>
+        <v>1.18%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>14,355</v>
+        <v>14,953</v>
       </c>
       <c r="F17" t="str">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G17" t="str">
-        <v>64,831</v>
+        <v>67,145</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>57,480,436,613</v>
+        <v>59,775,861,020</v>
       </c>
       <c r="M17" t="str">
-        <v>294,641,068</v>
+        <v>306,303,288</v>
       </c>
       <c r="N17" t="str">
         <v>0.51%</v>
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,248</v>
+        <v>1,300</v>
       </c>
       <c r="F18" t="str">
         <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>5,591</v>
+        <v>5,790</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>4,994,885,117</v>
+        <v>5,227,723,961</v>
       </c>
       <c r="M18" t="str">
         <v>13,388,652</v>
       </c>
       <c r="N18" t="str">
-        <v>0.27%</v>
+        <v>0.26%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>5,615</v>
+        <v>5,850</v>
       </c>
       <c r="F19" t="str">
         <v>57</v>
       </c>
       <c r="G19" t="str">
-        <v>24,267</v>
+        <v>25,190</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>22,820,438,940</v>
+        <v>23,662,688,303</v>
       </c>
       <c r="M19" t="str">
         <v>139,067,204</v>
       </c>
       <c r="N19" t="str">
-        <v>0.61%</v>
+        <v>0.59%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,227</v>
+        <v>3,239</v>
       </c>
       <c r="F20" t="str">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G20" t="str">
-        <v>18,524</v>
+        <v>19,336</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,931,260,911</v>
+        <v>11,942,076,845</v>
       </c>
       <c r="M20" t="str">
-        <v>154,077,298</v>
+        <v>155,577,298</v>
       </c>
       <c r="N20" t="str">
-        <v>1.29%</v>
+        <v>1.30%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,904</v>
+        <v>2,916</v>
       </c>
       <c r="F21" t="str">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G21" t="str">
-        <v>120,106</v>
+        <v>125,327</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,943,685,983</v>
+        <v>8,953,329,076</v>
       </c>
       <c r="M21" t="str">
-        <v>288,110,444</v>
+        <v>289,712,814</v>
       </c>
       <c r="N21" t="str">
-        <v>3.22%</v>
+        <v>3.24%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,19 +1337,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>11,843</v>
+        <v>12,165</v>
       </c>
       <c r="F22" t="str">
-        <v>991</v>
+        <v>1,061</v>
       </c>
       <c r="G22" t="str">
-        <v>461,561</v>
+        <v>482,133</v>
       </c>
       <c r="H22" t="str">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I22" t="str">
-        <v>368,124,920</v>
+        <v>422,986,680</v>
       </c>
       <c r="J22" t="str">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>57,539,078,875</v>
+        <v>58,947,518,734</v>
       </c>
       <c r="M22" t="str">
-        <v>1,698,469,822</v>
+        <v>1,833,711,001</v>
       </c>
       <c r="N22" t="str">
-        <v>2.95%</v>
+        <v>3.11%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>7,989</v>
+        <v>8,015</v>
       </c>
       <c r="F24" t="str">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G24" t="str">
-        <v>61,834</v>
+        <v>64,522</v>
       </c>
       <c r="H24" t="str">
         <v>20</v>
@@ -1446,13 +1446,13 @@
         <v>184,925,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,409,483,640</v>
+        <v>52,431,035,270</v>
       </c>
       <c r="M24" t="str">
-        <v>486,876,756</v>
+        <v>501,739,256</v>
       </c>
       <c r="N24" t="str">
-        <v>0.93%</v>
+        <v>0.96%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,19 +1513,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>27,669</v>
+        <v>28,936</v>
       </c>
       <c r="F26" t="str">
-        <v>8,984</v>
+        <v>9,374</v>
       </c>
       <c r="G26" t="str">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H26" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" t="str">
-        <v>160,770,077</v>
+        <v>175,320,132</v>
       </c>
       <c r="J26" t="str">
         <v>9</v>
@@ -1534,13 +1534,13 @@
         <v>163,965,708</v>
       </c>
       <c r="L26" t="str">
-        <v>60,564,451,821</v>
+        <v>63,249,656,723</v>
       </c>
       <c r="M26" t="str">
-        <v>21,343,807,461</v>
+        <v>22,233,251,643</v>
       </c>
       <c r="N26" t="str">
-        <v>35.24%</v>
+        <v>35.15%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>4,468</v>
+        <v>4,629</v>
       </c>
       <c r="F27" t="str">
-        <v>2,450</v>
+        <v>2,555</v>
       </c>
       <c r="G27" t="str">
-        <v>4,466</v>
+        <v>4,655</v>
       </c>
       <c r="H27" t="str">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="I27" t="str">
-        <v>8,396,729,500</v>
+        <v>8,771,769,949</v>
       </c>
       <c r="J27" t="str">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="K27" t="str">
-        <v>11,917,738,992</v>
+        <v>12,366,908,962</v>
       </c>
       <c r="L27" t="str">
-        <v>55,180,832,648</v>
+        <v>57,250,069,262</v>
       </c>
       <c r="M27" t="str">
-        <v>26,315,062,184</v>
+        <v>27,396,548,768</v>
       </c>
       <c r="N27" t="str">
-        <v>47.69%</v>
+        <v>47.85%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>4,183</v>
+        <v>4,384</v>
       </c>
       <c r="F28" t="str">
-        <v>2,125</v>
+        <v>2,216</v>
       </c>
       <c r="G28" t="str">
-        <v>4,101</v>
+        <v>4,303</v>
       </c>
       <c r="H28" t="str">
-        <v>641</v>
+        <v>665</v>
       </c>
       <c r="I28" t="str">
-        <v>8,033,088,090</v>
+        <v>8,330,278,067</v>
       </c>
       <c r="J28" t="str">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="K28" t="str">
-        <v>10,331,439,368</v>
+        <v>10,741,105,763</v>
       </c>
       <c r="L28" t="str">
-        <v>51,483,778,173</v>
+        <v>54,043,925,943</v>
       </c>
       <c r="M28" t="str">
-        <v>23,754,689,068</v>
+        <v>24,727,967,710</v>
       </c>
       <c r="N28" t="str">
-        <v>46.14%</v>
+        <v>45.76%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,731</v>
+        <v>2,853</v>
       </c>
       <c r="F29" t="str">
-        <v>1,413</v>
+        <v>1,483</v>
       </c>
       <c r="G29" t="str">
-        <v>2,800</v>
+        <v>2,928</v>
       </c>
       <c r="H29" t="str">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="I29" t="str">
-        <v>5,349,465,874</v>
+        <v>5,569,484,456</v>
       </c>
       <c r="J29" t="str">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="K29" t="str">
-        <v>7,582,594,755</v>
+        <v>8,106,946,518</v>
       </c>
       <c r="L29" t="str">
-        <v>33,727,836,398</v>
+        <v>35,224,045,165</v>
       </c>
       <c r="M29" t="str">
-        <v>16,006,919,956</v>
+        <v>16,854,076,403</v>
       </c>
       <c r="N29" t="str">
-        <v>47.46%</v>
+        <v>47.85%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>28,636</v>
+        <v>30,155</v>
       </c>
       <c r="F30" t="str">
-        <v>9,642</v>
+        <v>10,028</v>
       </c>
       <c r="G30" t="str">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H30" t="str">
         <v>15</v>
@@ -1710,13 +1710,13 @@
         <v>207,254,874</v>
       </c>
       <c r="L30" t="str">
-        <v>62,490,464,834</v>
+        <v>65,688,992,243</v>
       </c>
       <c r="M30" t="str">
-        <v>23,183,245,460</v>
+        <v>24,059,543,850</v>
       </c>
       <c r="N30" t="str">
-        <v>37.10%</v>
+        <v>36.63%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,670</v>
+        <v>2,772</v>
       </c>
       <c r="F31" t="str">
-        <v>1,193</v>
+        <v>1,248</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,015,703,832</v>
+        <v>1,057,343,172</v>
       </c>
       <c r="M31" t="str">
-        <v>459,369,510</v>
+        <v>478,815,275</v>
       </c>
       <c r="N31" t="str">
-        <v>45.23%</v>
+        <v>45.28%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,759</v>
+        <v>1,847</v>
       </c>
       <c r="F32" t="str">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="G32" t="str">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,176,882,854</v>
+        <v>3,324,440,302</v>
       </c>
       <c r="M32" t="str">
-        <v>516,644,307</v>
+        <v>529,236,560</v>
       </c>
       <c r="N32" t="str">
-        <v>16.26%</v>
+        <v>15.92%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,10 +1821,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,203</v>
+        <v>2,312</v>
       </c>
       <c r="F33" t="str">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="G33" t="str">
         <v>41</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>3,845,738,739</v>
+        <v>4,004,403,644</v>
       </c>
       <c r="M33" t="str">
-        <v>523,265,140</v>
+        <v>547,599,025</v>
       </c>
       <c r="N33" t="str">
-        <v>13.61%</v>
+        <v>13.67%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>9,113</v>
+        <v>9,551</v>
       </c>
       <c r="F34" t="str">
-        <v>1,492</v>
+        <v>1,545</v>
       </c>
       <c r="G34" t="str">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>17,113,497,950</v>
+        <v>17,849,515,111</v>
       </c>
       <c r="M34" t="str">
-        <v>2,365,432,594</v>
+        <v>2,437,306,300</v>
       </c>
       <c r="N34" t="str">
-        <v>13.82%</v>
+        <v>13.65%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,923</v>
+        <v>1,988</v>
       </c>
       <c r="F35" t="str">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="G35" t="str">
-        <v>5,949</v>
+        <v>6,201</v>
       </c>
       <c r="H35" t="str">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I35" t="str">
-        <v>1,279,810,318</v>
+        <v>1,336,640,339</v>
       </c>
       <c r="J35" t="str">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K35" t="str">
-        <v>1,063,995,837</v>
+        <v>1,118,099,906</v>
       </c>
       <c r="L35" t="str">
-        <v>21,130,531,494</v>
+        <v>21,784,620,169</v>
       </c>
       <c r="M35" t="str">
-        <v>3,319,856,475</v>
+        <v>3,515,397,342</v>
       </c>
       <c r="N35" t="str">
-        <v>15.71%</v>
+        <v>16.14%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,19 +1953,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,527</v>
+        <v>1,605</v>
       </c>
       <c r="F36" t="str">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="G36" t="str">
-        <v>4,156</v>
+        <v>4,378</v>
       </c>
       <c r="H36" t="str">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I36" t="str">
-        <v>804,307,362</v>
+        <v>826,679,704</v>
       </c>
       <c r="J36" t="str">
         <v>42</v>
@@ -1974,13 +1974,13 @@
         <v>836,314,099</v>
       </c>
       <c r="L36" t="str">
-        <v>16,658,989,484</v>
+        <v>17,492,959,431</v>
       </c>
       <c r="M36" t="str">
-        <v>2,444,814,790</v>
+        <v>2,537,466,069</v>
       </c>
       <c r="N36" t="str">
-        <v>14.68%</v>
+        <v>14.51%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>8,407</v>
+        <v>8,827</v>
       </c>
       <c r="F37" t="str">
-        <v>1,328</v>
+        <v>1,384</v>
       </c>
       <c r="G37" t="str">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>15,270,198,181</v>
+        <v>15,919,003,184</v>
       </c>
       <c r="M37" t="str">
-        <v>2,611,019,663</v>
+        <v>2,701,800,734</v>
       </c>
       <c r="N37" t="str">
-        <v>17.10%</v>
+        <v>16.97%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>949</v>
+        <v>994</v>
       </c>
       <c r="F38" t="str">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>422,975,607</v>
+        <v>437,749,149</v>
       </c>
       <c r="M38" t="str">
-        <v>93,643,521</v>
+        <v>96,005,647</v>
       </c>
       <c r="N38" t="str">
-        <v>22.14%</v>
+        <v>21.93%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,10 +2085,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,830</v>
+        <v>2,948</v>
       </c>
       <c r="F39" t="str">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="G39" t="str">
         <v>74</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>5,168,747,733</v>
+        <v>5,366,291,236</v>
       </c>
       <c r="M39" t="str">
-        <v>700,345,960</v>
+        <v>740,629,098</v>
       </c>
       <c r="N39" t="str">
-        <v>13.55%</v>
+        <v>13.80%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,446</v>
+        <v>2,581</v>
       </c>
       <c r="F41" t="str">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>4,433,154,461</v>
+        <v>4,659,248,197</v>
       </c>
       <c r="M41" t="str">
-        <v>649,814,473</v>
+        <v>671,616,379</v>
       </c>
       <c r="N41" t="str">
-        <v>14.66%</v>
+        <v>14.41%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,666</v>
+        <v>2,798</v>
       </c>
       <c r="F42" t="str">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="G42" t="str">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>4,978,308,500</v>
+        <v>5,251,242,057</v>
       </c>
       <c r="M42" t="str">
-        <v>705,065,469</v>
+        <v>726,755,379</v>
       </c>
       <c r="N42" t="str">
-        <v>14.16%</v>
+        <v>13.84%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>7,984</v>
+        <v>8,237</v>
       </c>
       <c r="F43" t="str">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="G43" t="str">
-        <v>10,354</v>
+        <v>10,733</v>
       </c>
       <c r="H43" t="str">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>22,323,569,071</v>
+        <v>22,924,171,503</v>
       </c>
       <c r="M43" t="str">
-        <v>758,000,021</v>
+        <v>772,419,558</v>
       </c>
       <c r="N43" t="str">
-        <v>3.40%</v>
+        <v>3.37%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,19 +2305,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>10,755</v>
+        <v>11,134</v>
       </c>
       <c r="F44" t="str">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="G44" t="str">
-        <v>14,435</v>
+        <v>15,034</v>
       </c>
       <c r="H44" t="str">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I44" t="str">
-        <v>218,788,073</v>
+        <v>232,461,030</v>
       </c>
       <c r="J44" t="str">
         <v>13</v>
@@ -2326,13 +2326,13 @@
         <v>243,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>30,917,764,000</v>
+        <v>31,797,128,778</v>
       </c>
       <c r="M44" t="str">
-        <v>1,344,355,635</v>
+        <v>1,376,977,414</v>
       </c>
       <c r="N44" t="str">
-        <v>4.35%</v>
+        <v>4.33%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,19 +2349,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>339</v>
+        <v>494</v>
       </c>
       <c r="F45" t="str">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G45" t="str">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="H45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="str">
-        <v>13,819,837</v>
+        <v>27,639,674</v>
       </c>
       <c r="J45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>1,239,648,419</v>
+        <v>1,685,800,789</v>
       </c>
       <c r="M45" t="str">
-        <v>32,848,040</v>
+        <v>69,913,162</v>
       </c>
       <c r="N45" t="str">
-        <v>2.65%</v>
+        <v>4.15%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>7,076</v>
+        <v>7,354</v>
       </c>
       <c r="F46" t="str">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G46" t="str">
-        <v>8,495</v>
+        <v>8,862</v>
       </c>
       <c r="H46" t="str">
         <v>17</v>
@@ -2414,13 +2414,13 @@
         <v>124,130,356</v>
       </c>
       <c r="L46" t="str">
-        <v>19,947,442,330</v>
+        <v>20,690,645,439</v>
       </c>
       <c r="M46" t="str">
-        <v>950,966,241</v>
+        <v>967,265,697</v>
       </c>
       <c r="N46" t="str">
-        <v>4.77%</v>
+        <v>4.67%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="F47" t="str">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G47" t="str">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>335,488,869</v>
+        <v>347,174,063</v>
       </c>
       <c r="M47" t="str">
-        <v>39,957,885</v>
+        <v>41,156,408</v>
       </c>
       <c r="N47" t="str">
-        <v>11.91%</v>
+        <v>11.85%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,13 +457,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>4,877</v>
+        <v>5,080</v>
       </c>
       <c r="F2" t="str">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G2" t="str">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="H2" t="str">
         <v>27</v>
@@ -478,13 +478,13 @@
         <v>140,563,756</v>
       </c>
       <c r="L2" t="str">
-        <v>21,424,452,735</v>
+        <v>22,205,644,407</v>
       </c>
       <c r="M2" t="str">
-        <v>1,171,229,372</v>
+        <v>1,188,784,807</v>
       </c>
       <c r="N2" t="str">
-        <v>5.47%</v>
+        <v>5.35%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,057</v>
+        <v>3,190</v>
       </c>
       <c r="F3" t="str">
-        <v>833</v>
+        <v>864</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>5,663,430,932</v>
+        <v>5,914,724,076</v>
       </c>
       <c r="M3" t="str">
-        <v>1,466,873,822</v>
+        <v>1,516,801,523</v>
       </c>
       <c r="N3" t="str">
-        <v>25.90%</v>
+        <v>25.64%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>12,153</v>
+        <v>12,779</v>
       </c>
       <c r="F4" t="str">
-        <v>3,496</v>
+        <v>3,652</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>22,684,062,955</v>
+        <v>23,809,151,735</v>
       </c>
       <c r="M4" t="str">
-        <v>6,260,183,078</v>
+        <v>6,556,975,307</v>
       </c>
       <c r="N4" t="str">
-        <v>27.60%</v>
+        <v>27.54%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,298</v>
+        <v>1,357</v>
       </c>
       <c r="F5" t="str">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="G5" t="str">
-        <v>774</v>
+        <v>811</v>
       </c>
       <c r="H5" t="str">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="I5" t="str">
-        <v>1,740,295,688</v>
+        <v>1,946,796,942</v>
       </c>
       <c r="J5" t="str">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K5" t="str">
-        <v>1,877,364,624</v>
+        <v>1,977,704,687</v>
       </c>
       <c r="L5" t="str">
-        <v>15,343,874,562</v>
+        <v>16,050,183,013</v>
       </c>
       <c r="M5" t="str">
-        <v>5,182,980,361</v>
+        <v>5,575,013,648</v>
       </c>
       <c r="N5" t="str">
-        <v>33.78%</v>
+        <v>34.73%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,775</v>
+        <v>1,848</v>
       </c>
       <c r="F6" t="str">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="G6" t="str">
-        <v>1,007</v>
+        <v>1,056</v>
       </c>
       <c r="H6" t="str">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="I6" t="str">
-        <v>2,360,716,189</v>
+        <v>2,523,668,607</v>
       </c>
       <c r="J6" t="str">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K6" t="str">
-        <v>1,966,316,796</v>
+        <v>2,044,482,843</v>
       </c>
       <c r="L6" t="str">
-        <v>20,794,552,485</v>
+        <v>21,695,497,981</v>
       </c>
       <c r="M6" t="str">
-        <v>6,714,865,941</v>
+        <v>6,995,114,341</v>
       </c>
       <c r="N6" t="str">
-        <v>32.29%</v>
+        <v>32.24%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,602</v>
+        <v>1,662</v>
       </c>
       <c r="F7" t="str">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="G7" t="str">
-        <v>938</v>
+        <v>974</v>
       </c>
       <c r="H7" t="str">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I7" t="str">
-        <v>2,353,966,607</v>
+        <v>2,364,678,653</v>
       </c>
       <c r="J7" t="str">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K7" t="str">
-        <v>1,648,487,456</v>
+        <v>1,769,765,861</v>
       </c>
       <c r="L7" t="str">
-        <v>18,871,891,664</v>
+        <v>19,562,698,730</v>
       </c>
       <c r="M7" t="str">
-        <v>6,056,247,626</v>
+        <v>6,267,292,216</v>
       </c>
       <c r="N7" t="str">
-        <v>32.09%</v>
+        <v>32.04%</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>802</v>
+        <v>832</v>
       </c>
       <c r="F8" t="str">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="G8" t="str">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="H8" t="str">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I8" t="str">
-        <v>951,683,544</v>
+        <v>1,011,129,931</v>
       </c>
       <c r="J8" t="str">
         <v>49</v>
@@ -742,13 +742,13 @@
         <v>987,288,717</v>
       </c>
       <c r="L8" t="str">
-        <v>9,596,985,519</v>
+        <v>9,923,636,312</v>
       </c>
       <c r="M8" t="str">
-        <v>3,000,958,606</v>
+        <v>3,098,953,339</v>
       </c>
       <c r="N8" t="str">
-        <v>31.27%</v>
+        <v>31.23%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>18,853</v>
+        <v>19,730</v>
       </c>
       <c r="F9" t="str">
-        <v>5,199</v>
+        <v>5,395</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>34,922,243,776</v>
+        <v>36,441,078,668</v>
       </c>
       <c r="M9" t="str">
-        <v>9,283,508,039</v>
+        <v>9,594,108,649</v>
       </c>
       <c r="N9" t="str">
-        <v>26.58%</v>
+        <v>26.33%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>1,978</v>
+        <v>2,056</v>
       </c>
       <c r="F10" t="str">
-        <v>932</v>
+        <v>965</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>664,042,905</v>
+        <v>690,059,135</v>
       </c>
       <c r="M10" t="str">
-        <v>283,919,693</v>
+        <v>293,366,321</v>
       </c>
       <c r="N10" t="str">
-        <v>42.76%</v>
+        <v>42.51%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,510</v>
+        <v>3,631</v>
       </c>
       <c r="F11" t="str">
-        <v>971</v>
+        <v>1,003</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>6,653,298,624</v>
+        <v>6,874,476,547</v>
       </c>
       <c r="M11" t="str">
-        <v>1,685,738,010</v>
+        <v>1,750,437,743</v>
       </c>
       <c r="N11" t="str">
-        <v>25.34%</v>
+        <v>25.46%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,718</v>
+        <v>2,873</v>
       </c>
       <c r="F12" t="str">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>5,152,176,167</v>
+        <v>5,444,869,816</v>
       </c>
       <c r="M12" t="str">
-        <v>1,401,323,790</v>
+        <v>1,457,645,633</v>
       </c>
       <c r="N12" t="str">
-        <v>27.20%</v>
+        <v>26.77%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>4,097</v>
+        <v>4,295</v>
       </c>
       <c r="F13" t="str">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G13" t="str">
-        <v>7,329</v>
+        <v>7,696</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>13,229,844,421</v>
+        <v>13,829,627,694</v>
       </c>
       <c r="M13" t="str">
-        <v>126,418,155</v>
+        <v>129,263,756</v>
       </c>
       <c r="N13" t="str">
-        <v>0.96%</v>
+        <v>0.93%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>11,497</v>
+        <v>12,053</v>
       </c>
       <c r="F14" t="str">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G14" t="str">
-        <v>25,652</v>
+        <v>26,653</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>36,327,403,243</v>
+        <v>38,008,836,773</v>
       </c>
       <c r="M14" t="str">
-        <v>403,936,215</v>
+        <v>410,499,218</v>
       </c>
       <c r="N14" t="str">
-        <v>1.11%</v>
+        <v>1.08%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>8,203</v>
+        <v>8,598</v>
       </c>
       <c r="F15" t="str">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G15" t="str">
-        <v>18,386</v>
+        <v>19,089</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>26,082,754,516</v>
+        <v>27,383,297,568</v>
       </c>
       <c r="M15" t="str">
-        <v>435,562,412</v>
+        <v>438,624,780</v>
       </c>
       <c r="N15" t="str">
-        <v>1.67%</v>
+        <v>1.60%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="F16" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>451,386,617</v>
+        <v>475,557,837</v>
       </c>
       <c r="M16" t="str">
-        <v>5,315,782</v>
+        <v>7,015,950</v>
       </c>
       <c r="N16" t="str">
-        <v>1.18%</v>
+        <v>1.48%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>14,953</v>
+        <v>15,563</v>
       </c>
       <c r="F17" t="str">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G17" t="str">
-        <v>67,145</v>
+        <v>69,428</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>59,775,861,020</v>
+        <v>62,015,351,931</v>
       </c>
       <c r="M17" t="str">
-        <v>306,303,288</v>
+        <v>313,757,678</v>
       </c>
       <c r="N17" t="str">
         <v>0.51%</v>
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,300</v>
+        <v>1,354</v>
       </c>
       <c r="F18" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="str">
-        <v>5,790</v>
+        <v>5,989</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>5,227,723,961</v>
+        <v>5,370,393,573</v>
       </c>
       <c r="M18" t="str">
-        <v>13,388,652</v>
+        <v>13,560,850</v>
       </c>
       <c r="N18" t="str">
-        <v>0.26%</v>
+        <v>0.25%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>5,850</v>
+        <v>6,087</v>
       </c>
       <c r="F19" t="str">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" t="str">
-        <v>25,190</v>
+        <v>26,103</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>23,662,688,303</v>
+        <v>24,531,692,118</v>
       </c>
       <c r="M19" t="str">
-        <v>139,067,204</v>
+        <v>140,896,165</v>
       </c>
       <c r="N19" t="str">
-        <v>0.59%</v>
+        <v>0.57%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,239</v>
+        <v>3,245</v>
       </c>
       <c r="F20" t="str">
         <v>54</v>
       </c>
       <c r="G20" t="str">
-        <v>19,336</v>
+        <v>20,150</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,7 +1270,7 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,942,076,845</v>
+        <v>11,946,323,298</v>
       </c>
       <c r="M20" t="str">
         <v>155,577,298</v>
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,916</v>
+        <v>2,926</v>
       </c>
       <c r="F21" t="str">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G21" t="str">
-        <v>125,327</v>
+        <v>130,547</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -1314,10 +1314,10 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,953,329,076</v>
+        <v>8,960,099,102</v>
       </c>
       <c r="M21" t="str">
-        <v>289,712,814</v>
+        <v>290,717,714</v>
       </c>
       <c r="N21" t="str">
         <v>3.24%</v>
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>12,165</v>
+        <v>12,478</v>
       </c>
       <c r="F22" t="str">
-        <v>1,061</v>
+        <v>1,092</v>
       </c>
       <c r="G22" t="str">
-        <v>482,133</v>
+        <v>502,739</v>
       </c>
       <c r="H22" t="str">
         <v>34</v>
@@ -1358,13 +1358,13 @@
         <v>135,738,710</v>
       </c>
       <c r="L22" t="str">
-        <v>58,947,518,734</v>
+        <v>60,300,497,299</v>
       </c>
       <c r="M22" t="str">
-        <v>1,833,711,001</v>
+        <v>1,911,392,751</v>
       </c>
       <c r="N22" t="str">
-        <v>3.11%</v>
+        <v>3.17%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,015</v>
+        <v>8,044</v>
       </c>
       <c r="F24" t="str">
         <v>196</v>
       </c>
       <c r="G24" t="str">
-        <v>64,522</v>
+        <v>67,210</v>
       </c>
       <c r="H24" t="str">
         <v>20</v>
@@ -1446,7 +1446,7 @@
         <v>184,925,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,431,035,270</v>
+        <v>52,455,371,758</v>
       </c>
       <c r="M24" t="str">
         <v>501,739,256</v>
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>28,936</v>
+        <v>30,342</v>
       </c>
       <c r="F26" t="str">
-        <v>9,374</v>
+        <v>9,774</v>
       </c>
       <c r="G26" t="str">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H26" t="str">
         <v>14</v>
@@ -1534,13 +1534,13 @@
         <v>163,965,708</v>
       </c>
       <c r="L26" t="str">
-        <v>63,249,656,723</v>
+        <v>66,181,059,596</v>
       </c>
       <c r="M26" t="str">
-        <v>22,233,251,643</v>
+        <v>23,146,711,182</v>
       </c>
       <c r="N26" t="str">
-        <v>35.15%</v>
+        <v>34.97%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>4,629</v>
+        <v>4,792</v>
       </c>
       <c r="F27" t="str">
-        <v>2,555</v>
+        <v>2,626</v>
       </c>
       <c r="G27" t="str">
-        <v>4,655</v>
+        <v>4,821</v>
       </c>
       <c r="H27" t="str">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="I27" t="str">
-        <v>8,771,769,949</v>
+        <v>9,043,094,259</v>
       </c>
       <c r="J27" t="str">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="K27" t="str">
-        <v>12,366,908,962</v>
+        <v>12,586,675,437</v>
       </c>
       <c r="L27" t="str">
-        <v>57,250,069,262</v>
+        <v>59,267,471,424</v>
       </c>
       <c r="M27" t="str">
-        <v>27,396,548,768</v>
+        <v>28,107,626,071</v>
       </c>
       <c r="N27" t="str">
-        <v>47.85%</v>
+        <v>47.43%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>4,384</v>
+        <v>4,567</v>
       </c>
       <c r="F28" t="str">
-        <v>2,216</v>
+        <v>2,292</v>
       </c>
       <c r="G28" t="str">
-        <v>4,303</v>
+        <v>4,502</v>
       </c>
       <c r="H28" t="str">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="I28" t="str">
-        <v>8,330,278,067</v>
+        <v>8,645,615,877</v>
       </c>
       <c r="J28" t="str">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="K28" t="str">
-        <v>10,741,105,763</v>
+        <v>11,150,880,939</v>
       </c>
       <c r="L28" t="str">
-        <v>54,043,925,943</v>
+        <v>56,341,800,504</v>
       </c>
       <c r="M28" t="str">
-        <v>24,727,967,710</v>
+        <v>25,609,901,609</v>
       </c>
       <c r="N28" t="str">
-        <v>45.76%</v>
+        <v>45.45%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,853</v>
+        <v>2,974</v>
       </c>
       <c r="F29" t="str">
-        <v>1,483</v>
+        <v>1,526</v>
       </c>
       <c r="G29" t="str">
-        <v>2,928</v>
+        <v>3,058</v>
       </c>
       <c r="H29" t="str">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="I29" t="str">
-        <v>5,569,484,456</v>
+        <v>5,754,907,517</v>
       </c>
       <c r="J29" t="str">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="K29" t="str">
-        <v>8,106,946,518</v>
+        <v>8,398,385,410</v>
       </c>
       <c r="L29" t="str">
-        <v>35,224,045,165</v>
+        <v>36,707,208,361</v>
       </c>
       <c r="M29" t="str">
-        <v>16,854,076,403</v>
+        <v>17,376,644,246</v>
       </c>
       <c r="N29" t="str">
-        <v>47.85%</v>
+        <v>47.34%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>30,155</v>
+        <v>31,510</v>
       </c>
       <c r="F30" t="str">
-        <v>10,028</v>
+        <v>10,423</v>
       </c>
       <c r="G30" t="str">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H30" t="str">
         <v>15</v>
@@ -1710,13 +1710,13 @@
         <v>207,254,874</v>
       </c>
       <c r="L30" t="str">
-        <v>65,688,992,243</v>
+        <v>68,541,003,385</v>
       </c>
       <c r="M30" t="str">
-        <v>24,059,543,850</v>
+        <v>24,924,818,539</v>
       </c>
       <c r="N30" t="str">
-        <v>36.63%</v>
+        <v>36.36%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,772</v>
+        <v>2,875</v>
       </c>
       <c r="F31" t="str">
-        <v>1,248</v>
+        <v>1,296</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,057,343,172</v>
+        <v>1,093,571,424</v>
       </c>
       <c r="M31" t="str">
-        <v>478,815,275</v>
+        <v>497,104,780</v>
       </c>
       <c r="N31" t="str">
-        <v>45.28%</v>
+        <v>45.46%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,847</v>
+        <v>1,923</v>
       </c>
       <c r="F32" t="str">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="G32" t="str">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,324,440,302</v>
+        <v>3,437,549,062</v>
       </c>
       <c r="M32" t="str">
-        <v>529,236,560</v>
+        <v>545,838,913</v>
       </c>
       <c r="N32" t="str">
-        <v>15.92%</v>
+        <v>15.88%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,312</v>
+        <v>2,409</v>
       </c>
       <c r="F33" t="str">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="G33" t="str">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>4,004,403,644</v>
+        <v>4,186,154,067</v>
       </c>
       <c r="M33" t="str">
-        <v>547,599,025</v>
+        <v>563,694,868</v>
       </c>
       <c r="N33" t="str">
-        <v>13.67%</v>
+        <v>13.47%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>9,551</v>
+        <v>10,016</v>
       </c>
       <c r="F34" t="str">
-        <v>1,545</v>
+        <v>1,609</v>
       </c>
       <c r="G34" t="str">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>17,849,515,111</v>
+        <v>18,620,871,989</v>
       </c>
       <c r="M34" t="str">
-        <v>2,437,306,300</v>
+        <v>2,536,502,583</v>
       </c>
       <c r="N34" t="str">
-        <v>13.65%</v>
+        <v>13.62%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>1,988</v>
+        <v>2,048</v>
       </c>
       <c r="F35" t="str">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="G35" t="str">
-        <v>6,201</v>
+        <v>6,436</v>
       </c>
       <c r="H35" t="str">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I35" t="str">
-        <v>1,336,640,339</v>
+        <v>1,446,274,586</v>
       </c>
       <c r="J35" t="str">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K35" t="str">
-        <v>1,118,099,906</v>
+        <v>1,136,914,926</v>
       </c>
       <c r="L35" t="str">
-        <v>21,784,620,169</v>
+        <v>22,461,515,450</v>
       </c>
       <c r="M35" t="str">
-        <v>3,515,397,342</v>
+        <v>3,638,957,669</v>
       </c>
       <c r="N35" t="str">
-        <v>16.14%</v>
+        <v>16.20%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,31 +1953,31 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,605</v>
+        <v>1,668</v>
       </c>
       <c r="F36" t="str">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="G36" t="str">
-        <v>4,378</v>
+        <v>4,601</v>
       </c>
       <c r="H36" t="str">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I36" t="str">
-        <v>826,679,704</v>
+        <v>866,082,561</v>
       </c>
       <c r="J36" t="str">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K36" t="str">
-        <v>836,314,099</v>
+        <v>881,423,534</v>
       </c>
       <c r="L36" t="str">
-        <v>17,492,959,431</v>
+        <v>18,165,909,062</v>
       </c>
       <c r="M36" t="str">
-        <v>2,537,466,069</v>
+        <v>2,635,277,895</v>
       </c>
       <c r="N36" t="str">
         <v>14.51%</v>
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>8,827</v>
+        <v>9,190</v>
       </c>
       <c r="F37" t="str">
-        <v>1,384</v>
+        <v>1,433</v>
       </c>
       <c r="G37" t="str">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>15,919,003,184</v>
+        <v>16,539,212,515</v>
       </c>
       <c r="M37" t="str">
-        <v>2,701,800,734</v>
+        <v>2,772,954,091</v>
       </c>
       <c r="N37" t="str">
-        <v>16.97%</v>
+        <v>16.77%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>994</v>
+        <v>1,038</v>
       </c>
       <c r="F38" t="str">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>437,749,149</v>
+        <v>452,296,438</v>
       </c>
       <c r="M38" t="str">
-        <v>96,005,647</v>
+        <v>101,448,900</v>
       </c>
       <c r="N38" t="str">
-        <v>21.93%</v>
+        <v>22.43%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,10 +2085,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,948</v>
+        <v>3,067</v>
       </c>
       <c r="F39" t="str">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="G39" t="str">
         <v>74</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>5,366,291,236</v>
+        <v>5,553,520,009</v>
       </c>
       <c r="M39" t="str">
-        <v>740,629,098</v>
+        <v>747,323,355</v>
       </c>
       <c r="N39" t="str">
-        <v>13.80%</v>
+        <v>13.46%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,581</v>
+        <v>2,686</v>
       </c>
       <c r="F41" t="str">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>4,659,248,197</v>
+        <v>4,845,173,141</v>
       </c>
       <c r="M41" t="str">
-        <v>671,616,379</v>
+        <v>693,021,236</v>
       </c>
       <c r="N41" t="str">
-        <v>14.41%</v>
+        <v>14.30%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,798</v>
+        <v>2,874</v>
       </c>
       <c r="F42" t="str">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="G42" t="str">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>5,251,242,057</v>
+        <v>5,380,824,556</v>
       </c>
       <c r="M42" t="str">
-        <v>726,755,379</v>
+        <v>747,773,237</v>
       </c>
       <c r="N42" t="str">
-        <v>13.84%</v>
+        <v>13.90%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>8,237</v>
+        <v>8,565</v>
       </c>
       <c r="F43" t="str">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="G43" t="str">
-        <v>10,733</v>
+        <v>11,122</v>
       </c>
       <c r="H43" t="str">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>22,924,171,503</v>
+        <v>23,939,304,126</v>
       </c>
       <c r="M43" t="str">
-        <v>772,419,558</v>
+        <v>774,942,740</v>
       </c>
       <c r="N43" t="str">
-        <v>3.37%</v>
+        <v>3.24%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,19 +2305,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>11,134</v>
+        <v>11,629</v>
       </c>
       <c r="F44" t="str">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="G44" t="str">
-        <v>15,034</v>
+        <v>15,630</v>
       </c>
       <c r="H44" t="str">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I44" t="str">
-        <v>232,461,030</v>
+        <v>246,187,987</v>
       </c>
       <c r="J44" t="str">
         <v>13</v>
@@ -2326,13 +2326,13 @@
         <v>243,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>31,797,128,778</v>
+        <v>33,070,657,228</v>
       </c>
       <c r="M44" t="str">
-        <v>1,376,977,414</v>
+        <v>1,410,377,666</v>
       </c>
       <c r="N44" t="str">
-        <v>4.33%</v>
+        <v>4.26%</v>
       </c>
     </row>
     <row r="45">
@@ -2355,7 +2355,7 @@
         <v>23</v>
       </c>
       <c r="G45" t="str">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>7,354</v>
+        <v>7,716</v>
       </c>
       <c r="F46" t="str">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G46" t="str">
-        <v>8,862</v>
+        <v>9,235</v>
       </c>
       <c r="H46" t="str">
         <v>17</v>
@@ -2414,13 +2414,13 @@
         <v>124,130,356</v>
       </c>
       <c r="L46" t="str">
-        <v>20,690,645,439</v>
+        <v>21,864,887,782</v>
       </c>
       <c r="M46" t="str">
-        <v>967,265,697</v>
+        <v>990,590,205</v>
       </c>
       <c r="N46" t="str">
-        <v>4.67%</v>
+        <v>4.53%</v>
       </c>
     </row>
     <row r="47">
@@ -2440,10 +2440,10 @@
         <v>641</v>
       </c>
       <c r="F47" t="str">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G47" t="str">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         <v>347,174,063</v>
       </c>
       <c r="M47" t="str">
-        <v>41,156,408</v>
+        <v>42,437,954</v>
       </c>
       <c r="N47" t="str">
-        <v>11.85%</v>
+        <v>12.22%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,13 +457,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>5,080</v>
+        <v>5,297</v>
       </c>
       <c r="F2" t="str">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G2" t="str">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="H2" t="str">
         <v>27</v>
@@ -478,13 +478,13 @@
         <v>140,563,756</v>
       </c>
       <c r="L2" t="str">
-        <v>22,205,644,407</v>
+        <v>23,115,602,874</v>
       </c>
       <c r="M2" t="str">
-        <v>1,188,784,807</v>
+        <v>1,241,018,440</v>
       </c>
       <c r="N2" t="str">
-        <v>5.35%</v>
+        <v>5.37%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,190</v>
+        <v>3,334</v>
       </c>
       <c r="F3" t="str">
-        <v>864</v>
+        <v>905</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>5,914,724,076</v>
+        <v>6,190,409,963</v>
       </c>
       <c r="M3" t="str">
-        <v>1,516,801,523</v>
+        <v>1,576,866,340</v>
       </c>
       <c r="N3" t="str">
-        <v>25.64%</v>
+        <v>25.47%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>12,779</v>
+        <v>13,489</v>
       </c>
       <c r="F4" t="str">
-        <v>3,652</v>
+        <v>3,868</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>23,809,151,735</v>
+        <v>25,134,103,165</v>
       </c>
       <c r="M4" t="str">
-        <v>6,556,975,307</v>
+        <v>6,986,644,445</v>
       </c>
       <c r="N4" t="str">
-        <v>27.54%</v>
+        <v>27.80%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,357</v>
+        <v>1,425</v>
       </c>
       <c r="F5" t="str">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="G5" t="str">
-        <v>811</v>
+        <v>850</v>
       </c>
       <c r="H5" t="str">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I5" t="str">
-        <v>1,946,796,942</v>
+        <v>2,063,003,582</v>
       </c>
       <c r="J5" t="str">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K5" t="str">
-        <v>1,977,704,687</v>
+        <v>2,062,977,184</v>
       </c>
       <c r="L5" t="str">
-        <v>16,050,183,013</v>
+        <v>16,860,871,783</v>
       </c>
       <c r="M5" t="str">
-        <v>5,575,013,648</v>
+        <v>5,879,556,418</v>
       </c>
       <c r="N5" t="str">
-        <v>34.73%</v>
+        <v>34.87%</v>
       </c>
     </row>
     <row r="6">
@@ -633,31 +633,31 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,848</v>
+        <v>1,931</v>
       </c>
       <c r="F6" t="str">
-        <v>725</v>
+        <v>761</v>
       </c>
       <c r="G6" t="str">
-        <v>1,056</v>
+        <v>1,113</v>
       </c>
       <c r="H6" t="str">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="I6" t="str">
-        <v>2,523,668,607</v>
+        <v>2,606,727,233</v>
       </c>
       <c r="J6" t="str">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K6" t="str">
-        <v>2,044,482,843</v>
+        <v>2,157,451,939</v>
       </c>
       <c r="L6" t="str">
-        <v>21,695,497,981</v>
+        <v>22,734,761,161</v>
       </c>
       <c r="M6" t="str">
-        <v>6,995,114,341</v>
+        <v>7,328,933,275</v>
       </c>
       <c r="N6" t="str">
         <v>32.24%</v>
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,662</v>
+        <v>1,729</v>
       </c>
       <c r="F7" t="str">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="G7" t="str">
-        <v>974</v>
+        <v>1,014</v>
       </c>
       <c r="H7" t="str">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="I7" t="str">
-        <v>2,364,678,653</v>
+        <v>2,528,097,680</v>
       </c>
       <c r="J7" t="str">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K7" t="str">
-        <v>1,769,765,861</v>
+        <v>1,896,374,267</v>
       </c>
       <c r="L7" t="str">
-        <v>19,562,698,730</v>
+        <v>20,382,794,880</v>
       </c>
       <c r="M7" t="str">
-        <v>6,267,292,216</v>
+        <v>6,594,047,528</v>
       </c>
       <c r="N7" t="str">
-        <v>32.04%</v>
+        <v>32.35%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>832</v>
+        <v>865</v>
       </c>
       <c r="F8" t="str">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="G8" t="str">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="H8" t="str">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I8" t="str">
-        <v>1,011,129,931</v>
+        <v>1,062,286,251</v>
       </c>
       <c r="J8" t="str">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" t="str">
-        <v>987,288,717</v>
+        <v>1,026,477,302</v>
       </c>
       <c r="L8" t="str">
-        <v>9,923,636,312</v>
+        <v>10,330,587,489</v>
       </c>
       <c r="M8" t="str">
-        <v>3,098,953,339</v>
+        <v>3,224,734,512</v>
       </c>
       <c r="N8" t="str">
-        <v>31.23%</v>
+        <v>31.22%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>19,730</v>
+        <v>20,630</v>
       </c>
       <c r="F9" t="str">
-        <v>5,395</v>
+        <v>5,662</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>36,441,078,668</v>
+        <v>38,090,266,619</v>
       </c>
       <c r="M9" t="str">
-        <v>9,594,108,649</v>
+        <v>10,055,326,881</v>
       </c>
       <c r="N9" t="str">
-        <v>26.33%</v>
+        <v>26.40%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,056</v>
+        <v>2,120</v>
       </c>
       <c r="F10" t="str">
-        <v>965</v>
+        <v>993</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>690,059,135</v>
+        <v>714,830,871</v>
       </c>
       <c r="M10" t="str">
-        <v>293,366,321</v>
+        <v>302,842,918</v>
       </c>
       <c r="N10" t="str">
-        <v>42.51%</v>
+        <v>42.37%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,631</v>
+        <v>3,762</v>
       </c>
       <c r="F11" t="str">
-        <v>1,003</v>
+        <v>1,048</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>6,874,476,547</v>
+        <v>7,099,669,120</v>
       </c>
       <c r="M11" t="str">
-        <v>1,750,437,743</v>
+        <v>1,837,480,766</v>
       </c>
       <c r="N11" t="str">
-        <v>25.46%</v>
+        <v>25.88%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>2,873</v>
+        <v>3,042</v>
       </c>
       <c r="F12" t="str">
-        <v>829</v>
+        <v>882</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>5,444,869,816</v>
+        <v>5,749,925,677</v>
       </c>
       <c r="M12" t="str">
-        <v>1,457,645,633</v>
+        <v>1,554,717,262</v>
       </c>
       <c r="N12" t="str">
-        <v>26.77%</v>
+        <v>27.04%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>4,295</v>
+        <v>4,448</v>
       </c>
       <c r="F13" t="str">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G13" t="str">
-        <v>7,696</v>
+        <v>8,069</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>13,829,627,694</v>
+        <v>14,398,674,682</v>
       </c>
       <c r="M13" t="str">
-        <v>129,263,756</v>
+        <v>146,107,543</v>
       </c>
       <c r="N13" t="str">
-        <v>0.93%</v>
+        <v>1.01%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>12,053</v>
+        <v>12,484</v>
       </c>
       <c r="F14" t="str">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G14" t="str">
-        <v>26,653</v>
+        <v>27,653</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>35,490,060</v>
       </c>
       <c r="L14" t="str">
-        <v>38,008,836,773</v>
+        <v>39,356,090,651</v>
       </c>
       <c r="M14" t="str">
-        <v>410,499,218</v>
+        <v>428,422,157</v>
       </c>
       <c r="N14" t="str">
-        <v>1.08%</v>
+        <v>1.09%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>8,598</v>
+        <v>8,908</v>
       </c>
       <c r="F15" t="str">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G15" t="str">
-        <v>19,089</v>
+        <v>19,777</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,13 +1050,13 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>27,383,297,568</v>
+        <v>28,244,702,223</v>
       </c>
       <c r="M15" t="str">
-        <v>438,624,780</v>
+        <v>450,383,183</v>
       </c>
       <c r="N15" t="str">
-        <v>1.60%</v>
+        <v>1.59%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="F16" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>475,557,837</v>
+        <v>497,841,731</v>
       </c>
       <c r="M16" t="str">
-        <v>7,015,950</v>
+        <v>7,264,691</v>
       </c>
       <c r="N16" t="str">
-        <v>1.48%</v>
+        <v>1.46%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>15,563</v>
+        <v>16,210</v>
       </c>
       <c r="F17" t="str">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="G17" t="str">
-        <v>69,428</v>
+        <v>71,700</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>62,015,351,931</v>
+        <v>64,283,439,064</v>
       </c>
       <c r="M17" t="str">
-        <v>313,757,678</v>
+        <v>327,114,880</v>
       </c>
       <c r="N17" t="str">
         <v>0.51%</v>
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,354</v>
+        <v>1,410</v>
       </c>
       <c r="F18" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="str">
-        <v>5,989</v>
+        <v>6,190</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>5,370,393,573</v>
+        <v>5,532,831,507</v>
       </c>
       <c r="M18" t="str">
-        <v>13,560,850</v>
+        <v>15,361,311</v>
       </c>
       <c r="N18" t="str">
-        <v>0.25%</v>
+        <v>0.28%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>6,087</v>
+        <v>6,340</v>
       </c>
       <c r="F19" t="str">
         <v>58</v>
       </c>
       <c r="G19" t="str">
-        <v>26,103</v>
+        <v>27,023</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>24,531,692,118</v>
+        <v>25,690,554,851</v>
       </c>
       <c r="M19" t="str">
         <v>140,896,165</v>
       </c>
       <c r="N19" t="str">
-        <v>0.57%</v>
+        <v>0.55%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,245</v>
+        <v>3,261</v>
       </c>
       <c r="F20" t="str">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G20" t="str">
-        <v>20,150</v>
+        <v>20,964</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,946,323,298</v>
+        <v>11,957,195,039</v>
       </c>
       <c r="M20" t="str">
-        <v>155,577,298</v>
+        <v>161,058,033</v>
       </c>
       <c r="N20" t="str">
-        <v>1.30%</v>
+        <v>1.35%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,19 +1293,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,926</v>
+        <v>2,947</v>
       </c>
       <c r="F21" t="str">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G21" t="str">
-        <v>130,547</v>
+        <v>135,771</v>
       </c>
       <c r="H21" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" t="str">
-        <v>0</v>
+        <v>50,855,480</v>
       </c>
       <c r="J21" t="str">
         <v>18</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>8,960,099,102</v>
+        <v>9,021,772,145</v>
       </c>
       <c r="M21" t="str">
-        <v>290,717,714</v>
+        <v>322,702,647</v>
       </c>
       <c r="N21" t="str">
-        <v>3.24%</v>
+        <v>3.58%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,34 +1337,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>12,478</v>
+        <v>12,758</v>
       </c>
       <c r="F22" t="str">
-        <v>1,092</v>
+        <v>1,195</v>
       </c>
       <c r="G22" t="str">
-        <v>502,739</v>
+        <v>523,367</v>
       </c>
       <c r="H22" t="str">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I22" t="str">
-        <v>422,986,680</v>
+        <v>513,083,920</v>
       </c>
       <c r="J22" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" t="str">
-        <v>135,738,710</v>
+        <v>167,076,150</v>
       </c>
       <c r="L22" t="str">
-        <v>60,300,497,299</v>
+        <v>61,462,555,894</v>
       </c>
       <c r="M22" t="str">
-        <v>1,911,392,751</v>
+        <v>2,153,764,360</v>
       </c>
       <c r="N22" t="str">
-        <v>3.17%</v>
+        <v>3.50%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,044</v>
+        <v>8,062</v>
       </c>
       <c r="F24" t="str">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="G24" t="str">
-        <v>67,210</v>
+        <v>69,898</v>
       </c>
       <c r="H24" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I24" t="str">
-        <v>240,826,900</v>
+        <v>282,826,900</v>
       </c>
       <c r="J24" t="str">
         <v>10</v>
@@ -1446,13 +1446,13 @@
         <v>184,925,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,455,371,758</v>
+        <v>52,470,386,290</v>
       </c>
       <c r="M24" t="str">
-        <v>501,739,256</v>
+        <v>565,968,518</v>
       </c>
       <c r="N24" t="str">
-        <v>0.96%</v>
+        <v>1.08%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>30,342</v>
+        <v>31,807</v>
       </c>
       <c r="F26" t="str">
-        <v>9,774</v>
+        <v>10,250</v>
       </c>
       <c r="G26" t="str">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H26" t="str">
         <v>14</v>
@@ -1534,13 +1534,13 @@
         <v>163,965,708</v>
       </c>
       <c r="L26" t="str">
-        <v>66,181,059,596</v>
+        <v>69,215,188,735</v>
       </c>
       <c r="M26" t="str">
-        <v>23,146,711,182</v>
+        <v>24,188,875,226</v>
       </c>
       <c r="N26" t="str">
-        <v>34.97%</v>
+        <v>34.95%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>4,792</v>
+        <v>4,952</v>
       </c>
       <c r="F27" t="str">
-        <v>2,626</v>
+        <v>2,701</v>
       </c>
       <c r="G27" t="str">
-        <v>4,821</v>
+        <v>4,989</v>
       </c>
       <c r="H27" t="str">
-        <v>728</v>
+        <v>747</v>
       </c>
       <c r="I27" t="str">
-        <v>9,043,094,259</v>
+        <v>9,275,216,649</v>
       </c>
       <c r="J27" t="str">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="K27" t="str">
-        <v>12,586,675,437</v>
+        <v>13,031,154,751</v>
       </c>
       <c r="L27" t="str">
-        <v>59,267,471,424</v>
+        <v>61,342,047,604</v>
       </c>
       <c r="M27" t="str">
-        <v>28,107,626,071</v>
+        <v>28,965,407,391</v>
       </c>
       <c r="N27" t="str">
-        <v>47.43%</v>
+        <v>47.22%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>4,567</v>
+        <v>4,728</v>
       </c>
       <c r="F28" t="str">
-        <v>2,292</v>
+        <v>2,392</v>
       </c>
       <c r="G28" t="str">
-        <v>4,502</v>
+        <v>4,691</v>
       </c>
       <c r="H28" t="str">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="I28" t="str">
-        <v>8,645,615,877</v>
+        <v>9,132,083,354</v>
       </c>
       <c r="J28" t="str">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="K28" t="str">
-        <v>11,150,880,939</v>
+        <v>11,564,073,286</v>
       </c>
       <c r="L28" t="str">
-        <v>56,341,800,504</v>
+        <v>58,406,542,116</v>
       </c>
       <c r="M28" t="str">
-        <v>25,609,901,609</v>
+        <v>26,746,938,773</v>
       </c>
       <c r="N28" t="str">
-        <v>45.45%</v>
+        <v>45.79%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,974</v>
+        <v>3,070</v>
       </c>
       <c r="F29" t="str">
-        <v>1,526</v>
+        <v>1,593</v>
       </c>
       <c r="G29" t="str">
-        <v>3,058</v>
+        <v>3,175</v>
       </c>
       <c r="H29" t="str">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="I29" t="str">
-        <v>5,754,907,517</v>
+        <v>6,031,326,869</v>
       </c>
       <c r="J29" t="str">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="K29" t="str">
-        <v>8,398,385,410</v>
+        <v>8,803,399,969</v>
       </c>
       <c r="L29" t="str">
-        <v>36,707,208,361</v>
+        <v>37,956,766,795</v>
       </c>
       <c r="M29" t="str">
-        <v>17,376,644,246</v>
+        <v>18,168,198,910</v>
       </c>
       <c r="N29" t="str">
-        <v>47.34%</v>
+        <v>47.87%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>31,510</v>
+        <v>32,862</v>
       </c>
       <c r="F30" t="str">
-        <v>10,423</v>
+        <v>10,862</v>
       </c>
       <c r="G30" t="str">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H30" t="str">
         <v>15</v>
@@ -1710,13 +1710,13 @@
         <v>207,254,874</v>
       </c>
       <c r="L30" t="str">
-        <v>68,541,003,385</v>
+        <v>71,356,683,408</v>
       </c>
       <c r="M30" t="str">
-        <v>24,924,818,539</v>
+        <v>25,967,175,393</v>
       </c>
       <c r="N30" t="str">
-        <v>36.36%</v>
+        <v>36.39%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,875</v>
+        <v>2,996</v>
       </c>
       <c r="F31" t="str">
-        <v>1,296</v>
+        <v>1,347</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,093,571,424</v>
+        <v>1,142,730,948</v>
       </c>
       <c r="M31" t="str">
-        <v>497,104,780</v>
+        <v>515,922,553</v>
       </c>
       <c r="N31" t="str">
-        <v>45.46%</v>
+        <v>45.15%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>1,923</v>
+        <v>2,006</v>
       </c>
       <c r="F32" t="str">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="G32" t="str">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,437,549,062</v>
+        <v>3,582,166,102</v>
       </c>
       <c r="M32" t="str">
-        <v>545,838,913</v>
+        <v>569,960,204</v>
       </c>
       <c r="N32" t="str">
-        <v>15.88%</v>
+        <v>15.91%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,409</v>
+        <v>2,510</v>
       </c>
       <c r="F33" t="str">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="G33" t="str">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>4,186,154,067</v>
+        <v>4,352,961,946</v>
       </c>
       <c r="M33" t="str">
-        <v>563,694,868</v>
+        <v>595,302,526</v>
       </c>
       <c r="N33" t="str">
-        <v>13.47%</v>
+        <v>13.68%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>10,016</v>
+        <v>10,500</v>
       </c>
       <c r="F34" t="str">
-        <v>1,609</v>
+        <v>1,705</v>
       </c>
       <c r="G34" t="str">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>18,620,871,989</v>
+        <v>19,498,655,138</v>
       </c>
       <c r="M34" t="str">
-        <v>2,536,502,583</v>
+        <v>2,682,189,428</v>
       </c>
       <c r="N34" t="str">
-        <v>13.62%</v>
+        <v>13.76%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>2,048</v>
+        <v>2,108</v>
       </c>
       <c r="F35" t="str">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="G35" t="str">
-        <v>6,436</v>
+        <v>6,663</v>
       </c>
       <c r="H35" t="str">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I35" t="str">
-        <v>1,446,274,586</v>
+        <v>1,486,466,298</v>
       </c>
       <c r="J35" t="str">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K35" t="str">
-        <v>1,136,914,926</v>
+        <v>1,249,812,619</v>
       </c>
       <c r="L35" t="str">
-        <v>22,461,515,450</v>
+        <v>23,167,673,405</v>
       </c>
       <c r="M35" t="str">
-        <v>3,638,957,669</v>
+        <v>3,835,168,127</v>
       </c>
       <c r="N35" t="str">
-        <v>16.20%</v>
+        <v>16.55%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,34 +1953,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,668</v>
+        <v>1,730</v>
       </c>
       <c r="F36" t="str">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="G36" t="str">
-        <v>4,601</v>
+        <v>4,830</v>
       </c>
       <c r="H36" t="str">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I36" t="str">
-        <v>866,082,561</v>
+        <v>917,043,359</v>
       </c>
       <c r="J36" t="str">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K36" t="str">
-        <v>881,423,534</v>
+        <v>973,850,339</v>
       </c>
       <c r="L36" t="str">
-        <v>18,165,909,062</v>
+        <v>18,858,190,266</v>
       </c>
       <c r="M36" t="str">
-        <v>2,635,277,895</v>
+        <v>2,872,880,064</v>
       </c>
       <c r="N36" t="str">
-        <v>14.51%</v>
+        <v>15.23%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>9,190</v>
+        <v>9,592</v>
       </c>
       <c r="F37" t="str">
-        <v>1,433</v>
+        <v>1,509</v>
       </c>
       <c r="G37" t="str">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>16,539,212,515</v>
+        <v>17,249,874,228</v>
       </c>
       <c r="M37" t="str">
-        <v>2,772,954,091</v>
+        <v>2,921,747,088</v>
       </c>
       <c r="N37" t="str">
-        <v>16.77%</v>
+        <v>16.94%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,038</v>
+        <v>1,080</v>
       </c>
       <c r="F38" t="str">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>452,296,438</v>
+        <v>469,774,006</v>
       </c>
       <c r="M38" t="str">
-        <v>101,448,900</v>
+        <v>104,189,685</v>
       </c>
       <c r="N38" t="str">
-        <v>22.43%</v>
+        <v>22.18%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,10 +2085,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,067</v>
+        <v>3,187</v>
       </c>
       <c r="F39" t="str">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="G39" t="str">
         <v>74</v>
@@ -2106,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>5,553,520,009</v>
+        <v>5,765,298,976</v>
       </c>
       <c r="M39" t="str">
-        <v>747,323,355</v>
+        <v>776,181,227</v>
       </c>
       <c r="N39" t="str">
         <v>13.46%</v>
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,686</v>
+        <v>2,852</v>
       </c>
       <c r="F41" t="str">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>4,845,173,141</v>
+        <v>5,135,243,021</v>
       </c>
       <c r="M41" t="str">
-        <v>693,021,236</v>
+        <v>733,428,182</v>
       </c>
       <c r="N41" t="str">
-        <v>14.30%</v>
+        <v>14.28%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,874</v>
+        <v>2,998</v>
       </c>
       <c r="F42" t="str">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="G42" t="str">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>5,380,824,556</v>
+        <v>5,586,057,719</v>
       </c>
       <c r="M42" t="str">
-        <v>747,773,237</v>
+        <v>784,560,701</v>
       </c>
       <c r="N42" t="str">
-        <v>13.90%</v>
+        <v>14.04%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>8,565</v>
+        <v>8,828</v>
       </c>
       <c r="F43" t="str">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="G43" t="str">
-        <v>11,122</v>
+        <v>11,504</v>
       </c>
       <c r="H43" t="str">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>23,939,304,126</v>
+        <v>24,590,036,230</v>
       </c>
       <c r="M43" t="str">
-        <v>774,942,740</v>
+        <v>795,447,434</v>
       </c>
       <c r="N43" t="str">
-        <v>3.24%</v>
+        <v>3.23%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>11,629</v>
+        <v>12,024</v>
       </c>
       <c r="F44" t="str">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="G44" t="str">
-        <v>15,630</v>
+        <v>16,214</v>
       </c>
       <c r="H44" t="str">
         <v>21</v>
@@ -2326,13 +2326,13 @@
         <v>243,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>33,070,657,228</v>
+        <v>33,980,298,344</v>
       </c>
       <c r="M44" t="str">
-        <v>1,410,377,666</v>
+        <v>1,468,038,969</v>
       </c>
       <c r="N44" t="str">
-        <v>4.26%</v>
+        <v>4.32%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>494</v>
+        <v>659</v>
       </c>
       <c r="F45" t="str">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G45" t="str">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>1,685,800,789</v>
+        <v>2,387,803,452</v>
       </c>
       <c r="M45" t="str">
-        <v>69,913,162</v>
+        <v>79,977,923</v>
       </c>
       <c r="N45" t="str">
-        <v>4.15%</v>
+        <v>3.35%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>7,716</v>
+        <v>8,004</v>
       </c>
       <c r="F46" t="str">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="G46" t="str">
-        <v>9,235</v>
+        <v>9,610</v>
       </c>
       <c r="H46" t="str">
         <v>17</v>
@@ -2408,19 +2408,19 @@
         <v>210,093,634</v>
       </c>
       <c r="J46" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K46" t="str">
-        <v>124,130,356</v>
+        <v>142,152,166</v>
       </c>
       <c r="L46" t="str">
-        <v>21,864,887,782</v>
+        <v>22,561,996,240</v>
       </c>
       <c r="M46" t="str">
-        <v>990,590,205</v>
+        <v>1,047,500,223</v>
       </c>
       <c r="N46" t="str">
-        <v>4.53%</v>
+        <v>4.64%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>641</v>
+        <v>704</v>
       </c>
       <c r="F47" t="str">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G47" t="str">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>347,174,063</v>
+        <v>370,848,214</v>
       </c>
       <c r="M47" t="str">
-        <v>42,437,954</v>
+        <v>43,090,419</v>
       </c>
       <c r="N47" t="str">
-        <v>12.22%</v>
+        <v>11.62%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,19 +457,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>5,297</v>
+        <v>5,498</v>
       </c>
       <c r="F2" t="str">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="G2" t="str">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="H2" t="str">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" t="str">
-        <v>325,083,458</v>
+        <v>348,366,698</v>
       </c>
       <c r="J2" t="str">
         <v>7</v>
@@ -478,13 +478,13 @@
         <v>140,563,756</v>
       </c>
       <c r="L2" t="str">
-        <v>23,115,602,874</v>
+        <v>23,991,647,531</v>
       </c>
       <c r="M2" t="str">
-        <v>1,241,018,440</v>
+        <v>1,321,457,513</v>
       </c>
       <c r="N2" t="str">
-        <v>5.37%</v>
+        <v>5.51%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,334</v>
+        <v>3,489</v>
       </c>
       <c r="F3" t="str">
-        <v>905</v>
+        <v>939</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>6,190,409,963</v>
+        <v>6,487,458,987</v>
       </c>
       <c r="M3" t="str">
-        <v>1,576,866,340</v>
+        <v>1,638,418,104</v>
       </c>
       <c r="N3" t="str">
-        <v>25.47%</v>
+        <v>25.26%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>13,489</v>
+        <v>14,107</v>
       </c>
       <c r="F4" t="str">
-        <v>3,868</v>
+        <v>4,038</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>25,134,103,165</v>
+        <v>26,161,322,404</v>
       </c>
       <c r="M4" t="str">
-        <v>6,986,644,445</v>
+        <v>7,224,640,129</v>
       </c>
       <c r="N4" t="str">
-        <v>27.80%</v>
+        <v>27.62%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,425</v>
+        <v>1,481</v>
       </c>
       <c r="F5" t="str">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="G5" t="str">
-        <v>850</v>
+        <v>884</v>
       </c>
       <c r="H5" t="str">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I5" t="str">
-        <v>2,063,003,582</v>
+        <v>2,144,351,587</v>
       </c>
       <c r="J5" t="str">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K5" t="str">
-        <v>2,062,977,184</v>
+        <v>2,103,131,816</v>
       </c>
       <c r="L5" t="str">
-        <v>16,860,871,783</v>
+        <v>17,552,192,346</v>
       </c>
       <c r="M5" t="str">
-        <v>5,879,556,418</v>
+        <v>6,145,575,598</v>
       </c>
       <c r="N5" t="str">
-        <v>34.87%</v>
+        <v>35.01%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>1,931</v>
+        <v>2,001</v>
       </c>
       <c r="F6" t="str">
-        <v>761</v>
+        <v>796</v>
       </c>
       <c r="G6" t="str">
-        <v>1,113</v>
+        <v>1,158</v>
       </c>
       <c r="H6" t="str">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I6" t="str">
-        <v>2,606,727,233</v>
+        <v>2,658,137,365</v>
       </c>
       <c r="J6" t="str">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K6" t="str">
-        <v>2,157,451,939</v>
+        <v>2,221,044,016</v>
       </c>
       <c r="L6" t="str">
-        <v>22,734,761,161</v>
+        <v>23,590,357,296</v>
       </c>
       <c r="M6" t="str">
-        <v>7,328,933,275</v>
+        <v>7,616,709,399</v>
       </c>
       <c r="N6" t="str">
-        <v>32.24%</v>
+        <v>32.29%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,729</v>
+        <v>1,785</v>
       </c>
       <c r="F7" t="str">
-        <v>678</v>
+        <v>701</v>
       </c>
       <c r="G7" t="str">
-        <v>1,014</v>
+        <v>1,048</v>
       </c>
       <c r="H7" t="str">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I7" t="str">
-        <v>2,528,097,680</v>
+        <v>2,581,196,029</v>
       </c>
       <c r="J7" t="str">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K7" t="str">
-        <v>1,896,374,267</v>
+        <v>1,955,887,812</v>
       </c>
       <c r="L7" t="str">
-        <v>20,382,794,880</v>
+        <v>21,047,327,489</v>
       </c>
       <c r="M7" t="str">
-        <v>6,594,047,528</v>
+        <v>6,795,835,399</v>
       </c>
       <c r="N7" t="str">
-        <v>32.35%</v>
+        <v>32.29%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>865</v>
+        <v>893</v>
       </c>
       <c r="F8" t="str">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="G8" t="str">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="H8" t="str">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I8" t="str">
-        <v>1,062,286,251</v>
+        <v>1,089,044,165</v>
       </c>
       <c r="J8" t="str">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K8" t="str">
-        <v>1,026,477,302</v>
+        <v>1,048,711,529</v>
       </c>
       <c r="L8" t="str">
-        <v>10,330,587,489</v>
+        <v>10,686,144,229</v>
       </c>
       <c r="M8" t="str">
-        <v>3,224,734,512</v>
+        <v>3,335,526,265</v>
       </c>
       <c r="N8" t="str">
-        <v>31.22%</v>
+        <v>31.21%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>20,630</v>
+        <v>21,546</v>
       </c>
       <c r="F9" t="str">
-        <v>5,662</v>
+        <v>5,905</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>38,090,266,619</v>
+        <v>39,716,032,504</v>
       </c>
       <c r="M9" t="str">
-        <v>10,055,326,881</v>
+        <v>10,471,688,493</v>
       </c>
       <c r="N9" t="str">
-        <v>26.40%</v>
+        <v>26.37%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,120</v>
+        <v>2,199</v>
       </c>
       <c r="F10" t="str">
-        <v>993</v>
+        <v>1,040</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>714,830,871</v>
+        <v>740,551,754</v>
       </c>
       <c r="M10" t="str">
-        <v>302,842,918</v>
+        <v>315,852,248</v>
       </c>
       <c r="N10" t="str">
-        <v>42.37%</v>
+        <v>42.65%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,762</v>
+        <v>3,926</v>
       </c>
       <c r="F11" t="str">
-        <v>1,048</v>
+        <v>1,088</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>7,099,669,120</v>
+        <v>7,404,771,481</v>
       </c>
       <c r="M11" t="str">
-        <v>1,837,480,766</v>
+        <v>1,893,897,271</v>
       </c>
       <c r="N11" t="str">
-        <v>25.88%</v>
+        <v>25.58%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,042</v>
+        <v>3,144</v>
       </c>
       <c r="F12" t="str">
-        <v>882</v>
+        <v>907</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>5,749,925,677</v>
+        <v>5,896,683,446</v>
       </c>
       <c r="M12" t="str">
-        <v>1,554,717,262</v>
+        <v>1,593,801,974</v>
       </c>
       <c r="N12" t="str">
-        <v>27.04%</v>
+        <v>27.03%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>4,448</v>
+        <v>4,603</v>
       </c>
       <c r="F13" t="str">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G13" t="str">
-        <v>8,069</v>
+        <v>8,428</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>14,398,674,682</v>
+        <v>14,727,779,661</v>
       </c>
       <c r="M13" t="str">
-        <v>146,107,543</v>
+        <v>161,949,434</v>
       </c>
       <c r="N13" t="str">
-        <v>1.01%</v>
+        <v>1.10%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>12,484</v>
+        <v>12,909</v>
       </c>
       <c r="F14" t="str">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="G14" t="str">
-        <v>27,653</v>
+        <v>28,629</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1000,19 +1000,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" t="str">
-        <v>35,490,060</v>
+        <v>71,755,405</v>
       </c>
       <c r="L14" t="str">
-        <v>39,356,090,651</v>
+        <v>40,558,874,526</v>
       </c>
       <c r="M14" t="str">
-        <v>428,422,157</v>
+        <v>482,306,510</v>
       </c>
       <c r="N14" t="str">
-        <v>1.09%</v>
+        <v>1.19%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>8,908</v>
+        <v>9,214</v>
       </c>
       <c r="F15" t="str">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G15" t="str">
-        <v>19,777</v>
+        <v>20,457</v>
       </c>
       <c r="H15" t="str">
         <v>4</v>
@@ -1050,10 +1050,10 @@
         <v>91,206,880</v>
       </c>
       <c r="L15" t="str">
-        <v>28,244,702,223</v>
+        <v>28,998,109,807</v>
       </c>
       <c r="M15" t="str">
-        <v>450,383,183</v>
+        <v>461,919,545</v>
       </c>
       <c r="N15" t="str">
         <v>1.59%</v>
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="F16" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>497,841,731</v>
+        <v>518,702,018</v>
       </c>
       <c r="M16" t="str">
-        <v>7,264,691</v>
+        <v>7,522,612</v>
       </c>
       <c r="N16" t="str">
-        <v>1.46%</v>
+        <v>1.45%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>16,210</v>
+        <v>16,886</v>
       </c>
       <c r="F17" t="str">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G17" t="str">
-        <v>71,700</v>
+        <v>73,955</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>64,283,439,064</v>
+        <v>66,760,217,168</v>
       </c>
       <c r="M17" t="str">
-        <v>327,114,880</v>
+        <v>343,477,961</v>
       </c>
       <c r="N17" t="str">
         <v>0.51%</v>
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,410</v>
+        <v>1,469</v>
       </c>
       <c r="F18" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="str">
-        <v>6,190</v>
+        <v>6,390</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>5,532,831,507</v>
+        <v>5,732,256,758</v>
       </c>
       <c r="M18" t="str">
-        <v>15,361,311</v>
+        <v>20,119,311</v>
       </c>
       <c r="N18" t="str">
-        <v>0.28%</v>
+        <v>0.35%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>6,340</v>
+        <v>6,606</v>
       </c>
       <c r="F19" t="str">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G19" t="str">
-        <v>27,023</v>
+        <v>27,947</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,10 +1226,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>25,690,554,851</v>
+        <v>26,552,603,746</v>
       </c>
       <c r="M19" t="str">
-        <v>140,896,165</v>
+        <v>147,171,908</v>
       </c>
       <c r="N19" t="str">
         <v>0.55%</v>
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,261</v>
+        <v>3,273</v>
       </c>
       <c r="F20" t="str">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G20" t="str">
-        <v>20,964</v>
+        <v>21,779</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,957,195,039</v>
+        <v>11,964,727,215</v>
       </c>
       <c r="M20" t="str">
-        <v>161,058,033</v>
+        <v>183,634,236</v>
       </c>
       <c r="N20" t="str">
-        <v>1.35%</v>
+        <v>1.53%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,947</v>
+        <v>2,963</v>
       </c>
       <c r="F21" t="str">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G21" t="str">
-        <v>135,771</v>
+        <v>140,992</v>
       </c>
       <c r="H21" t="str">
         <v>5</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>9,021,772,145</v>
+        <v>9,053,185,662</v>
       </c>
       <c r="M21" t="str">
-        <v>322,702,647</v>
+        <v>347,793,957</v>
       </c>
       <c r="N21" t="str">
-        <v>3.58%</v>
+        <v>3.84%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>12,758</v>
+        <v>13,053</v>
       </c>
       <c r="F22" t="str">
-        <v>1,195</v>
+        <v>1,261</v>
       </c>
       <c r="G22" t="str">
-        <v>523,367</v>
+        <v>544,019</v>
       </c>
       <c r="H22" t="str">
         <v>41</v>
@@ -1358,13 +1358,13 @@
         <v>167,076,150</v>
       </c>
       <c r="L22" t="str">
-        <v>61,462,555,894</v>
+        <v>62,715,398,893</v>
       </c>
       <c r="M22" t="str">
-        <v>2,153,764,360</v>
+        <v>2,277,555,315</v>
       </c>
       <c r="N22" t="str">
-        <v>3.50%</v>
+        <v>3.63%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,062</v>
+        <v>8,083</v>
       </c>
       <c r="F24" t="str">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G24" t="str">
-        <v>69,898</v>
+        <v>72,584</v>
       </c>
       <c r="H24" t="str">
         <v>24</v>
@@ -1446,13 +1446,13 @@
         <v>184,925,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,470,386,290</v>
+        <v>52,487,700,596</v>
       </c>
       <c r="M24" t="str">
-        <v>565,968,518</v>
+        <v>595,764,768</v>
       </c>
       <c r="N24" t="str">
-        <v>1.08%</v>
+        <v>1.14%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,31 +1513,31 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>31,807</v>
+        <v>33,288</v>
       </c>
       <c r="F26" t="str">
-        <v>10,250</v>
+        <v>10,685</v>
       </c>
       <c r="G26" t="str">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H26" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" t="str">
-        <v>175,320,132</v>
+        <v>186,961,752</v>
       </c>
       <c r="J26" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" t="str">
-        <v>163,965,708</v>
+        <v>184,331,633</v>
       </c>
       <c r="L26" t="str">
-        <v>69,215,188,735</v>
+        <v>72,189,156,343</v>
       </c>
       <c r="M26" t="str">
-        <v>24,188,875,226</v>
+        <v>25,232,937,152</v>
       </c>
       <c r="N26" t="str">
         <v>34.95%</v>
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>4,952</v>
+        <v>5,139</v>
       </c>
       <c r="F27" t="str">
-        <v>2,701</v>
+        <v>2,812</v>
       </c>
       <c r="G27" t="str">
-        <v>4,989</v>
+        <v>5,195</v>
       </c>
       <c r="H27" t="str">
-        <v>747</v>
+        <v>790</v>
       </c>
       <c r="I27" t="str">
-        <v>9,275,216,649</v>
+        <v>9,832,535,248</v>
       </c>
       <c r="J27" t="str">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="K27" t="str">
-        <v>13,031,154,751</v>
+        <v>13,550,392,732</v>
       </c>
       <c r="L27" t="str">
-        <v>61,342,047,604</v>
+        <v>63,750,886,168</v>
       </c>
       <c r="M27" t="str">
-        <v>28,965,407,391</v>
+        <v>30,262,297,212</v>
       </c>
       <c r="N27" t="str">
-        <v>47.22%</v>
+        <v>47.47%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>4,728</v>
+        <v>4,913</v>
       </c>
       <c r="F28" t="str">
-        <v>2,392</v>
+        <v>2,479</v>
       </c>
       <c r="G28" t="str">
-        <v>4,691</v>
+        <v>4,892</v>
       </c>
       <c r="H28" t="str">
-        <v>729</v>
+        <v>759</v>
       </c>
       <c r="I28" t="str">
-        <v>9,132,083,354</v>
+        <v>9,510,882,172</v>
       </c>
       <c r="J28" t="str">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="K28" t="str">
-        <v>11,564,073,286</v>
+        <v>12,182,462,636</v>
       </c>
       <c r="L28" t="str">
-        <v>58,406,542,116</v>
+        <v>60,815,315,330</v>
       </c>
       <c r="M28" t="str">
-        <v>26,746,938,773</v>
+        <v>27,899,985,822</v>
       </c>
       <c r="N28" t="str">
-        <v>45.79%</v>
+        <v>45.88%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>3,070</v>
+        <v>3,183</v>
       </c>
       <c r="F29" t="str">
-        <v>1,593</v>
+        <v>1,642</v>
       </c>
       <c r="G29" t="str">
-        <v>3,175</v>
+        <v>3,292</v>
       </c>
       <c r="H29" t="str">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="I29" t="str">
-        <v>6,031,326,869</v>
+        <v>6,211,292,773</v>
       </c>
       <c r="J29" t="str">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="K29" t="str">
-        <v>8,803,399,969</v>
+        <v>9,007,978,717</v>
       </c>
       <c r="L29" t="str">
-        <v>37,956,766,795</v>
+        <v>39,375,910,378</v>
       </c>
       <c r="M29" t="str">
-        <v>18,168,198,910</v>
+        <v>18,683,662,741</v>
       </c>
       <c r="N29" t="str">
-        <v>47.87%</v>
+        <v>47.45%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,19 +1689,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>32,862</v>
+        <v>34,467</v>
       </c>
       <c r="F30" t="str">
-        <v>10,862</v>
+        <v>11,335</v>
       </c>
       <c r="G30" t="str">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H30" t="str">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" t="str">
-        <v>184,261,169</v>
+        <v>194,447,571</v>
       </c>
       <c r="J30" t="str">
         <v>10</v>
@@ -1710,13 +1710,13 @@
         <v>207,254,874</v>
       </c>
       <c r="L30" t="str">
-        <v>71,356,683,408</v>
+        <v>74,600,578,885</v>
       </c>
       <c r="M30" t="str">
-        <v>25,967,175,393</v>
+        <v>27,021,280,006</v>
       </c>
       <c r="N30" t="str">
-        <v>36.39%</v>
+        <v>36.22%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>2,996</v>
+        <v>3,120</v>
       </c>
       <c r="F31" t="str">
-        <v>1,347</v>
+        <v>1,397</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,142,730,948</v>
+        <v>1,191,705,527</v>
       </c>
       <c r="M31" t="str">
-        <v>515,922,553</v>
+        <v>538,921,636</v>
       </c>
       <c r="N31" t="str">
-        <v>45.15%</v>
+        <v>45.22%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,006</v>
+        <v>2,090</v>
       </c>
       <c r="F32" t="str">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="G32" t="str">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,582,166,102</v>
+        <v>3,709,311,069</v>
       </c>
       <c r="M32" t="str">
-        <v>569,960,204</v>
+        <v>585,234,955</v>
       </c>
       <c r="N32" t="str">
-        <v>15.91%</v>
+        <v>15.78%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,510</v>
+        <v>2,616</v>
       </c>
       <c r="F33" t="str">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="G33" t="str">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>4,352,961,946</v>
+        <v>4,529,455,392</v>
       </c>
       <c r="M33" t="str">
-        <v>595,302,526</v>
+        <v>616,838,309</v>
       </c>
       <c r="N33" t="str">
-        <v>13.68%</v>
+        <v>13.62%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>10,500</v>
+        <v>10,993</v>
       </c>
       <c r="F34" t="str">
-        <v>1,705</v>
+        <v>1,787</v>
       </c>
       <c r="G34" t="str">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>19,498,655,138</v>
+        <v>20,347,591,915</v>
       </c>
       <c r="M34" t="str">
-        <v>2,682,189,428</v>
+        <v>2,804,958,137</v>
       </c>
       <c r="N34" t="str">
-        <v>13.76%</v>
+        <v>13.79%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>2,108</v>
+        <v>2,180</v>
       </c>
       <c r="F35" t="str">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="G35" t="str">
-        <v>6,663</v>
+        <v>6,885</v>
       </c>
       <c r="H35" t="str">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I35" t="str">
-        <v>1,486,466,298</v>
+        <v>1,523,261,773</v>
       </c>
       <c r="J35" t="str">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K35" t="str">
-        <v>1,249,812,619</v>
+        <v>1,380,012,928</v>
       </c>
       <c r="L35" t="str">
-        <v>23,167,673,405</v>
+        <v>24,056,139,037</v>
       </c>
       <c r="M35" t="str">
-        <v>3,835,168,127</v>
+        <v>4,090,231,844</v>
       </c>
       <c r="N35" t="str">
-        <v>16.55%</v>
+        <v>17.00%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,34 +1953,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,730</v>
+        <v>1,802</v>
       </c>
       <c r="F36" t="str">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="G36" t="str">
-        <v>4,830</v>
+        <v>5,056</v>
       </c>
       <c r="H36" t="str">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I36" t="str">
-        <v>917,043,359</v>
+        <v>965,730,737</v>
       </c>
       <c r="J36" t="str">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K36" t="str">
-        <v>973,850,339</v>
+        <v>1,061,494,403</v>
       </c>
       <c r="L36" t="str">
-        <v>18,858,190,266</v>
+        <v>19,582,066,165</v>
       </c>
       <c r="M36" t="str">
-        <v>2,872,880,064</v>
+        <v>3,064,835,749</v>
       </c>
       <c r="N36" t="str">
-        <v>15.23%</v>
+        <v>15.65%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>9,592</v>
+        <v>10,004</v>
       </c>
       <c r="F37" t="str">
-        <v>1,509</v>
+        <v>1,568</v>
       </c>
       <c r="G37" t="str">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="H37" t="str">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>17,249,874,228</v>
+        <v>17,998,368,897</v>
       </c>
       <c r="M37" t="str">
-        <v>2,921,747,088</v>
+        <v>3,042,965,848</v>
       </c>
       <c r="N37" t="str">
-        <v>16.94%</v>
+        <v>16.91%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,080</v>
+        <v>1,112</v>
       </c>
       <c r="F38" t="str">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>469,774,006</v>
+        <v>489,273,524</v>
       </c>
       <c r="M38" t="str">
-        <v>104,189,685</v>
+        <v>107,896,614</v>
       </c>
       <c r="N38" t="str">
-        <v>22.18%</v>
+        <v>22.05%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,187</v>
+        <v>3,293</v>
       </c>
       <c r="F39" t="str">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="G39" t="str">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>5,765,298,976</v>
+        <v>5,952,501,634</v>
       </c>
       <c r="M39" t="str">
-        <v>776,181,227</v>
+        <v>810,311,240</v>
       </c>
       <c r="N39" t="str">
-        <v>13.46%</v>
+        <v>13.61%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,852</v>
+        <v>2,989</v>
       </c>
       <c r="F41" t="str">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>5,135,243,021</v>
+        <v>5,354,092,864</v>
       </c>
       <c r="M41" t="str">
-        <v>733,428,182</v>
+        <v>764,049,061</v>
       </c>
       <c r="N41" t="str">
-        <v>14.28%</v>
+        <v>14.27%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>2,998</v>
+        <v>3,175</v>
       </c>
       <c r="F42" t="str">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="G42" t="str">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>5,586,057,719</v>
+        <v>5,888,719,200</v>
       </c>
       <c r="M42" t="str">
-        <v>784,560,701</v>
+        <v>822,359,614</v>
       </c>
       <c r="N42" t="str">
-        <v>14.04%</v>
+        <v>13.96%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,19 +2261,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>8,828</v>
+        <v>9,081</v>
       </c>
       <c r="F43" t="str">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="G43" t="str">
-        <v>11,504</v>
+        <v>11,888</v>
       </c>
       <c r="H43" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" t="str">
-        <v>59,836,290</v>
+        <v>73,710,127</v>
       </c>
       <c r="J43" t="str">
         <v>2</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>24,590,036,230</v>
+        <v>25,294,441,379</v>
       </c>
       <c r="M43" t="str">
-        <v>795,447,434</v>
+        <v>829,354,022</v>
       </c>
       <c r="N43" t="str">
-        <v>3.23%</v>
+        <v>3.28%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,34 +2305,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>12,024</v>
+        <v>12,405</v>
       </c>
       <c r="F44" t="str">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="G44" t="str">
-        <v>16,214</v>
+        <v>16,796</v>
       </c>
       <c r="H44" t="str">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I44" t="str">
-        <v>246,187,987</v>
+        <v>266,187,987</v>
       </c>
       <c r="J44" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" t="str">
-        <v>243,768,797</v>
+        <v>261,768,797</v>
       </c>
       <c r="L44" t="str">
-        <v>33,980,298,344</v>
+        <v>34,984,939,309</v>
       </c>
       <c r="M44" t="str">
-        <v>1,468,038,969</v>
+        <v>1,555,941,044</v>
       </c>
       <c r="N44" t="str">
-        <v>4.32%</v>
+        <v>4.45%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>659</v>
+        <v>813</v>
       </c>
       <c r="F45" t="str">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G45" t="str">
-        <v>159</v>
+        <v>232</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>2,387,803,452</v>
+        <v>3,087,571,980</v>
       </c>
       <c r="M45" t="str">
-        <v>79,977,923</v>
+        <v>102,774,341</v>
       </c>
       <c r="N45" t="str">
-        <v>3.35%</v>
+        <v>3.33%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,34 +2393,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>8,004</v>
+        <v>8,283</v>
       </c>
       <c r="F46" t="str">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="G46" t="str">
-        <v>9,610</v>
+        <v>10,000</v>
       </c>
       <c r="H46" t="str">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I46" t="str">
-        <v>210,093,634</v>
+        <v>237,541,308</v>
       </c>
       <c r="J46" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K46" t="str">
-        <v>142,152,166</v>
+        <v>158,259,221</v>
       </c>
       <c r="L46" t="str">
-        <v>22,561,996,240</v>
+        <v>23,425,516,355</v>
       </c>
       <c r="M46" t="str">
-        <v>1,047,500,223</v>
+        <v>1,118,174,103</v>
       </c>
       <c r="N46" t="str">
-        <v>4.64%</v>
+        <v>4.77%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>704</v>
+        <v>726</v>
       </c>
       <c r="F47" t="str">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G47" t="str">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>370,848,214</v>
+        <v>379,125,852</v>
       </c>
       <c r="M47" t="str">
-        <v>43,090,419</v>
+        <v>44,663,603</v>
       </c>
       <c r="N47" t="str">
-        <v>11.62%</v>
+        <v>11.78%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,13 +457,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>5,498</v>
+        <v>5,703</v>
       </c>
       <c r="F2" t="str">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G2" t="str">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="H2" t="str">
         <v>29</v>
@@ -478,13 +478,13 @@
         <v>140,563,756</v>
       </c>
       <c r="L2" t="str">
-        <v>23,991,647,531</v>
+        <v>24,950,469,234</v>
       </c>
       <c r="M2" t="str">
-        <v>1,321,457,513</v>
+        <v>1,362,797,332</v>
       </c>
       <c r="N2" t="str">
-        <v>5.51%</v>
+        <v>5.46%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,489</v>
+        <v>3,650</v>
       </c>
       <c r="F3" t="str">
-        <v>939</v>
+        <v>978</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>6,487,458,987</v>
+        <v>6,797,242,094</v>
       </c>
       <c r="M3" t="str">
-        <v>1,638,418,104</v>
+        <v>1,720,006,487</v>
       </c>
       <c r="N3" t="str">
-        <v>25.26%</v>
+        <v>25.30%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>14,107</v>
+        <v>14,689</v>
       </c>
       <c r="F4" t="str">
-        <v>4,038</v>
+        <v>4,187</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>26,161,322,404</v>
+        <v>27,195,894,697</v>
       </c>
       <c r="M4" t="str">
-        <v>7,224,640,129</v>
+        <v>7,477,420,197</v>
       </c>
       <c r="N4" t="str">
-        <v>27.62%</v>
+        <v>27.49%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,481</v>
+        <v>1,526</v>
       </c>
       <c r="F5" t="str">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="G5" t="str">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="H5" t="str">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I5" t="str">
-        <v>2,144,351,587</v>
+        <v>2,240,424,575</v>
       </c>
       <c r="J5" t="str">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K5" t="str">
-        <v>2,103,131,816</v>
+        <v>2,218,075,060</v>
       </c>
       <c r="L5" t="str">
-        <v>17,552,192,346</v>
+        <v>18,118,778,651</v>
       </c>
       <c r="M5" t="str">
-        <v>6,145,575,598</v>
+        <v>6,433,711,513</v>
       </c>
       <c r="N5" t="str">
-        <v>35.01%</v>
+        <v>35.51%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>2,001</v>
+        <v>2,076</v>
       </c>
       <c r="F6" t="str">
-        <v>796</v>
+        <v>824</v>
       </c>
       <c r="G6" t="str">
-        <v>1,158</v>
+        <v>1,203</v>
       </c>
       <c r="H6" t="str">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I6" t="str">
-        <v>2,658,137,365</v>
+        <v>2,719,802,828</v>
       </c>
       <c r="J6" t="str">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K6" t="str">
-        <v>2,221,044,016</v>
+        <v>2,300,883,975</v>
       </c>
       <c r="L6" t="str">
-        <v>23,590,357,296</v>
+        <v>24,537,521,322</v>
       </c>
       <c r="M6" t="str">
-        <v>7,616,709,399</v>
+        <v>7,869,966,970</v>
       </c>
       <c r="N6" t="str">
-        <v>32.29%</v>
+        <v>32.07%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,785</v>
+        <v>1,846</v>
       </c>
       <c r="F7" t="str">
-        <v>701</v>
+        <v>729</v>
       </c>
       <c r="G7" t="str">
-        <v>1,048</v>
+        <v>1,091</v>
       </c>
       <c r="H7" t="str">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I7" t="str">
-        <v>2,581,196,029</v>
+        <v>2,666,440,277</v>
       </c>
       <c r="J7" t="str">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K7" t="str">
-        <v>1,955,887,812</v>
+        <v>1,996,821,662</v>
       </c>
       <c r="L7" t="str">
-        <v>21,047,327,489</v>
+        <v>21,792,970,521</v>
       </c>
       <c r="M7" t="str">
-        <v>6,795,835,399</v>
+        <v>7,031,352,072</v>
       </c>
       <c r="N7" t="str">
-        <v>32.29%</v>
+        <v>32.26%</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>893</v>
+        <v>923</v>
       </c>
       <c r="F8" t="str">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="G8" t="str">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="H8" t="str">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I8" t="str">
-        <v>1,089,044,165</v>
+        <v>1,179,150,595</v>
       </c>
       <c r="J8" t="str">
         <v>52</v>
@@ -742,13 +742,13 @@
         <v>1,048,711,529</v>
       </c>
       <c r="L8" t="str">
-        <v>10,686,144,229</v>
+        <v>11,070,315,661</v>
       </c>
       <c r="M8" t="str">
-        <v>3,335,526,265</v>
+        <v>3,469,043,953</v>
       </c>
       <c r="N8" t="str">
-        <v>31.21%</v>
+        <v>31.34%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>21,546</v>
+        <v>22,496</v>
       </c>
       <c r="F9" t="str">
-        <v>5,905</v>
+        <v>6,176</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>39,716,032,504</v>
+        <v>41,428,620,771</v>
       </c>
       <c r="M9" t="str">
-        <v>10,471,688,493</v>
+        <v>10,916,295,277</v>
       </c>
       <c r="N9" t="str">
-        <v>26.37%</v>
+        <v>26.35%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,199</v>
+        <v>2,284</v>
       </c>
       <c r="F10" t="str">
-        <v>1,040</v>
+        <v>1,075</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>740,551,754</v>
+        <v>771,596,537</v>
       </c>
       <c r="M10" t="str">
-        <v>315,852,248</v>
+        <v>328,592,244</v>
       </c>
       <c r="N10" t="str">
-        <v>42.65%</v>
+        <v>42.59%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,926</v>
+        <v>4,079</v>
       </c>
       <c r="F11" t="str">
-        <v>1,088</v>
+        <v>1,133</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>7,404,771,481</v>
+        <v>7,706,323,589</v>
       </c>
       <c r="M11" t="str">
-        <v>1,893,897,271</v>
+        <v>1,974,265,143</v>
       </c>
       <c r="N11" t="str">
-        <v>25.58%</v>
+        <v>25.62%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,144</v>
+        <v>3,284</v>
       </c>
       <c r="F12" t="str">
-        <v>907</v>
+        <v>934</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>5,896,683,446</v>
+        <v>6,136,473,866</v>
       </c>
       <c r="M12" t="str">
-        <v>1,593,801,974</v>
+        <v>1,630,349,851</v>
       </c>
       <c r="N12" t="str">
-        <v>27.03%</v>
+        <v>26.57%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>4,603</v>
+        <v>4,796</v>
       </c>
       <c r="F13" t="str">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G13" t="str">
-        <v>8,428</v>
+        <v>8,799</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>14,727,779,661</v>
+        <v>15,408,216,689</v>
       </c>
       <c r="M13" t="str">
-        <v>161,949,434</v>
+        <v>163,865,392</v>
       </c>
       <c r="N13" t="str">
-        <v>1.10%</v>
+        <v>1.06%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>12,909</v>
+        <v>13,453</v>
       </c>
       <c r="F14" t="str">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G14" t="str">
-        <v>28,629</v>
+        <v>29,606</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>71,755,405</v>
       </c>
       <c r="L14" t="str">
-        <v>40,558,874,526</v>
+        <v>42,327,308,386</v>
       </c>
       <c r="M14" t="str">
-        <v>482,306,510</v>
+        <v>495,078,965</v>
       </c>
       <c r="N14" t="str">
-        <v>1.19%</v>
+        <v>1.17%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,34 +1029,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>9,214</v>
+        <v>9,600</v>
       </c>
       <c r="F15" t="str">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G15" t="str">
-        <v>20,457</v>
+        <v>21,137</v>
       </c>
       <c r="H15" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="str">
-        <v>50,633,992</v>
+        <v>61,922,672</v>
       </c>
       <c r="J15" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K15" t="str">
-        <v>91,206,880</v>
+        <v>176,637,045</v>
       </c>
       <c r="L15" t="str">
-        <v>28,998,109,807</v>
+        <v>30,303,144,436</v>
       </c>
       <c r="M15" t="str">
-        <v>461,919,545</v>
+        <v>554,518,476</v>
       </c>
       <c r="N15" t="str">
-        <v>1.59%</v>
+        <v>1.83%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="F16" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>518,702,018</v>
+        <v>534,947,465</v>
       </c>
       <c r="M16" t="str">
-        <v>7,522,612</v>
+        <v>7,790,238</v>
       </c>
       <c r="N16" t="str">
-        <v>1.45%</v>
+        <v>1.46%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>16,886</v>
+        <v>17,572</v>
       </c>
       <c r="F17" t="str">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G17" t="str">
-        <v>73,955</v>
+        <v>76,185</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>66,760,217,168</v>
+        <v>69,206,415,400</v>
       </c>
       <c r="M17" t="str">
-        <v>343,477,961</v>
+        <v>358,079,838</v>
       </c>
       <c r="N17" t="str">
-        <v>0.51%</v>
+        <v>0.52%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,469</v>
+        <v>1,529</v>
       </c>
       <c r="F18" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" t="str">
-        <v>6,390</v>
+        <v>6,589</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>5,732,256,758</v>
+        <v>5,930,919,103</v>
       </c>
       <c r="M18" t="str">
-        <v>20,119,311</v>
+        <v>20,619,311</v>
       </c>
       <c r="N18" t="str">
         <v>0.35%</v>
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>6,606</v>
+        <v>6,873</v>
       </c>
       <c r="F19" t="str">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G19" t="str">
-        <v>27,947</v>
+        <v>28,869</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>26,552,603,746</v>
+        <v>27,609,876,194</v>
       </c>
       <c r="M19" t="str">
-        <v>147,171,908</v>
+        <v>149,312,379</v>
       </c>
       <c r="N19" t="str">
-        <v>0.55%</v>
+        <v>0.54%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,273</v>
+        <v>3,287</v>
       </c>
       <c r="F20" t="str">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G20" t="str">
-        <v>21,779</v>
+        <v>22,595</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,964,727,215</v>
+        <v>11,972,107,733</v>
       </c>
       <c r="M20" t="str">
-        <v>183,634,236</v>
+        <v>187,541,247</v>
       </c>
       <c r="N20" t="str">
-        <v>1.53%</v>
+        <v>1.57%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,963</v>
+        <v>2,979</v>
       </c>
       <c r="F21" t="str">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G21" t="str">
-        <v>140,992</v>
+        <v>146,210</v>
       </c>
       <c r="H21" t="str">
         <v>5</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>9,053,185,662</v>
+        <v>9,062,222,619</v>
       </c>
       <c r="M21" t="str">
-        <v>347,793,957</v>
+        <v>356,145,879</v>
       </c>
       <c r="N21" t="str">
-        <v>3.84%</v>
+        <v>3.93%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,19 +1337,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>13,053</v>
+        <v>13,336</v>
       </c>
       <c r="F22" t="str">
-        <v>1,261</v>
+        <v>1,339</v>
       </c>
       <c r="G22" t="str">
-        <v>544,019</v>
+        <v>564,709</v>
       </c>
       <c r="H22" t="str">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I22" t="str">
-        <v>513,083,920</v>
+        <v>540,443,400</v>
       </c>
       <c r="J22" t="str">
         <v>10</v>
@@ -1358,13 +1358,13 @@
         <v>167,076,150</v>
       </c>
       <c r="L22" t="str">
-        <v>62,715,398,893</v>
+        <v>64,004,111,510</v>
       </c>
       <c r="M22" t="str">
-        <v>2,277,555,315</v>
+        <v>2,410,661,725</v>
       </c>
       <c r="N22" t="str">
-        <v>3.63%</v>
+        <v>3.77%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,083</v>
+        <v>8,106</v>
       </c>
       <c r="F24" t="str">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="G24" t="str">
-        <v>72,584</v>
+        <v>75,272</v>
       </c>
       <c r="H24" t="str">
         <v>24</v>
@@ -1446,13 +1446,13 @@
         <v>184,925,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,487,700,596</v>
+        <v>52,500,896,550</v>
       </c>
       <c r="M24" t="str">
-        <v>595,764,768</v>
+        <v>631,709,106</v>
       </c>
       <c r="N24" t="str">
-        <v>1.14%</v>
+        <v>1.20%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>33,288</v>
+        <v>34,772</v>
       </c>
       <c r="F26" t="str">
-        <v>10,685</v>
+        <v>11,182</v>
       </c>
       <c r="G26" t="str">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H26" t="str">
         <v>15</v>
@@ -1534,13 +1534,13 @@
         <v>184,331,633</v>
       </c>
       <c r="L26" t="str">
-        <v>72,189,156,343</v>
+        <v>75,259,522,727</v>
       </c>
       <c r="M26" t="str">
-        <v>25,232,937,152</v>
+        <v>26,411,435,070</v>
       </c>
       <c r="N26" t="str">
-        <v>34.95%</v>
+        <v>35.09%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>5,139</v>
+        <v>5,327</v>
       </c>
       <c r="F27" t="str">
-        <v>2,812</v>
+        <v>2,907</v>
       </c>
       <c r="G27" t="str">
-        <v>5,195</v>
+        <v>5,389</v>
       </c>
       <c r="H27" t="str">
-        <v>790</v>
+        <v>821</v>
       </c>
       <c r="I27" t="str">
-        <v>9,832,535,248</v>
+        <v>10,232,156,576</v>
       </c>
       <c r="J27" t="str">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="K27" t="str">
-        <v>13,550,392,732</v>
+        <v>13,822,884,424</v>
       </c>
       <c r="L27" t="str">
-        <v>63,750,886,168</v>
+        <v>66,132,462,577</v>
       </c>
       <c r="M27" t="str">
-        <v>30,262,297,212</v>
+        <v>31,213,543,660</v>
       </c>
       <c r="N27" t="str">
-        <v>47.47%</v>
+        <v>47.20%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>4,913</v>
+        <v>5,068</v>
       </c>
       <c r="F28" t="str">
-        <v>2,479</v>
+        <v>2,578</v>
       </c>
       <c r="G28" t="str">
-        <v>4,892</v>
+        <v>5,083</v>
       </c>
       <c r="H28" t="str">
-        <v>759</v>
+        <v>798</v>
       </c>
       <c r="I28" t="str">
-        <v>9,510,882,172</v>
+        <v>9,993,266,238</v>
       </c>
       <c r="J28" t="str">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="K28" t="str">
-        <v>12,182,462,636</v>
+        <v>12,749,154,352</v>
       </c>
       <c r="L28" t="str">
-        <v>60,815,315,330</v>
+        <v>62,786,819,163</v>
       </c>
       <c r="M28" t="str">
-        <v>27,899,985,822</v>
+        <v>29,104,604,417</v>
       </c>
       <c r="N28" t="str">
-        <v>45.88%</v>
+        <v>46.35%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>3,183</v>
+        <v>3,275</v>
       </c>
       <c r="F29" t="str">
-        <v>1,642</v>
+        <v>1,703</v>
       </c>
       <c r="G29" t="str">
-        <v>3,292</v>
+        <v>3,416</v>
       </c>
       <c r="H29" t="str">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="I29" t="str">
-        <v>6,211,292,773</v>
+        <v>6,456,881,510</v>
       </c>
       <c r="J29" t="str">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="K29" t="str">
-        <v>9,007,978,717</v>
+        <v>9,423,353,384</v>
       </c>
       <c r="L29" t="str">
-        <v>39,375,910,378</v>
+        <v>40,603,643,969</v>
       </c>
       <c r="M29" t="str">
-        <v>18,683,662,741</v>
+        <v>19,446,503,878</v>
       </c>
       <c r="N29" t="str">
-        <v>47.45%</v>
+        <v>47.89%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>34,467</v>
+        <v>36,009</v>
       </c>
       <c r="F30" t="str">
-        <v>11,335</v>
+        <v>11,869</v>
       </c>
       <c r="G30" t="str">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H30" t="str">
         <v>16</v>
@@ -1704,19 +1704,19 @@
         <v>194,447,571</v>
       </c>
       <c r="J30" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" t="str">
-        <v>207,254,874</v>
+        <v>223,318,503</v>
       </c>
       <c r="L30" t="str">
-        <v>74,600,578,885</v>
+        <v>77,781,665,891</v>
       </c>
       <c r="M30" t="str">
-        <v>27,021,280,006</v>
+        <v>28,200,148,077</v>
       </c>
       <c r="N30" t="str">
-        <v>36.22%</v>
+        <v>36.26%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,120</v>
+        <v>3,248</v>
       </c>
       <c r="F31" t="str">
-        <v>1,397</v>
+        <v>1,450</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,191,705,527</v>
+        <v>1,244,334,541</v>
       </c>
       <c r="M31" t="str">
-        <v>538,921,636</v>
+        <v>561,949,066</v>
       </c>
       <c r="N31" t="str">
-        <v>45.22%</v>
+        <v>45.16%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,090</v>
+        <v>2,176</v>
       </c>
       <c r="F32" t="str">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="G32" t="str">
         <v>22</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,709,311,069</v>
+        <v>3,848,903,089</v>
       </c>
       <c r="M32" t="str">
-        <v>585,234,955</v>
+        <v>609,292,040</v>
       </c>
       <c r="N32" t="str">
-        <v>15.78%</v>
+        <v>15.83%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,616</v>
+        <v>2,726</v>
       </c>
       <c r="F33" t="str">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="G33" t="str">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>4,529,455,392</v>
+        <v>4,727,254,827</v>
       </c>
       <c r="M33" t="str">
-        <v>616,838,309</v>
+        <v>679,567,342</v>
       </c>
       <c r="N33" t="str">
-        <v>13.62%</v>
+        <v>14.38%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>10,993</v>
+        <v>11,447</v>
       </c>
       <c r="F34" t="str">
-        <v>1,787</v>
+        <v>1,896</v>
       </c>
       <c r="G34" t="str">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>20,347,591,915</v>
+        <v>21,104,575,264</v>
       </c>
       <c r="M34" t="str">
-        <v>2,804,958,137</v>
+        <v>2,963,795,574</v>
       </c>
       <c r="N34" t="str">
-        <v>13.79%</v>
+        <v>14.04%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>2,180</v>
+        <v>2,240</v>
       </c>
       <c r="F35" t="str">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="G35" t="str">
-        <v>6,885</v>
+        <v>7,098</v>
       </c>
       <c r="H35" t="str">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I35" t="str">
-        <v>1,523,261,773</v>
+        <v>1,576,403,351</v>
       </c>
       <c r="J35" t="str">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K35" t="str">
-        <v>1,380,012,928</v>
+        <v>1,414,078,447</v>
       </c>
       <c r="L35" t="str">
-        <v>24,056,139,037</v>
+        <v>24,772,064,069</v>
       </c>
       <c r="M35" t="str">
-        <v>4,090,231,844</v>
+        <v>4,241,581,222</v>
       </c>
       <c r="N35" t="str">
-        <v>17.00%</v>
+        <v>17.12%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,34 +1953,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,802</v>
+        <v>1,862</v>
       </c>
       <c r="F36" t="str">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G36" t="str">
-        <v>5,056</v>
+        <v>5,279</v>
       </c>
       <c r="H36" t="str">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I36" t="str">
-        <v>965,730,737</v>
+        <v>1,029,012,034</v>
       </c>
       <c r="J36" t="str">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K36" t="str">
-        <v>1,061,494,403</v>
+        <v>1,097,498,183</v>
       </c>
       <c r="L36" t="str">
-        <v>19,582,066,165</v>
+        <v>20,252,813,524</v>
       </c>
       <c r="M36" t="str">
-        <v>3,064,835,749</v>
+        <v>3,206,385,120</v>
       </c>
       <c r="N36" t="str">
-        <v>15.65%</v>
+        <v>15.83%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,19 +1997,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>10,004</v>
+        <v>10,392</v>
       </c>
       <c r="F37" t="str">
-        <v>1,568</v>
+        <v>1,632</v>
       </c>
       <c r="G37" t="str">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="H37" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" t="str">
-        <v>21,640,092</v>
+        <v>45,640,092</v>
       </c>
       <c r="J37" t="str">
         <v>1</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>17,998,368,897</v>
+        <v>18,637,168,553</v>
       </c>
       <c r="M37" t="str">
-        <v>3,042,965,848</v>
+        <v>3,206,959,694</v>
       </c>
       <c r="N37" t="str">
-        <v>16.91%</v>
+        <v>17.21%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,112</v>
+        <v>1,144</v>
       </c>
       <c r="F38" t="str">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>489,273,524</v>
+        <v>508,563,729</v>
       </c>
       <c r="M38" t="str">
-        <v>107,896,614</v>
+        <v>121,469,949</v>
       </c>
       <c r="N38" t="str">
-        <v>22.05%</v>
+        <v>23.88%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,293</v>
+        <v>3,455</v>
       </c>
       <c r="F39" t="str">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="G39" t="str">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>5,952,501,634</v>
+        <v>6,275,964,458</v>
       </c>
       <c r="M39" t="str">
-        <v>810,311,240</v>
+        <v>855,056,549</v>
       </c>
       <c r="N39" t="str">
-        <v>13.61%</v>
+        <v>13.62%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>2,989</v>
+        <v>3,118</v>
       </c>
       <c r="F41" t="str">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>5,354,092,864</v>
+        <v>5,560,606,590</v>
       </c>
       <c r="M41" t="str">
-        <v>764,049,061</v>
+        <v>802,116,168</v>
       </c>
       <c r="N41" t="str">
-        <v>14.27%</v>
+        <v>14.42%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>3,175</v>
+        <v>3,271</v>
       </c>
       <c r="F42" t="str">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="G42" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>5,888,719,200</v>
+        <v>6,057,667,663</v>
       </c>
       <c r="M42" t="str">
-        <v>822,359,614</v>
+        <v>870,686,680</v>
       </c>
       <c r="N42" t="str">
-        <v>13.96%</v>
+        <v>14.37%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>9,081</v>
+        <v>9,350</v>
       </c>
       <c r="F43" t="str">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G43" t="str">
-        <v>11,888</v>
+        <v>12,260</v>
       </c>
       <c r="H43" t="str">
         <v>6</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>25,294,441,379</v>
+        <v>25,997,804,558</v>
       </c>
       <c r="M43" t="str">
-        <v>829,354,022</v>
+        <v>867,782,509</v>
       </c>
       <c r="N43" t="str">
-        <v>3.28%</v>
+        <v>3.34%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>12,405</v>
+        <v>12,820</v>
       </c>
       <c r="F44" t="str">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="G44" t="str">
-        <v>16,796</v>
+        <v>17,361</v>
       </c>
       <c r="H44" t="str">
         <v>23</v>
@@ -2320,19 +2320,19 @@
         <v>266,187,987</v>
       </c>
       <c r="J44" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K44" t="str">
-        <v>261,768,797</v>
+        <v>280,029,887</v>
       </c>
       <c r="L44" t="str">
-        <v>34,984,939,309</v>
+        <v>36,015,082,857</v>
       </c>
       <c r="M44" t="str">
-        <v>1,555,941,044</v>
+        <v>1,644,055,547</v>
       </c>
       <c r="N44" t="str">
-        <v>4.45%</v>
+        <v>4.56%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>813</v>
+        <v>980</v>
       </c>
       <c r="F45" t="str">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G45" t="str">
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>3,087,571,980</v>
+        <v>3,712,973,701</v>
       </c>
       <c r="M45" t="str">
-        <v>102,774,341</v>
+        <v>116,647,604</v>
       </c>
       <c r="N45" t="str">
-        <v>3.33%</v>
+        <v>3.14%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,19 +2393,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>8,283</v>
+        <v>8,585</v>
       </c>
       <c r="F46" t="str">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="G46" t="str">
-        <v>10,000</v>
+        <v>10,383</v>
       </c>
       <c r="H46" t="str">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I46" t="str">
-        <v>237,541,308</v>
+        <v>261,588,148</v>
       </c>
       <c r="J46" t="str">
         <v>9</v>
@@ -2414,13 +2414,13 @@
         <v>158,259,221</v>
       </c>
       <c r="L46" t="str">
-        <v>23,425,516,355</v>
+        <v>24,157,009,925</v>
       </c>
       <c r="M46" t="str">
-        <v>1,118,174,103</v>
+        <v>1,212,294,918</v>
       </c>
       <c r="N46" t="str">
-        <v>4.77%</v>
+        <v>5.02%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="F47" t="str">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G47" t="str">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>379,125,852</v>
+        <v>386,947,199</v>
       </c>
       <c r="M47" t="str">
-        <v>44,663,603</v>
+        <v>46,862,614</v>
       </c>
       <c r="N47" t="str">
-        <v>11.78%</v>
+        <v>12.11%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,13 +457,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>5,703</v>
+        <v>5,906</v>
       </c>
       <c r="F2" t="str">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="G2" t="str">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="H2" t="str">
         <v>29</v>
@@ -478,13 +478,13 @@
         <v>140,563,756</v>
       </c>
       <c r="L2" t="str">
-        <v>24,950,469,234</v>
+        <v>25,841,422,977</v>
       </c>
       <c r="M2" t="str">
-        <v>1,362,797,332</v>
+        <v>1,401,724,306</v>
       </c>
       <c r="N2" t="str">
-        <v>5.46%</v>
+        <v>5.42%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,650</v>
+        <v>3,814</v>
       </c>
       <c r="F3" t="str">
-        <v>978</v>
+        <v>1,010</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>6,797,242,094</v>
+        <v>7,109,398,906</v>
       </c>
       <c r="M3" t="str">
-        <v>1,720,006,487</v>
+        <v>1,765,155,101</v>
       </c>
       <c r="N3" t="str">
-        <v>25.30%</v>
+        <v>24.83%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>14,689</v>
+        <v>15,376</v>
       </c>
       <c r="F4" t="str">
-        <v>4,187</v>
+        <v>4,368</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>27,195,894,697</v>
+        <v>28,301,941,661</v>
       </c>
       <c r="M4" t="str">
-        <v>7,477,420,197</v>
+        <v>7,750,036,533</v>
       </c>
       <c r="N4" t="str">
-        <v>27.49%</v>
+        <v>27.38%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,526</v>
+        <v>1,571</v>
       </c>
       <c r="F5" t="str">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="G5" t="str">
-        <v>911</v>
+        <v>943</v>
       </c>
       <c r="H5" t="str">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I5" t="str">
-        <v>2,240,424,575</v>
+        <v>2,341,499,574</v>
       </c>
       <c r="J5" t="str">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K5" t="str">
-        <v>2,218,075,060</v>
+        <v>2,291,604,326</v>
       </c>
       <c r="L5" t="str">
-        <v>18,118,778,651</v>
+        <v>18,667,635,575</v>
       </c>
       <c r="M5" t="str">
-        <v>6,433,711,513</v>
+        <v>6,657,847,697</v>
       </c>
       <c r="N5" t="str">
-        <v>35.51%</v>
+        <v>35.67%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>2,076</v>
+        <v>2,160</v>
       </c>
       <c r="F6" t="str">
-        <v>824</v>
+        <v>860</v>
       </c>
       <c r="G6" t="str">
-        <v>1,203</v>
+        <v>1,257</v>
       </c>
       <c r="H6" t="str">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="I6" t="str">
-        <v>2,719,802,828</v>
+        <v>2,873,996,821</v>
       </c>
       <c r="J6" t="str">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K6" t="str">
-        <v>2,300,883,975</v>
+        <v>2,430,050,785</v>
       </c>
       <c r="L6" t="str">
-        <v>24,537,521,322</v>
+        <v>25,549,576,519</v>
       </c>
       <c r="M6" t="str">
-        <v>7,869,966,970</v>
+        <v>8,238,760,838</v>
       </c>
       <c r="N6" t="str">
-        <v>32.07%</v>
+        <v>32.25%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,846</v>
+        <v>1,907</v>
       </c>
       <c r="F7" t="str">
-        <v>729</v>
+        <v>755</v>
       </c>
       <c r="G7" t="str">
-        <v>1,091</v>
+        <v>1,132</v>
       </c>
       <c r="H7" t="str">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="I7" t="str">
-        <v>2,666,440,277</v>
+        <v>2,760,674,835</v>
       </c>
       <c r="J7" t="str">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K7" t="str">
-        <v>1,996,821,662</v>
+        <v>2,076,715,214</v>
       </c>
       <c r="L7" t="str">
-        <v>21,792,970,521</v>
+        <v>22,503,810,503</v>
       </c>
       <c r="M7" t="str">
-        <v>7,031,352,072</v>
+        <v>7,276,932,759</v>
       </c>
       <c r="N7" t="str">
-        <v>32.26%</v>
+        <v>32.34%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>923</v>
+        <v>953</v>
       </c>
       <c r="F8" t="str">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="G8" t="str">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="H8" t="str">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I8" t="str">
-        <v>1,179,150,595</v>
+        <v>1,204,476,816</v>
       </c>
       <c r="J8" t="str">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K8" t="str">
-        <v>1,048,711,529</v>
+        <v>1,162,225,963</v>
       </c>
       <c r="L8" t="str">
-        <v>11,070,315,661</v>
+        <v>11,438,476,742</v>
       </c>
       <c r="M8" t="str">
-        <v>3,469,043,953</v>
+        <v>3,645,621,734</v>
       </c>
       <c r="N8" t="str">
-        <v>31.34%</v>
+        <v>31.87%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>22,496</v>
+        <v>23,519</v>
       </c>
       <c r="F9" t="str">
-        <v>6,176</v>
+        <v>6,408</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>41,428,620,771</v>
+        <v>43,168,262,479</v>
       </c>
       <c r="M9" t="str">
-        <v>10,916,295,277</v>
+        <v>11,274,069,123</v>
       </c>
       <c r="N9" t="str">
-        <v>26.35%</v>
+        <v>26.12%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,284</v>
+        <v>2,378</v>
       </c>
       <c r="F10" t="str">
-        <v>1,075</v>
+        <v>1,121</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>771,596,537</v>
+        <v>804,936,517</v>
       </c>
       <c r="M10" t="str">
-        <v>328,592,244</v>
+        <v>342,792,359</v>
       </c>
       <c r="N10" t="str">
         <v>42.59%</v>
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>4,079</v>
+        <v>4,239</v>
       </c>
       <c r="F11" t="str">
-        <v>1,133</v>
+        <v>1,176</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>7,706,323,589</v>
+        <v>7,961,069,597</v>
       </c>
       <c r="M11" t="str">
-        <v>1,974,265,143</v>
+        <v>2,047,721,966</v>
       </c>
       <c r="N11" t="str">
-        <v>25.62%</v>
+        <v>25.72%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,284</v>
+        <v>3,406</v>
       </c>
       <c r="F12" t="str">
-        <v>934</v>
+        <v>975</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>6,136,473,866</v>
+        <v>6,368,343,093</v>
       </c>
       <c r="M12" t="str">
-        <v>1,630,349,851</v>
+        <v>1,712,465,656</v>
       </c>
       <c r="N12" t="str">
-        <v>26.57%</v>
+        <v>26.89%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>4,796</v>
+        <v>4,974</v>
       </c>
       <c r="F13" t="str">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G13" t="str">
-        <v>8,799</v>
+        <v>9,158</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,10 +962,10 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>15,408,216,689</v>
+        <v>15,886,812,980</v>
       </c>
       <c r="M13" t="str">
-        <v>163,865,392</v>
+        <v>168,660,609</v>
       </c>
       <c r="N13" t="str">
         <v>1.06%</v>
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>13,453</v>
+        <v>13,951</v>
       </c>
       <c r="F14" t="str">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="G14" t="str">
-        <v>29,606</v>
+        <v>30,566</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>71,755,405</v>
       </c>
       <c r="L14" t="str">
-        <v>42,327,308,386</v>
+        <v>43,763,579,633</v>
       </c>
       <c r="M14" t="str">
-        <v>495,078,965</v>
+        <v>516,467,318</v>
       </c>
       <c r="N14" t="str">
-        <v>1.17%</v>
+        <v>1.18%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>9,600</v>
+        <v>9,956</v>
       </c>
       <c r="F15" t="str">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G15" t="str">
-        <v>21,137</v>
+        <v>21,803</v>
       </c>
       <c r="H15" t="str">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>176,637,045</v>
       </c>
       <c r="L15" t="str">
-        <v>30,303,144,436</v>
+        <v>31,409,935,567</v>
       </c>
       <c r="M15" t="str">
-        <v>554,518,476</v>
+        <v>565,129,223</v>
       </c>
       <c r="N15" t="str">
-        <v>1.83%</v>
+        <v>1.80%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="F16" t="str">
         <v>15</v>
       </c>
       <c r="G16" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>534,947,465</v>
+        <v>550,890,122</v>
       </c>
       <c r="M16" t="str">
         <v>7,790,238</v>
       </c>
       <c r="N16" t="str">
-        <v>1.46%</v>
+        <v>1.41%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>17,572</v>
+        <v>18,296</v>
       </c>
       <c r="F17" t="str">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G17" t="str">
-        <v>76,185</v>
+        <v>78,411</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>69,206,415,400</v>
+        <v>71,805,230,049</v>
       </c>
       <c r="M17" t="str">
-        <v>358,079,838</v>
+        <v>366,701,935</v>
       </c>
       <c r="N17" t="str">
-        <v>0.52%</v>
+        <v>0.51%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,529</v>
+        <v>1,591</v>
       </c>
       <c r="F18" t="str">
         <v>9</v>
       </c>
       <c r="G18" t="str">
-        <v>6,589</v>
+        <v>6,788</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>5,930,919,103</v>
+        <v>6,218,963,430</v>
       </c>
       <c r="M18" t="str">
         <v>20,619,311</v>
       </c>
       <c r="N18" t="str">
-        <v>0.35%</v>
+        <v>0.33%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>6,873</v>
+        <v>7,153</v>
       </c>
       <c r="F19" t="str">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" t="str">
-        <v>28,869</v>
+        <v>29,805</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>27,609,876,194</v>
+        <v>28,789,479,312</v>
       </c>
       <c r="M19" t="str">
-        <v>149,312,379</v>
+        <v>151,367,379</v>
       </c>
       <c r="N19" t="str">
-        <v>0.54%</v>
+        <v>0.53%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,287</v>
+        <v>3,301</v>
       </c>
       <c r="F20" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" t="str">
-        <v>22,595</v>
+        <v>23,411</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,972,107,733</v>
+        <v>11,983,541,955</v>
       </c>
       <c r="M20" t="str">
-        <v>187,541,247</v>
+        <v>190,429,687</v>
       </c>
       <c r="N20" t="str">
-        <v>1.57%</v>
+        <v>1.59%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,979</v>
+        <v>2,982</v>
       </c>
       <c r="F21" t="str">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G21" t="str">
-        <v>146,210</v>
+        <v>151,428</v>
       </c>
       <c r="H21" t="str">
         <v>5</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>9,062,222,619</v>
+        <v>9,064,007,599</v>
       </c>
       <c r="M21" t="str">
-        <v>356,145,879</v>
+        <v>359,530,255</v>
       </c>
       <c r="N21" t="str">
-        <v>3.93%</v>
+        <v>3.97%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>13,336</v>
+        <v>13,618</v>
       </c>
       <c r="F22" t="str">
-        <v>1,339</v>
+        <v>1,418</v>
       </c>
       <c r="G22" t="str">
-        <v>564,709</v>
+        <v>585,427</v>
       </c>
       <c r="H22" t="str">
         <v>43</v>
@@ -1358,13 +1358,13 @@
         <v>167,076,150</v>
       </c>
       <c r="L22" t="str">
-        <v>64,004,111,510</v>
+        <v>65,179,440,324</v>
       </c>
       <c r="M22" t="str">
-        <v>2,410,661,725</v>
+        <v>2,523,651,593</v>
       </c>
       <c r="N22" t="str">
-        <v>3.77%</v>
+        <v>3.87%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,106</v>
+        <v>8,118</v>
       </c>
       <c r="F24" t="str">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G24" t="str">
-        <v>75,272</v>
+        <v>77,959</v>
       </c>
       <c r="H24" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I24" t="str">
-        <v>282,826,900</v>
+        <v>305,826,900</v>
       </c>
       <c r="J24" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K24" t="str">
-        <v>184,925,540</v>
+        <v>231,125,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,500,896,550</v>
+        <v>52,513,314,612</v>
       </c>
       <c r="M24" t="str">
-        <v>631,709,106</v>
+        <v>692,722,658</v>
       </c>
       <c r="N24" t="str">
-        <v>1.20%</v>
+        <v>1.32%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,19 +1513,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>34,772</v>
+        <v>36,173</v>
       </c>
       <c r="F26" t="str">
-        <v>11,182</v>
+        <v>11,636</v>
       </c>
       <c r="G26" t="str">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H26" t="str">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I26" t="str">
-        <v>186,961,752</v>
+        <v>219,080,130</v>
       </c>
       <c r="J26" t="str">
         <v>10</v>
@@ -1534,13 +1534,13 @@
         <v>184,331,633</v>
       </c>
       <c r="L26" t="str">
-        <v>75,259,522,727</v>
+        <v>78,154,531,984</v>
       </c>
       <c r="M26" t="str">
-        <v>26,411,435,070</v>
+        <v>27,463,505,612</v>
       </c>
       <c r="N26" t="str">
-        <v>35.09%</v>
+        <v>35.14%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>5,327</v>
+        <v>5,519</v>
       </c>
       <c r="F27" t="str">
-        <v>2,907</v>
+        <v>3,020</v>
       </c>
       <c r="G27" t="str">
-        <v>5,389</v>
+        <v>5,600</v>
       </c>
       <c r="H27" t="str">
-        <v>821</v>
+        <v>861</v>
       </c>
       <c r="I27" t="str">
-        <v>10,232,156,576</v>
+        <v>10,718,436,007</v>
       </c>
       <c r="J27" t="str">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="K27" t="str">
-        <v>13,822,884,424</v>
+        <v>14,391,244,409</v>
       </c>
       <c r="L27" t="str">
-        <v>66,132,462,577</v>
+        <v>68,561,878,056</v>
       </c>
       <c r="M27" t="str">
-        <v>31,213,543,660</v>
+        <v>32,511,233,220</v>
       </c>
       <c r="N27" t="str">
-        <v>47.20%</v>
+        <v>47.42%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>5,068</v>
+        <v>5,196</v>
       </c>
       <c r="F28" t="str">
-        <v>2,578</v>
+        <v>2,661</v>
       </c>
       <c r="G28" t="str">
-        <v>5,083</v>
+        <v>5,235</v>
       </c>
       <c r="H28" t="str">
-        <v>798</v>
+        <v>833</v>
       </c>
       <c r="I28" t="str">
-        <v>9,993,266,238</v>
+        <v>10,422,876,411</v>
       </c>
       <c r="J28" t="str">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="K28" t="str">
-        <v>12,749,154,352</v>
+        <v>13,071,485,880</v>
       </c>
       <c r="L28" t="str">
-        <v>62,786,819,163</v>
+        <v>64,381,814,541</v>
       </c>
       <c r="M28" t="str">
-        <v>29,104,604,417</v>
+        <v>29,998,715,067</v>
       </c>
       <c r="N28" t="str">
-        <v>46.35%</v>
+        <v>46.60%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>3,275</v>
+        <v>3,369</v>
       </c>
       <c r="F29" t="str">
-        <v>1,703</v>
+        <v>1,770</v>
       </c>
       <c r="G29" t="str">
-        <v>3,416</v>
+        <v>3,526</v>
       </c>
       <c r="H29" t="str">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="I29" t="str">
-        <v>6,456,881,510</v>
+        <v>6,719,489,811</v>
       </c>
       <c r="J29" t="str">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="K29" t="str">
-        <v>9,423,353,384</v>
+        <v>9,823,707,908</v>
       </c>
       <c r="L29" t="str">
-        <v>40,603,643,969</v>
+        <v>41,841,251,754</v>
       </c>
       <c r="M29" t="str">
-        <v>19,446,503,878</v>
+        <v>20,204,620,048</v>
       </c>
       <c r="N29" t="str">
-        <v>47.89%</v>
+        <v>48.29%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>36,009</v>
+        <v>37,435</v>
       </c>
       <c r="F30" t="str">
-        <v>11,869</v>
+        <v>12,361</v>
       </c>
       <c r="G30" t="str">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H30" t="str">
         <v>16</v>
@@ -1710,13 +1710,13 @@
         <v>223,318,503</v>
       </c>
       <c r="L30" t="str">
-        <v>77,781,665,891</v>
+        <v>80,796,371,078</v>
       </c>
       <c r="M30" t="str">
-        <v>28,200,148,077</v>
+        <v>29,398,222,024</v>
       </c>
       <c r="N30" t="str">
-        <v>36.26%</v>
+        <v>36.39%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,248</v>
+        <v>3,368</v>
       </c>
       <c r="F31" t="str">
-        <v>1,450</v>
+        <v>1,496</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,244,334,541</v>
+        <v>1,287,471,917</v>
       </c>
       <c r="M31" t="str">
-        <v>561,949,066</v>
+        <v>579,091,942</v>
       </c>
       <c r="N31" t="str">
-        <v>45.16%</v>
+        <v>44.98%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,176</v>
+        <v>2,254</v>
       </c>
       <c r="F32" t="str">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="G32" t="str">
         <v>22</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,848,903,089</v>
+        <v>3,969,198,160</v>
       </c>
       <c r="M32" t="str">
-        <v>609,292,040</v>
+        <v>644,017,519</v>
       </c>
       <c r="N32" t="str">
-        <v>15.83%</v>
+        <v>16.23%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,726</v>
+        <v>2,823</v>
       </c>
       <c r="F33" t="str">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="G33" t="str">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>4,727,254,827</v>
+        <v>4,873,735,986</v>
       </c>
       <c r="M33" t="str">
-        <v>679,567,342</v>
+        <v>699,935,769</v>
       </c>
       <c r="N33" t="str">
-        <v>14.38%</v>
+        <v>14.36%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>11,447</v>
+        <v>11,916</v>
       </c>
       <c r="F34" t="str">
-        <v>1,896</v>
+        <v>1,970</v>
       </c>
       <c r="G34" t="str">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>21,104,575,264</v>
+        <v>21,946,005,874</v>
       </c>
       <c r="M34" t="str">
-        <v>2,963,795,574</v>
+        <v>3,064,855,968</v>
       </c>
       <c r="N34" t="str">
-        <v>14.04%</v>
+        <v>13.97%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>2,240</v>
+        <v>2,304</v>
       </c>
       <c r="F35" t="str">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="G35" t="str">
-        <v>7,098</v>
+        <v>7,332</v>
       </c>
       <c r="H35" t="str">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="I35" t="str">
-        <v>1,576,403,351</v>
+        <v>1,725,251,764</v>
       </c>
       <c r="J35" t="str">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K35" t="str">
-        <v>1,414,078,447</v>
+        <v>1,504,762,781</v>
       </c>
       <c r="L35" t="str">
-        <v>24,772,064,069</v>
+        <v>25,621,356,514</v>
       </c>
       <c r="M35" t="str">
-        <v>4,241,581,222</v>
+        <v>4,543,212,026</v>
       </c>
       <c r="N35" t="str">
-        <v>17.12%</v>
+        <v>17.73%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,19 +1953,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,862</v>
+        <v>1,916</v>
       </c>
       <c r="F36" t="str">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="G36" t="str">
-        <v>5,279</v>
+        <v>5,492</v>
       </c>
       <c r="H36" t="str">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I36" t="str">
-        <v>1,029,012,034</v>
+        <v>1,087,808,495</v>
       </c>
       <c r="J36" t="str">
         <v>56</v>
@@ -1974,13 +1974,13 @@
         <v>1,097,498,183</v>
       </c>
       <c r="L36" t="str">
-        <v>20,252,813,524</v>
+        <v>20,786,665,459</v>
       </c>
       <c r="M36" t="str">
-        <v>3,206,385,120</v>
+        <v>3,303,200,249</v>
       </c>
       <c r="N36" t="str">
-        <v>15.83%</v>
+        <v>15.89%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>10,392</v>
+        <v>10,757</v>
       </c>
       <c r="F37" t="str">
-        <v>1,632</v>
+        <v>1,680</v>
       </c>
       <c r="G37" t="str">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="H37" t="str">
         <v>4</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>18,637,168,553</v>
+        <v>19,316,347,287</v>
       </c>
       <c r="M37" t="str">
-        <v>3,206,959,694</v>
+        <v>3,277,826,879</v>
       </c>
       <c r="N37" t="str">
-        <v>17.21%</v>
+        <v>16.97%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,144</v>
+        <v>1,195</v>
       </c>
       <c r="F38" t="str">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>508,563,729</v>
+        <v>528,301,706</v>
       </c>
       <c r="M38" t="str">
-        <v>121,469,949</v>
+        <v>125,092,423</v>
       </c>
       <c r="N38" t="str">
-        <v>23.88%</v>
+        <v>23.68%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,455</v>
+        <v>3,570</v>
       </c>
       <c r="F39" t="str">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="G39" t="str">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>6,275,964,458</v>
+        <v>6,458,310,921</v>
       </c>
       <c r="M39" t="str">
-        <v>855,056,549</v>
+        <v>891,012,260</v>
       </c>
       <c r="N39" t="str">
-        <v>13.62%</v>
+        <v>13.80%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>3,118</v>
+        <v>3,282</v>
       </c>
       <c r="F41" t="str">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>5,560,606,590</v>
+        <v>5,846,216,588</v>
       </c>
       <c r="M41" t="str">
-        <v>802,116,168</v>
+        <v>845,586,394</v>
       </c>
       <c r="N41" t="str">
-        <v>14.42%</v>
+        <v>14.46%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>3,271</v>
+        <v>3,423</v>
       </c>
       <c r="F42" t="str">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="G42" t="str">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>6,057,667,663</v>
+        <v>6,332,778,347</v>
       </c>
       <c r="M42" t="str">
-        <v>870,686,680</v>
+        <v>899,676,000</v>
       </c>
       <c r="N42" t="str">
-        <v>14.37%</v>
+        <v>14.21%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>9,350</v>
+        <v>9,575</v>
       </c>
       <c r="F43" t="str">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="G43" t="str">
-        <v>12,260</v>
+        <v>12,628</v>
       </c>
       <c r="H43" t="str">
         <v>6</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>25,997,804,558</v>
+        <v>26,551,333,632</v>
       </c>
       <c r="M43" t="str">
-        <v>867,782,509</v>
+        <v>897,211,806</v>
       </c>
       <c r="N43" t="str">
-        <v>3.34%</v>
+        <v>3.38%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>12,820</v>
+        <v>13,158</v>
       </c>
       <c r="F44" t="str">
-        <v>614</v>
+        <v>641</v>
       </c>
       <c r="G44" t="str">
-        <v>17,361</v>
+        <v>17,905</v>
       </c>
       <c r="H44" t="str">
         <v>23</v>
@@ -2326,13 +2326,13 @@
         <v>280,029,887</v>
       </c>
       <c r="L44" t="str">
-        <v>36,015,082,857</v>
+        <v>36,862,058,895</v>
       </c>
       <c r="M44" t="str">
-        <v>1,644,055,547</v>
+        <v>1,698,633,493</v>
       </c>
       <c r="N44" t="str">
-        <v>4.56%</v>
+        <v>4.61%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>980</v>
+        <v>1,244</v>
       </c>
       <c r="F45" t="str">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G45" t="str">
-        <v>317</v>
+        <v>413</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>3,712,973,701</v>
+        <v>4,405,200,396</v>
       </c>
       <c r="M45" t="str">
-        <v>116,647,604</v>
+        <v>125,526,408</v>
       </c>
       <c r="N45" t="str">
-        <v>3.14%</v>
+        <v>2.85%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,19 +2393,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>8,585</v>
+        <v>8,834</v>
       </c>
       <c r="F46" t="str">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="G46" t="str">
-        <v>10,383</v>
+        <v>10,770</v>
       </c>
       <c r="H46" t="str">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I46" t="str">
-        <v>261,588,148</v>
+        <v>271,588,148</v>
       </c>
       <c r="J46" t="str">
         <v>9</v>
@@ -2414,13 +2414,13 @@
         <v>158,259,221</v>
       </c>
       <c r="L46" t="str">
-        <v>24,157,009,925</v>
+        <v>24,785,550,180</v>
       </c>
       <c r="M46" t="str">
-        <v>1,212,294,918</v>
+        <v>1,263,223,552</v>
       </c>
       <c r="N46" t="str">
-        <v>5.02%</v>
+        <v>5.10%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="F47" t="str">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G47" t="str">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,13 +2458,13 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>386,947,199</v>
+        <v>399,742,222</v>
       </c>
       <c r="M47" t="str">
-        <v>46,862,614</v>
+        <v>47,530,075</v>
       </c>
       <c r="N47" t="str">
-        <v>12.11%</v>
+        <v>11.89%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,13 +457,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>5,906</v>
+        <v>6,112</v>
       </c>
       <c r="F2" t="str">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="G2" t="str">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="H2" t="str">
         <v>29</v>
@@ -472,19 +472,19 @@
         <v>348,366,698</v>
       </c>
       <c r="J2" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" t="str">
-        <v>140,563,756</v>
+        <v>160,929,681</v>
       </c>
       <c r="L2" t="str">
-        <v>25,841,422,977</v>
+        <v>26,802,584,972</v>
       </c>
       <c r="M2" t="str">
-        <v>1,401,724,306</v>
+        <v>1,444,348,156</v>
       </c>
       <c r="N2" t="str">
-        <v>5.42%</v>
+        <v>5.39%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,814</v>
+        <v>3,976</v>
       </c>
       <c r="F3" t="str">
-        <v>1,010</v>
+        <v>1,070</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>7,109,398,906</v>
+        <v>7,386,032,896</v>
       </c>
       <c r="M3" t="str">
-        <v>1,765,155,101</v>
+        <v>1,855,147,643</v>
       </c>
       <c r="N3" t="str">
-        <v>24.83%</v>
+        <v>25.12%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>15,376</v>
+        <v>16,029</v>
       </c>
       <c r="F4" t="str">
-        <v>4,368</v>
+        <v>4,561</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>28,301,941,661</v>
+        <v>29,423,837,230</v>
       </c>
       <c r="M4" t="str">
-        <v>7,750,036,533</v>
+        <v>8,082,405,099</v>
       </c>
       <c r="N4" t="str">
-        <v>27.38%</v>
+        <v>27.47%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,571</v>
+        <v>1,607</v>
       </c>
       <c r="F5" t="str">
-        <v>656</v>
+        <v>682</v>
       </c>
       <c r="G5" t="str">
-        <v>943</v>
+        <v>968</v>
       </c>
       <c r="H5" t="str">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="I5" t="str">
-        <v>2,341,499,574</v>
+        <v>2,431,354,305</v>
       </c>
       <c r="J5" t="str">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K5" t="str">
-        <v>2,291,604,326</v>
+        <v>2,369,034,850</v>
       </c>
       <c r="L5" t="str">
-        <v>18,667,635,575</v>
+        <v>19,116,448,297</v>
       </c>
       <c r="M5" t="str">
-        <v>6,657,847,697</v>
+        <v>6,912,824,706</v>
       </c>
       <c r="N5" t="str">
-        <v>35.67%</v>
+        <v>36.16%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>2,160</v>
+        <v>2,214</v>
       </c>
       <c r="F6" t="str">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="G6" t="str">
-        <v>1,257</v>
+        <v>1,295</v>
       </c>
       <c r="H6" t="str">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I6" t="str">
-        <v>2,873,996,821</v>
+        <v>2,973,186,640</v>
       </c>
       <c r="J6" t="str">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K6" t="str">
-        <v>2,430,050,785</v>
+        <v>2,448,790,205</v>
       </c>
       <c r="L6" t="str">
-        <v>25,549,576,519</v>
+        <v>26,214,369,155</v>
       </c>
       <c r="M6" t="str">
-        <v>8,238,760,838</v>
+        <v>8,422,008,785</v>
       </c>
       <c r="N6" t="str">
-        <v>32.25%</v>
+        <v>32.13%</v>
       </c>
     </row>
     <row r="7">
@@ -677,19 +677,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,907</v>
+        <v>1,955</v>
       </c>
       <c r="F7" t="str">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="G7" t="str">
-        <v>1,132</v>
+        <v>1,167</v>
       </c>
       <c r="H7" t="str">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I7" t="str">
-        <v>2,760,674,835</v>
+        <v>2,844,655,108</v>
       </c>
       <c r="J7" t="str">
         <v>105</v>
@@ -698,13 +698,13 @@
         <v>2,076,715,214</v>
       </c>
       <c r="L7" t="str">
-        <v>22,503,810,503</v>
+        <v>23,098,660,573</v>
       </c>
       <c r="M7" t="str">
-        <v>7,276,932,759</v>
+        <v>7,427,264,561</v>
       </c>
       <c r="N7" t="str">
-        <v>32.34%</v>
+        <v>32.15%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>953</v>
+        <v>976</v>
       </c>
       <c r="F8" t="str">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="G8" t="str">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H8" t="str">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I8" t="str">
-        <v>1,204,476,816</v>
+        <v>1,257,472,487</v>
       </c>
       <c r="J8" t="str">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K8" t="str">
-        <v>1,162,225,963</v>
+        <v>1,201,867,243</v>
       </c>
       <c r="L8" t="str">
-        <v>11,438,476,742</v>
+        <v>11,725,230,808</v>
       </c>
       <c r="M8" t="str">
-        <v>3,645,621,734</v>
+        <v>3,752,430,385</v>
       </c>
       <c r="N8" t="str">
-        <v>31.87%</v>
+        <v>32.00%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>23,519</v>
+        <v>24,492</v>
       </c>
       <c r="F9" t="str">
-        <v>6,408</v>
+        <v>6,692</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>43,168,262,479</v>
+        <v>44,879,607,820</v>
       </c>
       <c r="M9" t="str">
-        <v>11,274,069,123</v>
+        <v>11,749,209,126</v>
       </c>
       <c r="N9" t="str">
-        <v>26.12%</v>
+        <v>26.18%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,378</v>
+        <v>2,467</v>
       </c>
       <c r="F10" t="str">
-        <v>1,121</v>
+        <v>1,166</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>804,936,517</v>
+        <v>837,990,395</v>
       </c>
       <c r="M10" t="str">
-        <v>342,792,359</v>
+        <v>357,311,014</v>
       </c>
       <c r="N10" t="str">
-        <v>42.59%</v>
+        <v>42.64%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>4,239</v>
+        <v>4,414</v>
       </c>
       <c r="F11" t="str">
-        <v>1,176</v>
+        <v>1,219</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>7,961,069,597</v>
+        <v>8,234,071,607</v>
       </c>
       <c r="M11" t="str">
-        <v>2,047,721,966</v>
+        <v>2,109,379,478</v>
       </c>
       <c r="N11" t="str">
-        <v>25.72%</v>
+        <v>25.62%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,406</v>
+        <v>3,568</v>
       </c>
       <c r="F12" t="str">
-        <v>975</v>
+        <v>1,022</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>6,368,343,093</v>
+        <v>6,664,628,031</v>
       </c>
       <c r="M12" t="str">
-        <v>1,712,465,656</v>
+        <v>1,804,653,447</v>
       </c>
       <c r="N12" t="str">
-        <v>26.89%</v>
+        <v>27.08%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>4,974</v>
+        <v>5,155</v>
       </c>
       <c r="F13" t="str">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G13" t="str">
-        <v>9,158</v>
+        <v>9,525</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>15,886,812,980</v>
+        <v>16,500,421,620</v>
       </c>
       <c r="M13" t="str">
-        <v>168,660,609</v>
+        <v>179,009,854</v>
       </c>
       <c r="N13" t="str">
-        <v>1.06%</v>
+        <v>1.08%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>13,951</v>
+        <v>14,462</v>
       </c>
       <c r="F14" t="str">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G14" t="str">
-        <v>30,566</v>
+        <v>31,507</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>71,755,405</v>
       </c>
       <c r="L14" t="str">
-        <v>43,763,579,633</v>
+        <v>45,269,181,443</v>
       </c>
       <c r="M14" t="str">
-        <v>516,467,318</v>
+        <v>537,366,326</v>
       </c>
       <c r="N14" t="str">
-        <v>1.18%</v>
+        <v>1.19%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>9,956</v>
+        <v>10,318</v>
       </c>
       <c r="F15" t="str">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G15" t="str">
-        <v>21,803</v>
+        <v>22,459</v>
       </c>
       <c r="H15" t="str">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>176,637,045</v>
       </c>
       <c r="L15" t="str">
-        <v>31,409,935,567</v>
+        <v>32,560,427,949</v>
       </c>
       <c r="M15" t="str">
-        <v>565,129,223</v>
+        <v>572,891,223</v>
       </c>
       <c r="N15" t="str">
-        <v>1.80%</v>
+        <v>1.76%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="F16" t="str">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G16" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>550,890,122</v>
+        <v>564,724,466</v>
       </c>
       <c r="M16" t="str">
-        <v>7,790,238</v>
+        <v>9,695,715</v>
       </c>
       <c r="N16" t="str">
-        <v>1.41%</v>
+        <v>1.72%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>18,296</v>
+        <v>18,972</v>
       </c>
       <c r="F17" t="str">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="G17" t="str">
-        <v>78,411</v>
+        <v>80,626</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>71,805,230,049</v>
+        <v>74,340,829,058</v>
       </c>
       <c r="M17" t="str">
-        <v>366,701,935</v>
+        <v>399,086,492</v>
       </c>
       <c r="N17" t="str">
-        <v>0.51%</v>
+        <v>0.54%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,591</v>
+        <v>1,649</v>
       </c>
       <c r="F18" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" t="str">
-        <v>6,788</v>
+        <v>6,987</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>6,218,963,430</v>
+        <v>6,495,472,380</v>
       </c>
       <c r="M18" t="str">
-        <v>20,619,311</v>
+        <v>24,927,311</v>
       </c>
       <c r="N18" t="str">
-        <v>0.33%</v>
+        <v>0.38%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>7,153</v>
+        <v>7,417</v>
       </c>
       <c r="F19" t="str">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" t="str">
-        <v>29,805</v>
+        <v>30,737</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>28,789,479,312</v>
+        <v>29,825,888,598</v>
       </c>
       <c r="M19" t="str">
-        <v>151,367,379</v>
+        <v>153,577,379</v>
       </c>
       <c r="N19" t="str">
-        <v>0.53%</v>
+        <v>0.51%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,301</v>
+        <v>3,308</v>
       </c>
       <c r="F20" t="str">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G20" t="str">
-        <v>23,411</v>
+        <v>24,227</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,983,541,955</v>
+        <v>11,989,366,101</v>
       </c>
       <c r="M20" t="str">
-        <v>190,429,687</v>
+        <v>198,094,371</v>
       </c>
       <c r="N20" t="str">
-        <v>1.59%</v>
+        <v>1.65%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,982</v>
+        <v>2,996</v>
       </c>
       <c r="F21" t="str">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G21" t="str">
-        <v>151,428</v>
+        <v>156,646</v>
       </c>
       <c r="H21" t="str">
         <v>5</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>9,064,007,599</v>
+        <v>9,071,289,286</v>
       </c>
       <c r="M21" t="str">
-        <v>359,530,255</v>
+        <v>370,683,171</v>
       </c>
       <c r="N21" t="str">
-        <v>3.97%</v>
+        <v>4.09%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,34 +1337,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>13,618</v>
+        <v>13,901</v>
       </c>
       <c r="F22" t="str">
-        <v>1,418</v>
+        <v>1,551</v>
       </c>
       <c r="G22" t="str">
-        <v>585,427</v>
+        <v>606,177</v>
       </c>
       <c r="H22" t="str">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I22" t="str">
-        <v>540,443,400</v>
+        <v>615,443,400</v>
       </c>
       <c r="J22" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K22" t="str">
-        <v>167,076,150</v>
+        <v>199,076,150</v>
       </c>
       <c r="L22" t="str">
-        <v>65,179,440,324</v>
+        <v>66,410,376,784</v>
       </c>
       <c r="M22" t="str">
-        <v>2,523,651,593</v>
+        <v>2,763,895,296</v>
       </c>
       <c r="N22" t="str">
-        <v>3.87%</v>
+        <v>4.16%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,118</v>
+        <v>8,136</v>
       </c>
       <c r="F24" t="str">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="G24" t="str">
-        <v>77,959</v>
+        <v>80,643</v>
       </c>
       <c r="H24" t="str">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I24" t="str">
-        <v>305,826,900</v>
+        <v>331,826,900</v>
       </c>
       <c r="J24" t="str">
         <v>13</v>
@@ -1446,13 +1446,13 @@
         <v>231,125,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,513,314,612</v>
+        <v>52,523,902,565</v>
       </c>
       <c r="M24" t="str">
-        <v>692,722,658</v>
+        <v>755,825,698</v>
       </c>
       <c r="N24" t="str">
-        <v>1.32%</v>
+        <v>1.44%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,19 +1513,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>36,173</v>
+        <v>37,553</v>
       </c>
       <c r="F26" t="str">
-        <v>11,636</v>
+        <v>12,121</v>
       </c>
       <c r="G26" t="str">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H26" t="str">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I26" t="str">
-        <v>219,080,130</v>
+        <v>242,345,610</v>
       </c>
       <c r="J26" t="str">
         <v>10</v>
@@ -1534,13 +1534,13 @@
         <v>184,331,633</v>
       </c>
       <c r="L26" t="str">
-        <v>78,154,531,984</v>
+        <v>80,869,172,967</v>
       </c>
       <c r="M26" t="str">
-        <v>27,463,505,612</v>
+        <v>28,478,648,167</v>
       </c>
       <c r="N26" t="str">
-        <v>35.14%</v>
+        <v>35.22%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>5,519</v>
+        <v>5,688</v>
       </c>
       <c r="F27" t="str">
-        <v>3,020</v>
+        <v>3,107</v>
       </c>
       <c r="G27" t="str">
-        <v>5,600</v>
+        <v>5,795</v>
       </c>
       <c r="H27" t="str">
-        <v>861</v>
+        <v>890</v>
       </c>
       <c r="I27" t="str">
-        <v>10,718,436,007</v>
+        <v>11,079,184,633</v>
       </c>
       <c r="J27" t="str">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="K27" t="str">
-        <v>14,391,244,409</v>
+        <v>14,902,689,021</v>
       </c>
       <c r="L27" t="str">
-        <v>68,561,878,056</v>
+        <v>70,731,549,367</v>
       </c>
       <c r="M27" t="str">
-        <v>32,511,233,220</v>
+        <v>33,515,639,456</v>
       </c>
       <c r="N27" t="str">
-        <v>47.42%</v>
+        <v>47.38%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>5,196</v>
+        <v>5,364</v>
       </c>
       <c r="F28" t="str">
-        <v>2,661</v>
+        <v>2,734</v>
       </c>
       <c r="G28" t="str">
-        <v>5,235</v>
+        <v>5,402</v>
       </c>
       <c r="H28" t="str">
-        <v>833</v>
+        <v>852</v>
       </c>
       <c r="I28" t="str">
-        <v>10,422,876,411</v>
+        <v>10,657,848,057</v>
       </c>
       <c r="J28" t="str">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="K28" t="str">
-        <v>13,071,485,880</v>
+        <v>13,520,709,523</v>
       </c>
       <c r="L28" t="str">
-        <v>64,381,814,541</v>
+        <v>66,538,859,221</v>
       </c>
       <c r="M28" t="str">
-        <v>29,998,715,067</v>
+        <v>30,843,143,867</v>
       </c>
       <c r="N28" t="str">
-        <v>46.60%</v>
+        <v>46.35%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>3,369</v>
+        <v>3,470</v>
       </c>
       <c r="F29" t="str">
-        <v>1,770</v>
+        <v>1,829</v>
       </c>
       <c r="G29" t="str">
-        <v>3,526</v>
+        <v>3,635</v>
       </c>
       <c r="H29" t="str">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="I29" t="str">
-        <v>6,719,489,811</v>
+        <v>6,863,575,165</v>
       </c>
       <c r="J29" t="str">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="K29" t="str">
-        <v>9,823,707,908</v>
+        <v>10,042,183,303</v>
       </c>
       <c r="L29" t="str">
-        <v>41,841,251,754</v>
+        <v>43,116,749,808</v>
       </c>
       <c r="M29" t="str">
-        <v>20,204,620,048</v>
+        <v>20,775,417,289</v>
       </c>
       <c r="N29" t="str">
-        <v>48.29%</v>
+        <v>48.18%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>37,435</v>
+        <v>38,821</v>
       </c>
       <c r="F30" t="str">
-        <v>12,361</v>
+        <v>12,861</v>
       </c>
       <c r="G30" t="str">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H30" t="str">
         <v>16</v>
@@ -1710,13 +1710,13 @@
         <v>223,318,503</v>
       </c>
       <c r="L30" t="str">
-        <v>80,796,371,078</v>
+        <v>83,662,804,698</v>
       </c>
       <c r="M30" t="str">
-        <v>29,398,222,024</v>
+        <v>30,468,556,159</v>
       </c>
       <c r="N30" t="str">
-        <v>36.39%</v>
+        <v>36.42%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,368</v>
+        <v>3,489</v>
       </c>
       <c r="F31" t="str">
-        <v>1,496</v>
+        <v>1,554</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,287,471,917</v>
+        <v>1,338,529,502</v>
       </c>
       <c r="M31" t="str">
-        <v>579,091,942</v>
+        <v>601,322,073</v>
       </c>
       <c r="N31" t="str">
-        <v>44.98%</v>
+        <v>44.92%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,254</v>
+        <v>2,351</v>
       </c>
       <c r="F32" t="str">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G32" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>3,969,198,160</v>
+        <v>4,121,453,636</v>
       </c>
       <c r="M32" t="str">
-        <v>644,017,519</v>
+        <v>671,048,658</v>
       </c>
       <c r="N32" t="str">
-        <v>16.23%</v>
+        <v>16.28%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,823</v>
+        <v>2,947</v>
       </c>
       <c r="F33" t="str">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="G33" t="str">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>4,873,735,986</v>
+        <v>5,114,690,074</v>
       </c>
       <c r="M33" t="str">
-        <v>699,935,769</v>
+        <v>736,647,721</v>
       </c>
       <c r="N33" t="str">
-        <v>14.36%</v>
+        <v>14.40%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>11,916</v>
+        <v>12,469</v>
       </c>
       <c r="F34" t="str">
-        <v>1,970</v>
+        <v>2,077</v>
       </c>
       <c r="G34" t="str">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>21,946,005,874</v>
+        <v>22,832,288,997</v>
       </c>
       <c r="M34" t="str">
-        <v>3,064,855,968</v>
+        <v>3,225,783,510</v>
       </c>
       <c r="N34" t="str">
-        <v>13.97%</v>
+        <v>14.13%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,19 +1909,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>2,304</v>
+        <v>2,360</v>
       </c>
       <c r="F35" t="str">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="G35" t="str">
-        <v>7,332</v>
+        <v>7,546</v>
       </c>
       <c r="H35" t="str">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I35" t="str">
-        <v>1,725,251,764</v>
+        <v>1,773,578,007</v>
       </c>
       <c r="J35" t="str">
         <v>77</v>
@@ -1930,13 +1930,13 @@
         <v>1,504,762,781</v>
       </c>
       <c r="L35" t="str">
-        <v>25,621,356,514</v>
+        <v>26,296,587,259</v>
       </c>
       <c r="M35" t="str">
-        <v>4,543,212,026</v>
+        <v>4,629,967,475</v>
       </c>
       <c r="N35" t="str">
-        <v>17.73%</v>
+        <v>17.61%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,34 +1953,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,916</v>
+        <v>1,990</v>
       </c>
       <c r="F36" t="str">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="G36" t="str">
-        <v>5,492</v>
+        <v>5,694</v>
       </c>
       <c r="H36" t="str">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I36" t="str">
-        <v>1,087,808,495</v>
+        <v>1,125,517,570</v>
       </c>
       <c r="J36" t="str">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K36" t="str">
-        <v>1,097,498,183</v>
+        <v>1,130,617,732</v>
       </c>
       <c r="L36" t="str">
-        <v>20,786,665,459</v>
+        <v>21,524,850,781</v>
       </c>
       <c r="M36" t="str">
-        <v>3,303,200,249</v>
+        <v>3,428,641,839</v>
       </c>
       <c r="N36" t="str">
-        <v>15.89%</v>
+        <v>15.93%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>10,757</v>
+        <v>11,175</v>
       </c>
       <c r="F37" t="str">
-        <v>1,680</v>
+        <v>1,762</v>
       </c>
       <c r="G37" t="str">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="H37" t="str">
         <v>4</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>19,316,347,287</v>
+        <v>19,986,503,712</v>
       </c>
       <c r="M37" t="str">
-        <v>3,277,826,879</v>
+        <v>3,386,077,810</v>
       </c>
       <c r="N37" t="str">
-        <v>16.97%</v>
+        <v>16.94%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,195</v>
+        <v>1,241</v>
       </c>
       <c r="F38" t="str">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>528,301,706</v>
+        <v>549,119,447</v>
       </c>
       <c r="M38" t="str">
-        <v>125,092,423</v>
+        <v>139,044,438</v>
       </c>
       <c r="N38" t="str">
-        <v>23.68%</v>
+        <v>25.32%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,570</v>
+        <v>3,717</v>
       </c>
       <c r="F39" t="str">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="G39" t="str">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>6,458,310,921</v>
+        <v>6,689,591,045</v>
       </c>
       <c r="M39" t="str">
-        <v>891,012,260</v>
+        <v>940,047,375</v>
       </c>
       <c r="N39" t="str">
-        <v>13.80%</v>
+        <v>14.05%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>3,282</v>
+        <v>3,442</v>
       </c>
       <c r="F41" t="str">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>5,846,216,588</v>
+        <v>6,109,734,043</v>
       </c>
       <c r="M41" t="str">
-        <v>845,586,394</v>
+        <v>890,470,289</v>
       </c>
       <c r="N41" t="str">
-        <v>14.46%</v>
+        <v>14.57%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>3,423</v>
+        <v>3,522</v>
       </c>
       <c r="F42" t="str">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="G42" t="str">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>6,332,778,347</v>
+        <v>6,515,892,055</v>
       </c>
       <c r="M42" t="str">
-        <v>899,676,000</v>
+        <v>928,778,434</v>
       </c>
       <c r="N42" t="str">
-        <v>14.21%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>9,575</v>
+        <v>9,810</v>
       </c>
       <c r="F43" t="str">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="G43" t="str">
-        <v>12,628</v>
+        <v>12,992</v>
       </c>
       <c r="H43" t="str">
         <v>6</v>
@@ -2282,13 +2282,13 @@
         <v>35,905,362</v>
       </c>
       <c r="L43" t="str">
-        <v>26,551,333,632</v>
+        <v>27,294,973,703</v>
       </c>
       <c r="M43" t="str">
-        <v>897,211,806</v>
+        <v>935,093,259</v>
       </c>
       <c r="N43" t="str">
-        <v>3.38%</v>
+        <v>3.43%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,34 +2305,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>13,158</v>
+        <v>13,511</v>
       </c>
       <c r="F44" t="str">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="G44" t="str">
-        <v>17,905</v>
+        <v>18,448</v>
       </c>
       <c r="H44" t="str">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I44" t="str">
-        <v>266,187,987</v>
+        <v>287,437,633</v>
       </c>
       <c r="J44" t="str">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K44" t="str">
-        <v>280,029,887</v>
+        <v>295,302,942</v>
       </c>
       <c r="L44" t="str">
-        <v>36,862,058,895</v>
+        <v>37,919,860,462</v>
       </c>
       <c r="M44" t="str">
-        <v>1,698,633,493</v>
+        <v>1,829,947,849</v>
       </c>
       <c r="N44" t="str">
-        <v>4.61%</v>
+        <v>4.83%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,244</v>
+        <v>1,524</v>
       </c>
       <c r="F45" t="str">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G45" t="str">
-        <v>413</v>
+        <v>531</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>4,405,200,396</v>
+        <v>5,335,924,985</v>
       </c>
       <c r="M45" t="str">
-        <v>125,526,408</v>
+        <v>158,023,856</v>
       </c>
       <c r="N45" t="str">
-        <v>2.85%</v>
+        <v>2.96%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>8,834</v>
+        <v>9,092</v>
       </c>
       <c r="F46" t="str">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="G46" t="str">
-        <v>10,770</v>
+        <v>11,167</v>
       </c>
       <c r="H46" t="str">
         <v>22</v>
@@ -2414,13 +2414,13 @@
         <v>158,259,221</v>
       </c>
       <c r="L46" t="str">
-        <v>24,785,550,180</v>
+        <v>25,656,392,672</v>
       </c>
       <c r="M46" t="str">
-        <v>1,263,223,552</v>
+        <v>1,310,752,731</v>
       </c>
       <c r="N46" t="str">
-        <v>5.10%</v>
+        <v>5.11%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>786</v>
+        <v>822</v>
       </c>
       <c r="F47" t="str">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G47" t="str">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2458,10 +2458,10 @@
         <v>18,808,290</v>
       </c>
       <c r="L47" t="str">
-        <v>399,742,222</v>
+        <v>415,553,850</v>
       </c>
       <c r="M47" t="str">
-        <v>47,530,075</v>
+        <v>49,421,914</v>
       </c>
       <c r="N47" t="str">
         <v>11.89%</v>

--- a/rawdata/Bulanan/10. Okt-SK.xlsx
+++ b/rawdata/Bulanan/10. Okt-SK.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>6,112</v>
+        <v>6,320</v>
       </c>
       <c r="F2" t="str">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="G2" t="str">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="H2" t="str">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I2" t="str">
-        <v>348,366,698</v>
+        <v>400,723,287</v>
       </c>
       <c r="J2" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K2" t="str">
-        <v>160,929,681</v>
+        <v>209,837,956</v>
       </c>
       <c r="L2" t="str">
-        <v>26,802,584,972</v>
+        <v>27,703,150,706</v>
       </c>
       <c r="M2" t="str">
-        <v>1,444,348,156</v>
+        <v>1,552,898,899</v>
       </c>
       <c r="N2" t="str">
-        <v>5.39%</v>
+        <v>5.61%</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>3,976</v>
+        <v>4,127</v>
       </c>
       <c r="F3" t="str">
-        <v>1,070</v>
+        <v>1,099</v>
       </c>
       <c r="G3" t="str">
         <v>0</v>
@@ -522,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>7,386,032,896</v>
+        <v>7,675,409,327</v>
       </c>
       <c r="M3" t="str">
-        <v>1,855,147,643</v>
+        <v>1,898,271,987</v>
       </c>
       <c r="N3" t="str">
-        <v>25.12%</v>
+        <v>24.73%</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>16,029</v>
+        <v>16,638</v>
       </c>
       <c r="F4" t="str">
-        <v>4,561</v>
+        <v>4,704</v>
       </c>
       <c r="G4" t="str">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>29,423,837,230</v>
+        <v>30,484,099,474</v>
       </c>
       <c r="M4" t="str">
-        <v>8,082,405,099</v>
+        <v>8,332,234,280</v>
       </c>
       <c r="N4" t="str">
-        <v>27.47%</v>
+        <v>27.33%</v>
       </c>
     </row>
     <row r="5">
@@ -589,34 +589,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>1,607</v>
+        <v>1,655</v>
       </c>
       <c r="F5" t="str">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="G5" t="str">
-        <v>968</v>
+        <v>1,002</v>
       </c>
       <c r="H5" t="str">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I5" t="str">
-        <v>2,431,354,305</v>
+        <v>2,472,735,274</v>
       </c>
       <c r="J5" t="str">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K5" t="str">
-        <v>2,369,034,850</v>
+        <v>2,482,464,007</v>
       </c>
       <c r="L5" t="str">
-        <v>19,116,448,297</v>
+        <v>19,758,885,591</v>
       </c>
       <c r="M5" t="str">
-        <v>6,912,824,706</v>
+        <v>7,127,348,884</v>
       </c>
       <c r="N5" t="str">
-        <v>36.16%</v>
+        <v>36.07%</v>
       </c>
     </row>
     <row r="6">
@@ -633,34 +633,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>2,214</v>
+        <v>2,274</v>
       </c>
       <c r="F6" t="str">
-        <v>882</v>
+        <v>910</v>
       </c>
       <c r="G6" t="str">
-        <v>1,295</v>
+        <v>1,338</v>
       </c>
       <c r="H6" t="str">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="I6" t="str">
-        <v>2,973,186,640</v>
+        <v>3,117,900,805</v>
       </c>
       <c r="J6" t="str">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K6" t="str">
-        <v>2,448,790,205</v>
+        <v>2,510,191,980</v>
       </c>
       <c r="L6" t="str">
-        <v>26,214,369,155</v>
+        <v>26,935,381,184</v>
       </c>
       <c r="M6" t="str">
-        <v>8,422,008,785</v>
+        <v>8,693,971,360</v>
       </c>
       <c r="N6" t="str">
-        <v>32.13%</v>
+        <v>32.28%</v>
       </c>
     </row>
     <row r="7">
@@ -677,19 +677,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>1,955</v>
+        <v>2,004</v>
       </c>
       <c r="F7" t="str">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="G7" t="str">
-        <v>1,167</v>
+        <v>1,197</v>
       </c>
       <c r="H7" t="str">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I7" t="str">
-        <v>2,844,655,108</v>
+        <v>2,902,857,397</v>
       </c>
       <c r="J7" t="str">
         <v>105</v>
@@ -698,13 +698,13 @@
         <v>2,076,715,214</v>
       </c>
       <c r="L7" t="str">
-        <v>23,098,660,573</v>
+        <v>23,636,814,328</v>
       </c>
       <c r="M7" t="str">
-        <v>7,427,264,561</v>
+        <v>7,544,785,961</v>
       </c>
       <c r="N7" t="str">
-        <v>32.15%</v>
+        <v>31.92%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>976</v>
+        <v>1,000</v>
       </c>
       <c r="F8" t="str">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="G8" t="str">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="H8" t="str">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I8" t="str">
-        <v>1,257,472,487</v>
+        <v>1,306,889,711</v>
       </c>
       <c r="J8" t="str">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K8" t="str">
-        <v>1,201,867,243</v>
+        <v>1,252,024,398</v>
       </c>
       <c r="L8" t="str">
-        <v>11,725,230,808</v>
+        <v>12,031,382,126</v>
       </c>
       <c r="M8" t="str">
-        <v>3,752,430,385</v>
+        <v>3,868,743,089</v>
       </c>
       <c r="N8" t="str">
-        <v>32.00%</v>
+        <v>32.16%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>24,492</v>
+        <v>25,421</v>
       </c>
       <c r="F9" t="str">
-        <v>6,692</v>
+        <v>6,932</v>
       </c>
       <c r="G9" t="str">
         <v>1</v>
@@ -786,13 +786,13 @@
         <v>28,104,690</v>
       </c>
       <c r="L9" t="str">
-        <v>44,879,607,820</v>
+        <v>46,444,054,609</v>
       </c>
       <c r="M9" t="str">
-        <v>11,749,209,126</v>
+        <v>12,127,217,429</v>
       </c>
       <c r="N9" t="str">
-        <v>26.18%</v>
+        <v>26.11%</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,467</v>
+        <v>2,555</v>
       </c>
       <c r="F10" t="str">
-        <v>1,166</v>
+        <v>1,214</v>
       </c>
       <c r="G10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>837,990,395</v>
+        <v>866,248,984</v>
       </c>
       <c r="M10" t="str">
-        <v>357,311,014</v>
+        <v>371,125,619</v>
       </c>
       <c r="N10" t="str">
-        <v>42.64%</v>
+        <v>42.84%</v>
       </c>
     </row>
     <row r="11">
@@ -853,10 +853,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>4,414</v>
+        <v>4,528</v>
       </c>
       <c r="F11" t="str">
-        <v>1,219</v>
+        <v>1,247</v>
       </c>
       <c r="G11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>8,234,071,607</v>
+        <v>8,426,446,747</v>
       </c>
       <c r="M11" t="str">
-        <v>2,109,379,478</v>
+        <v>2,150,978,724</v>
       </c>
       <c r="N11" t="str">
-        <v>25.62%</v>
+        <v>25.53%</v>
       </c>
     </row>
     <row r="12">
@@ -897,10 +897,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,568</v>
+        <v>3,679</v>
       </c>
       <c r="F12" t="str">
-        <v>1,022</v>
+        <v>1,059</v>
       </c>
       <c r="G12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>6,664,628,031</v>
+        <v>6,862,234,365</v>
       </c>
       <c r="M12" t="str">
-        <v>1,804,653,447</v>
+        <v>1,863,691,224</v>
       </c>
       <c r="N12" t="str">
-        <v>27.08%</v>
+        <v>27.16%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>5,155</v>
+        <v>5,315</v>
       </c>
       <c r="F13" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G13" t="str">
-        <v>9,525</v>
+        <v>9,887</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>19,352,560</v>
       </c>
       <c r="L13" t="str">
-        <v>16,500,421,620</v>
+        <v>16,957,974,662</v>
       </c>
       <c r="M13" t="str">
-        <v>179,009,854</v>
+        <v>179,553,148</v>
       </c>
       <c r="N13" t="str">
-        <v>1.08%</v>
+        <v>1.06%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>14,462</v>
+        <v>14,907</v>
       </c>
       <c r="F14" t="str">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G14" t="str">
-        <v>31,507</v>
+        <v>32,455</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>71,755,405</v>
       </c>
       <c r="L14" t="str">
-        <v>45,269,181,443</v>
+        <v>46,774,587,512</v>
       </c>
       <c r="M14" t="str">
-        <v>537,366,326</v>
+        <v>545,217,386</v>
       </c>
       <c r="N14" t="str">
-        <v>1.19%</v>
+        <v>1.17%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>10,318</v>
+        <v>10,637</v>
       </c>
       <c r="F15" t="str">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G15" t="str">
-        <v>22,459</v>
+        <v>23,100</v>
       </c>
       <c r="H15" t="str">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>176,637,045</v>
       </c>
       <c r="L15" t="str">
-        <v>32,560,427,949</v>
+        <v>33,493,653,693</v>
       </c>
       <c r="M15" t="str">
-        <v>572,891,223</v>
+        <v>579,478,411</v>
       </c>
       <c r="N15" t="str">
-        <v>1.76%</v>
+        <v>1.73%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="F16" t="str">
         <v>18</v>
       </c>
       <c r="G16" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>564,724,466</v>
+        <v>589,039,050</v>
       </c>
       <c r="M16" t="str">
         <v>9,695,715</v>
       </c>
       <c r="N16" t="str">
-        <v>1.72%</v>
+        <v>1.65%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>18,972</v>
+        <v>19,570</v>
       </c>
       <c r="F17" t="str">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G17" t="str">
-        <v>80,626</v>
+        <v>82,852</v>
       </c>
       <c r="H17" t="str">
         <v>6</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>74,340,829,058</v>
+        <v>76,736,373,241</v>
       </c>
       <c r="M17" t="str">
-        <v>399,086,492</v>
+        <v>407,649,675</v>
       </c>
       <c r="N17" t="str">
-        <v>0.54%</v>
+        <v>0.53%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>1,649</v>
+        <v>1,701</v>
       </c>
       <c r="F18" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" t="str">
-        <v>6,987</v>
+        <v>7,177</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>6,495,472,380</v>
+        <v>6,648,118,305</v>
       </c>
       <c r="M18" t="str">
-        <v>24,927,311</v>
+        <v>30,335,311</v>
       </c>
       <c r="N18" t="str">
-        <v>0.38%</v>
+        <v>0.46%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>7,417</v>
+        <v>7,651</v>
       </c>
       <c r="F19" t="str">
         <v>65</v>
       </c>
       <c r="G19" t="str">
-        <v>30,737</v>
+        <v>31,666</v>
       </c>
       <c r="H19" t="str">
         <v>5</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>29,825,888,598</v>
+        <v>30,746,677,024</v>
       </c>
       <c r="M19" t="str">
         <v>153,577,379</v>
       </c>
       <c r="N19" t="str">
-        <v>0.51%</v>
+        <v>0.50%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,308</v>
+        <v>3,317</v>
       </c>
       <c r="F20" t="str">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G20" t="str">
-        <v>24,227</v>
+        <v>25,043</v>
       </c>
       <c r="H20" t="str">
         <v>2</v>
@@ -1270,13 +1270,13 @@
         <v>67,103,720</v>
       </c>
       <c r="L20" t="str">
-        <v>11,989,366,101</v>
+        <v>11,992,323,619</v>
       </c>
       <c r="M20" t="str">
-        <v>198,094,371</v>
+        <v>204,578,738</v>
       </c>
       <c r="N20" t="str">
-        <v>1.65%</v>
+        <v>1.71%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>2,996</v>
+        <v>3,002</v>
       </c>
       <c r="F21" t="str">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G21" t="str">
-        <v>156,646</v>
+        <v>161,864</v>
       </c>
       <c r="H21" t="str">
         <v>5</v>
@@ -1314,13 +1314,13 @@
         <v>305,831,070</v>
       </c>
       <c r="L21" t="str">
-        <v>9,071,289,286</v>
+        <v>9,074,344,452</v>
       </c>
       <c r="M21" t="str">
-        <v>370,683,171</v>
+        <v>375,745,531</v>
       </c>
       <c r="N21" t="str">
-        <v>4.09%</v>
+        <v>4.14%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>13,901</v>
+        <v>14,157</v>
       </c>
       <c r="F22" t="str">
-        <v>1,551</v>
+        <v>1,658</v>
       </c>
       <c r="G22" t="str">
-        <v>606,177</v>
+        <v>626,962</v>
       </c>
       <c r="H22" t="str">
         <v>49</v>
@@ -1352,19 +1352,19 @@
         <v>615,443,400</v>
       </c>
       <c r="J22" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" t="str">
-        <v>199,076,150</v>
+        <v>222,391,196</v>
       </c>
       <c r="L22" t="str">
-        <v>66,410,376,784</v>
+        <v>67,625,817,403</v>
       </c>
       <c r="M22" t="str">
-        <v>2,763,895,296</v>
+        <v>2,923,447,465</v>
       </c>
       <c r="N22" t="str">
-        <v>4.16%</v>
+        <v>4.32%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>8,136</v>
+        <v>8,148</v>
       </c>
       <c r="F24" t="str">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="G24" t="str">
-        <v>80,643</v>
+        <v>83,330</v>
       </c>
       <c r="H24" t="str">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I24" t="str">
-        <v>331,826,900</v>
+        <v>378,826,900</v>
       </c>
       <c r="J24" t="str">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K24" t="str">
-        <v>231,125,540</v>
+        <v>263,125,540</v>
       </c>
       <c r="L24" t="str">
-        <v>52,523,902,565</v>
+        <v>52,534,612,445</v>
       </c>
       <c r="M24" t="str">
-        <v>755,825,698</v>
+        <v>841,117,707</v>
       </c>
       <c r="N24" t="str">
-        <v>1.44%</v>
+        <v>1.60%</v>
       </c>
     </row>
     <row r="25">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>37,553</v>
+        <v>39,021</v>
       </c>
       <c r="F26" t="str">
-        <v>12,121</v>
+        <v>12,572</v>
       </c>
       <c r="G26" t="str">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H26" t="str">
         <v>20</v>
@@ -1534,13 +1534,13 @@
         <v>184,331,633</v>
       </c>
       <c r="L26" t="str">
-        <v>80,869,172,967</v>
+        <v>83,917,219,805</v>
       </c>
       <c r="M26" t="str">
-        <v>28,478,648,167</v>
+        <v>29,470,926,834</v>
       </c>
       <c r="N26" t="str">
-        <v>35.22%</v>
+        <v>35.12%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,34 +1557,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>5,688</v>
+        <v>5,858</v>
       </c>
       <c r="F27" t="str">
-        <v>3,107</v>
+        <v>3,223</v>
       </c>
       <c r="G27" t="str">
-        <v>5,795</v>
+        <v>5,986</v>
       </c>
       <c r="H27" t="str">
-        <v>890</v>
+        <v>929</v>
       </c>
       <c r="I27" t="str">
-        <v>11,079,184,633</v>
+        <v>11,557,647,431</v>
       </c>
       <c r="J27" t="str">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="K27" t="str">
-        <v>14,902,689,021</v>
+        <v>15,417,230,738</v>
       </c>
       <c r="L27" t="str">
-        <v>70,731,549,367</v>
+        <v>72,882,410,505</v>
       </c>
       <c r="M27" t="str">
-        <v>33,515,639,456</v>
+        <v>34,770,738,471</v>
       </c>
       <c r="N27" t="str">
-        <v>47.38%</v>
+        <v>47.71%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>5,364</v>
+        <v>5,574</v>
       </c>
       <c r="F28" t="str">
-        <v>2,734</v>
+        <v>2,844</v>
       </c>
       <c r="G28" t="str">
-        <v>5,402</v>
+        <v>5,621</v>
       </c>
       <c r="H28" t="str">
-        <v>852</v>
+        <v>896</v>
       </c>
       <c r="I28" t="str">
-        <v>10,657,848,057</v>
+        <v>11,200,810,735</v>
       </c>
       <c r="J28" t="str">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="K28" t="str">
-        <v>13,520,709,523</v>
+        <v>14,124,709,071</v>
       </c>
       <c r="L28" t="str">
-        <v>66,538,859,221</v>
+        <v>69,258,636,613</v>
       </c>
       <c r="M28" t="str">
-        <v>30,843,143,867</v>
+        <v>32,186,872,373</v>
       </c>
       <c r="N28" t="str">
-        <v>46.35%</v>
+        <v>46.47%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,34 +1645,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>3,470</v>
+        <v>3,596</v>
       </c>
       <c r="F29" t="str">
-        <v>1,829</v>
+        <v>1,893</v>
       </c>
       <c r="G29" t="str">
-        <v>3,635</v>
+        <v>3,765</v>
       </c>
       <c r="H29" t="str">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="I29" t="str">
-        <v>6,863,575,165</v>
+        <v>7,062,384,846</v>
       </c>
       <c r="J29" t="str">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="K29" t="str">
-        <v>10,042,183,303</v>
+        <v>10,393,088,969</v>
       </c>
       <c r="L29" t="str">
-        <v>43,116,749,808</v>
+        <v>44,768,385,674</v>
       </c>
       <c r="M29" t="str">
-        <v>20,775,417,289</v>
+        <v>21,460,185,549</v>
       </c>
       <c r="N29" t="str">
-        <v>48.18%</v>
+        <v>47.94%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>38,821</v>
+        <v>40,197</v>
       </c>
       <c r="F30" t="str">
-        <v>12,861</v>
+        <v>13,321</v>
       </c>
       <c r="G30" t="str">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H30" t="str">
         <v>16</v>
@@ -1710,13 +1710,13 @@
         <v>223,318,503</v>
       </c>
       <c r="L30" t="str">
-        <v>83,662,804,698</v>
+        <v>86,489,940,489</v>
       </c>
       <c r="M30" t="str">
-        <v>30,468,556,159</v>
+        <v>31,441,138,008</v>
       </c>
       <c r="N30" t="str">
-        <v>36.42%</v>
+        <v>36.35%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,489</v>
+        <v>3,635</v>
       </c>
       <c r="F31" t="str">
-        <v>1,554</v>
+        <v>1,605</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>1,338,529,502</v>
+        <v>1,397,321,948</v>
       </c>
       <c r="M31" t="str">
-        <v>601,322,073</v>
+        <v>620,967,556</v>
       </c>
       <c r="N31" t="str">
-        <v>44.92%</v>
+        <v>44.44%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,351</v>
+        <v>2,443</v>
       </c>
       <c r="F32" t="str">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="G32" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" t="str">
         <v>0</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>4,121,453,636</v>
+        <v>4,266,737,536</v>
       </c>
       <c r="M32" t="str">
-        <v>671,048,658</v>
+        <v>709,851,620</v>
       </c>
       <c r="N32" t="str">
-        <v>16.28%</v>
+        <v>16.64%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>2,947</v>
+        <v>3,062</v>
       </c>
       <c r="F33" t="str">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="G33" t="str">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H33" t="str">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>5,114,690,074</v>
+        <v>5,368,392,703</v>
       </c>
       <c r="M33" t="str">
-        <v>736,647,721</v>
+        <v>769,596,583</v>
       </c>
       <c r="N33" t="str">
-        <v>14.40%</v>
+        <v>14.34%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,13 +1865,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>12,469</v>
+        <v>12,983</v>
       </c>
       <c r="F34" t="str">
-        <v>2,077</v>
+        <v>2,166</v>
       </c>
       <c r="G34" t="str">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H34" t="str">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>22,832,288,997</v>
+        <v>23,707,190,734</v>
       </c>
       <c r="M34" t="str">
-        <v>3,225,783,510</v>
+        <v>3,360,915,068</v>
       </c>
       <c r="N34" t="str">
-        <v>14.13%</v>
+        <v>14.18%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,34 +1909,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>2,360</v>
+        <v>2,408</v>
       </c>
       <c r="F35" t="str">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="G35" t="str">
-        <v>7,546</v>
+        <v>7,764</v>
       </c>
       <c r="H35" t="str">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I35" t="str">
-        <v>1,773,578,007</v>
+        <v>1,808,246,413</v>
       </c>
       <c r="J35" t="str">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K35" t="str">
-        <v>1,504,762,781</v>
+        <v>1,560,637,549</v>
       </c>
       <c r="L35" t="str">
-        <v>26,296,587,259</v>
+        <v>26,825,700,990</v>
       </c>
       <c r="M35" t="str">
-        <v>4,629,967,475</v>
+        <v>4,720,527,120</v>
       </c>
       <c r="N35" t="str">
-        <v>17.61%</v>
+        <v>17.60%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,19 +1953,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>1,990</v>
+        <v>2,039</v>
       </c>
       <c r="F36" t="str">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="G36" t="str">
-        <v>5,694</v>
+        <v>5,879</v>
       </c>
       <c r="H36" t="str">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I36" t="str">
-        <v>1,125,517,570</v>
+        <v>1,213,738,882</v>
       </c>
       <c r="J36" t="str">
         <v>58</v>
@@ -1974,13 +1974,13 @@
         <v>1,130,617,732</v>
       </c>
       <c r="L36" t="str">
-        <v>21,524,850,781</v>
+        <v>22,016,340,506</v>
       </c>
       <c r="M36" t="str">
-        <v>3,428,641,839</v>
+        <v>3,552,482,879</v>
       </c>
       <c r="N36" t="str">
-        <v>15.93%</v>
+        <v>16.14%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,13 +1997,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>11,175</v>
+        <v>11,595</v>
       </c>
       <c r="F37" t="str">
-        <v>1,762</v>
+        <v>1,824</v>
       </c>
       <c r="G37" t="str">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="H37" t="str">
         <v>4</v>
@@ -2018,13 +2018,13 @@
         <v>18,815,020</v>
       </c>
       <c r="L37" t="str">
-        <v>19,986,503,712</v>
+        <v>20,666,120,309</v>
       </c>
       <c r="M37" t="str">
-        <v>3,386,077,810</v>
+        <v>3,482,342,239</v>
       </c>
       <c r="N37" t="str">
-        <v>16.94%</v>
+        <v>16.85%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,241</v>
+        <v>1,281</v>
       </c>
       <c r="F38" t="str">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="G38" t="str">
         <v>15</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>549,119,447</v>
+        <v>565,167,608</v>
       </c>
       <c r="M38" t="str">
-        <v>139,044,438</v>
+        <v>143,432,662</v>
       </c>
       <c r="N38" t="str">
-        <v>25.32%</v>
+        <v>25.38%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,717</v>
+        <v>3,830</v>
       </c>
       <c r="F39" t="str">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="G39" t="str">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>6,689,591,045</v>
+        <v>6,850,841,748</v>
       </c>
       <c r="M39" t="str">
-        <v>940,047,375</v>
+        <v>970,795,979</v>
       </c>
       <c r="N39" t="str">
-        <v>14.05%</v>
+        <v>14.17%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,10 +2173,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>3,442</v>
+        <v>3,546</v>
       </c>
       <c r="F41" t="str">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="G41" t="str">
         <v>44</v>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>6,109,734,043</v>
+        <v>6,262,980,118</v>
       </c>
       <c r="M41" t="str">
-        <v>890,470,289</v>
+        <v>924,892,965</v>
       </c>
       <c r="N41" t="str">
-        <v>14.57%</v>
+        <v>14.77%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>3,522</v>
+        <v>3,625</v>
       </c>
       <c r="F42" t="str">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="G42" t="str">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>6,515,892,055</v>
+        <v>6,716,192,176</v>
       </c>
       <c r="M42" t="str">
-        <v>928,778,434</v>
+        <v>964,139,696</v>
       </c>
       <c r="N42" t="str">
-        <v>14.25%</v>
+        <v>14.36%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,34 +2261,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>9,810</v>
+        <v>10,061</v>
       </c>
       <c r="F43" t="str">
-        <v>526</v>
+        <v>548</v>
       </c>
       <c r="G43" t="str">
-        <v>12,992</v>
+        <v>13,355</v>
       </c>
       <c r="H43" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" t="str">
-        <v>73,710,127</v>
+        <v>86,631,182</v>
       </c>
       <c r="J43" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" t="str">
-        <v>35,905,362</v>
+        <v>51,408,852</v>
       </c>
       <c r="L43" t="str">
-        <v>27,294,973,703</v>
+        <v>27,880,742,270</v>
       </c>
       <c r="M43" t="str">
-        <v>935,093,259</v>
+        <v>983,774,860</v>
       </c>
       <c r="N43" t="str">
-        <v>3.43%</v>
+        <v>3.53%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>13,511</v>
+        <v>13,888</v>
       </c>
       <c r="F44" t="str">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="G44" t="str">
-        <v>18,448</v>
+        <v>18,969</v>
       </c>
       <c r="H44" t="str">
         <v>25</v>
@@ -2326,13 +2326,13 @@
         <v>295,302,942</v>
       </c>
       <c r="L44" t="str">
-        <v>37,919,860,462</v>
+        <v>38,822,046,444</v>
       </c>
       <c r="M44" t="str">
-        <v>1,829,947,849</v>
+        <v>1,892,273,542</v>
       </c>
       <c r="N44" t="str">
-        <v>4.83%</v>
+        <v>4.87%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,524</v>
+        <v>1,824</v>
       </c>
       <c r="F45" t="str">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="G45" t="str">
-        <v>531</v>
+        <v>659</v>
       </c>
       <c r="H45" t="str">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>5,335,924,985</v>
+        <v>6,074,452,480</v>
       </c>
       <c r="M45" t="str">
-        <v>158,023,856</v>
+        <v>181,595,717</v>
       </c>
       <c r="N45" t="str">
-        <v>2.96%</v>
+        <v>2.99%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,34 +2393,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>9,092</v>
+        <v>9,367</v>
       </c>
       <c r="F46" t="str">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="G46" t="str">
-        <v>11,167</v>
+        <v>11,573</v>
       </c>
       <c r="H46" t="str">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I46" t="str">
-        <v>271,588,148</v>
+        <v>308,161,434</v>
       </c>
       <c r="J46" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K46" t="str">
-        <v>158,259,221</v>
+        <v>190,149,331</v>
       </c>
       <c r="L46" t="str">
-        <v>25,656,392,672</v>
+        <v>26,396,801,211</v>
       </c>
       <c r="M46" t="str">
-        <v>1,310,752,731</v>
+        <v>1,413,844,788</v>
       </c>
       <c r="N46" t="str">
-        <v>5.11%</v>
+        <v>5.36%</v>
       </c>
     </row>
     <row r="47">
@@ -2440,10 +2440,10 @@
         <v>822</v>
       </c>
       <c r="F47" t="str">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G47" t="str">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H47" t="str">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         <v>415,553,850</v>
       </c>
       <c r="M47" t="str">
-        <v>49,421,914</v>
+        <v>50,915,188</v>
       </c>
       <c r="N47" t="str">
-        <v>11.89%</v>
+        <v>12.25%</v>
       </c>
     </row>
   </sheetData>
